--- a/artfynd/A 55431-2024 artfynd.xlsx
+++ b/artfynd/A 55431-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121252238</v>
       </c>
       <c r="B2" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 55431-2024 artfynd.xlsx
+++ b/artfynd/A 55431-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121252238</v>
       </c>
       <c r="B2" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 55431-2024 artfynd.xlsx
+++ b/artfynd/A 55431-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121252238</v>
       </c>
       <c r="B2" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 55431-2024 artfynd.xlsx
+++ b/artfynd/A 55431-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121252238</v>
       </c>
       <c r="B2" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 55431-2024 artfynd.xlsx
+++ b/artfynd/A 55431-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122818536</v>
+        <v>122817714</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,42 +802,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528665</v>
+        <v>528625</v>
       </c>
       <c r="R3" t="n">
-        <v>6998574</v>
+        <v>6998424</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,14 +859,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,19 +891,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122817714</v>
+        <v>122817546</v>
       </c>
       <c r="B4" t="n">
         <v>74863</v>
@@ -938,13 +943,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528625</v>
+        <v>528628</v>
       </c>
       <c r="R4" t="n">
-        <v>6998424</v>
+        <v>6998367</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -983,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1015,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122817546</v>
+        <v>122817758</v>
       </c>
       <c r="B5" t="n">
-        <v>74863</v>
+        <v>77699</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,13 +1060,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528628</v>
+        <v>528610</v>
       </c>
       <c r="R5" t="n">
-        <v>6998367</v>
+        <v>6998403</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1090,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1132,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122817758</v>
+        <v>122818536</v>
       </c>
       <c r="B6" t="n">
-        <v>77699</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,34 +1153,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528610</v>
+        <v>528665</v>
       </c>
       <c r="R6" t="n">
-        <v>6998403</v>
+        <v>6998574</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,24 +1215,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,12 +1237,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1620,7 +1620,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122816988</v>
+        <v>122817142</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1659,24 +1659,19 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528756</v>
+        <v>528699</v>
       </c>
       <c r="R10" t="n">
-        <v>6998450</v>
+        <v>6998430</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1710,7 +1705,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en tall.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1721,31 +1716,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1762,7 +1732,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122817142</v>
+        <v>122817550</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1807,10 +1777,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528699</v>
+        <v>528648</v>
       </c>
       <c r="R11" t="n">
-        <v>6998430</v>
+        <v>6998358</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1874,10 +1844,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122817550</v>
+        <v>122817112</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>78762</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1890,27 +1860,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1919,13 +1893,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528648</v>
+        <v>528711</v>
       </c>
       <c r="R12" t="n">
-        <v>6998358</v>
+        <v>6998411</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1952,14 +1926,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1974,22 +1958,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122817112</v>
+        <v>122816988</v>
       </c>
       <c r="B13" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2002,31 +1986,32 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2035,13 +2020,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528711</v>
+        <v>528756</v>
       </c>
       <c r="R13" t="n">
-        <v>6998411</v>
+        <v>6998450</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2068,24 +2053,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Äldre ringhack på en tall.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2096,16 +2071,41 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2224,10 +2224,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122817127</v>
+        <v>122817942</v>
       </c>
       <c r="B15" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2240,36 +2240,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2278,10 +2269,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528700</v>
+        <v>528655</v>
       </c>
       <c r="R15" t="n">
-        <v>6998476</v>
+        <v>6998433</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2316,6 +2307,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2324,11 +2320,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2345,10 +2336,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122817942</v>
+        <v>122818032</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>79872</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2357,43 +2348,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528655</v>
+        <v>528631</v>
       </c>
       <c r="R16" t="n">
-        <v>6998433</v>
+        <v>6998469</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2426,11 +2412,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2457,10 +2438,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122818032</v>
+        <v>122818026</v>
       </c>
       <c r="B17" t="n">
-        <v>79872</v>
+        <v>79843</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2469,25 +2450,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2559,10 +2540,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122818026</v>
+        <v>122816979</v>
       </c>
       <c r="B18" t="n">
-        <v>79843</v>
+        <v>78499</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2575,21 +2556,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2599,13 +2580,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528631</v>
+        <v>528730</v>
       </c>
       <c r="R18" t="n">
-        <v>6998469</v>
+        <v>6998447</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2632,9 +2613,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På kolad ved</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2649,22 +2645,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122816979</v>
+        <v>122818653</v>
       </c>
       <c r="B19" t="n">
-        <v>78499</v>
+        <v>79843</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2677,21 +2673,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2701,10 +2697,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528730</v>
+        <v>528732</v>
       </c>
       <c r="R19" t="n">
-        <v>6998447</v>
+        <v>6998541</v>
       </c>
       <c r="S19" t="n">
         <v>8</v>
@@ -2736,7 +2732,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2746,12 +2742,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På kolad ved</t>
+          <t>På asplåga i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2766,22 +2762,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122818930</v>
+        <v>122818174</v>
       </c>
       <c r="B20" t="n">
-        <v>98347</v>
+        <v>57478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2790,51 +2786,46 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528680</v>
+        <v>528625</v>
       </c>
       <c r="R20" t="n">
-        <v>6998601</v>
+        <v>6998500</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2868,7 +2859,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Minst 32 st skott/stjälkar och 10 st vinterståndare inom ca 1 m2. Finns troligen fler skott under barmarkssäsongen.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2879,11 +2870,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2900,10 +2886,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122818653</v>
+        <v>122818168</v>
       </c>
       <c r="B21" t="n">
-        <v>79843</v>
+        <v>79803</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2912,25 +2898,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2940,13 +2926,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528732</v>
+        <v>528669</v>
       </c>
       <c r="R21" t="n">
-        <v>6998541</v>
+        <v>6998500</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2975,7 +2961,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2985,12 +2971,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På asplåga i gammal barrblandskog</t>
+          <t>På bark på stam av död gammal asp (40 cm dbh) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3001,6 +2987,21 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3017,10 +3018,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122818174</v>
+        <v>122817339</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>79380</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3033,42 +3034,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528625</v>
+        <v>528649</v>
       </c>
       <c r="R22" t="n">
-        <v>6998500</v>
+        <v>6998383</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3095,14 +3091,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3117,22 +3123,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122818168</v>
+        <v>122818573</v>
       </c>
       <c r="B23" t="n">
-        <v>79803</v>
+        <v>78762</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3141,41 +3147,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528669</v>
+        <v>528630</v>
       </c>
       <c r="R23" t="n">
-        <v>6998500</v>
+        <v>6998539</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3202,26 +3208,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På bark på stam av död gammal asp (40 cm dbh) i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3231,40 +3222,50 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122818573</v>
+        <v>122818323</v>
       </c>
       <c r="B24" t="n">
-        <v>78762</v>
+        <v>79843</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3277,37 +3278,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528630</v>
+        <v>528667</v>
       </c>
       <c r="R24" t="n">
-        <v>6998539</v>
+        <v>6998534</v>
       </c>
       <c r="S24" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3334,11 +3335,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt på bark på stam av levande gammal sälg i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3347,51 +3363,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122818323</v>
+        <v>122818387</v>
       </c>
       <c r="B25" t="n">
-        <v>79843</v>
+        <v>78762</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3404,21 +3395,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3428,13 +3419,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528667</v>
+        <v>528619</v>
       </c>
       <c r="R25" t="n">
-        <v>6998534</v>
+        <v>6998495</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3461,26 +3452,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt på bark på stam av levande gammal sälg i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3489,26 +3465,51 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122818387</v>
+        <v>122817869</v>
       </c>
       <c r="B26" t="n">
-        <v>78762</v>
+        <v>57499</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3517,38 +3518,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100110</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528619</v>
+        <v>528645</v>
       </c>
       <c r="R26" t="n">
-        <v>6998495</v>
+        <v>6998384</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3591,31 +3601,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3632,10 +3617,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122817339</v>
+        <v>122817054</v>
       </c>
       <c r="B27" t="n">
-        <v>79380</v>
+        <v>79747</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3644,25 +3629,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6456</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3672,13 +3657,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528649</v>
+        <v>528755</v>
       </c>
       <c r="R27" t="n">
-        <v>6998383</v>
+        <v>6998448</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3707,7 +3692,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3717,12 +3702,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gammal tallstubbe</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3737,22 +3722,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122817869</v>
+        <v>122818247</v>
       </c>
       <c r="B28" t="n">
-        <v>57499</v>
+        <v>78762</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3761,47 +3746,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100110</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528645</v>
+        <v>528605</v>
       </c>
       <c r="R28" t="n">
-        <v>6998384</v>
+        <v>6998454</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3844,6 +3820,31 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3860,10 +3861,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122817054</v>
+        <v>122817289</v>
       </c>
       <c r="B29" t="n">
-        <v>79747</v>
+        <v>79141</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3872,25 +3873,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6456</v>
+        <v>257107</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blek lundlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Bacidia rosellizans</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>S.Ekman</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3900,13 +3901,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528755</v>
+        <v>528632</v>
       </c>
       <c r="R29" t="n">
-        <v>6998448</v>
+        <v>6998403</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3935,7 +3936,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3945,7 +3946,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3977,10 +3978,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122818247</v>
+        <v>122818955</v>
       </c>
       <c r="B30" t="n">
-        <v>78762</v>
+        <v>74786</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3993,34 +3994,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1460</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528605</v>
+        <v>528791</v>
       </c>
       <c r="R30" t="n">
-        <v>6998454</v>
+        <v>6998633</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4050,11 +4056,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4063,51 +4084,26 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122817289</v>
+        <v>122818321</v>
       </c>
       <c r="B31" t="n">
-        <v>79141</v>
+        <v>74863</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4120,21 +4116,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>257107</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blek lundlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bacidia rosellizans</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>S.Ekman</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4144,13 +4140,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528632</v>
+        <v>528805</v>
       </c>
       <c r="R31" t="n">
-        <v>6998403</v>
+        <v>6998631</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4179,7 +4175,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4189,12 +4185,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4209,22 +4205,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122818955</v>
+        <v>122818864</v>
       </c>
       <c r="B32" t="n">
-        <v>74786</v>
+        <v>74863</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4237,42 +4233,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1460</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528791</v>
+        <v>528732</v>
       </c>
       <c r="R32" t="n">
-        <v>6998633</v>
+        <v>6998659</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4301,7 +4292,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4311,12 +4302,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4343,10 +4334,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122818321</v>
+        <v>122817657</v>
       </c>
       <c r="B33" t="n">
-        <v>74863</v>
+        <v>78762</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4359,21 +4350,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4383,13 +4374,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528805</v>
+        <v>528650</v>
       </c>
       <c r="R33" t="n">
-        <v>6998631</v>
+        <v>6998397</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4416,24 +4407,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4444,26 +4425,51 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122818864</v>
+        <v>122817325</v>
       </c>
       <c r="B34" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4476,37 +4482,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528732</v>
+        <v>528640</v>
       </c>
       <c r="R34" t="n">
-        <v>6998659</v>
+        <v>6998336</v>
       </c>
       <c r="S34" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4533,24 +4544,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4565,22 +4566,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122819024</v>
+        <v>122817554</v>
       </c>
       <c r="B35" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4593,37 +4594,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528636</v>
+        <v>528648</v>
       </c>
       <c r="R35" t="n">
-        <v>6998609</v>
+        <v>6998359</v>
       </c>
       <c r="S35" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4655,6 +4661,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4663,31 +4674,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Dead branch  # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4704,7 +4690,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122817657</v>
+        <v>122819024</v>
       </c>
       <c r="B36" t="n">
         <v>78762</v>
@@ -4740,17 +4726,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528650</v>
+        <v>528636</v>
       </c>
       <c r="R36" t="n">
-        <v>6998397</v>
+        <v>6998609</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4782,11 +4768,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4798,27 +4779,27 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4836,10 +4817,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122817325</v>
+        <v>122818514</v>
       </c>
       <c r="B37" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4852,39 +4833,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528640</v>
+        <v>528635</v>
       </c>
       <c r="R37" t="n">
-        <v>6998336</v>
+        <v>6998546</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4917,11 +4893,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4948,10 +4919,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122817554</v>
+        <v>122817273</v>
       </c>
       <c r="B38" t="n">
-        <v>57478</v>
+        <v>78762</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4964,27 +4935,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4993,13 +4968,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528648</v>
+        <v>528623</v>
       </c>
       <c r="R38" t="n">
-        <v>6998359</v>
+        <v>6998311</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5026,14 +5001,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5048,22 +5033,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122817273</v>
+        <v>122817601</v>
       </c>
       <c r="B39" t="n">
-        <v>78762</v>
+        <v>90960</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5076,46 +5061,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528623</v>
+        <v>528645</v>
       </c>
       <c r="R39" t="n">
-        <v>6998311</v>
+        <v>6998384</v>
       </c>
       <c r="S39" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5142,24 +5118,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5174,22 +5135,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122817601</v>
+        <v>122818204</v>
       </c>
       <c r="B40" t="n">
-        <v>90960</v>
+        <v>79843</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5202,21 +5163,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5226,13 +5187,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528645</v>
+        <v>528649</v>
       </c>
       <c r="R40" t="n">
-        <v>6998384</v>
+        <v>6998490</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5259,9 +5220,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På innerbark på gammal björkhögstubbe i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5276,22 +5252,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122818514</v>
+        <v>122816987</v>
       </c>
       <c r="B41" t="n">
-        <v>74863</v>
+        <v>79380</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5304,37 +5280,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528635</v>
+        <v>528755</v>
       </c>
       <c r="R41" t="n">
-        <v>6998546</v>
+        <v>6998446</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5361,9 +5337,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På bränd jöttetallstubbe</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5378,22 +5369,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122816987</v>
+        <v>122818025</v>
       </c>
       <c r="B42" t="n">
-        <v>79380</v>
+        <v>79844</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5406,21 +5397,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5430,13 +5421,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528755</v>
+        <v>528631</v>
       </c>
       <c r="R42" t="n">
-        <v>6998446</v>
+        <v>6998469</v>
       </c>
       <c r="S42" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5463,24 +5454,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>09:04</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>09:04</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På bränd jöttetallstubbe</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5495,22 +5471,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122818025</v>
+        <v>122818035</v>
       </c>
       <c r="B43" t="n">
-        <v>79844</v>
+        <v>79803</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5519,25 +5495,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>229497</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5547,10 +5523,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528631</v>
+        <v>528677</v>
       </c>
       <c r="R43" t="n">
-        <v>6998469</v>
+        <v>6998487</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5580,9 +5556,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5597,22 +5588,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122818035</v>
+        <v>122817278</v>
       </c>
       <c r="B44" t="n">
-        <v>79803</v>
+        <v>57478</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5621,38 +5612,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528677</v>
+        <v>528671</v>
       </c>
       <c r="R44" t="n">
-        <v>6998487</v>
+        <v>6998337</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5682,24 +5678,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5714,22 +5700,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122818204</v>
+        <v>122817186</v>
       </c>
       <c r="B45" t="n">
-        <v>79843</v>
+        <v>57428</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5738,41 +5724,55 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>102621</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528649</v>
+        <v>528689</v>
       </c>
       <c r="R45" t="n">
-        <v>6998490</v>
+        <v>6998416</v>
       </c>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5799,24 +5799,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>10:09</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>10:09</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På innerbark på gammal björkhögstubbe i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5831,22 +5816,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122817278</v>
+        <v>122818122</v>
       </c>
       <c r="B46" t="n">
-        <v>57478</v>
+        <v>79844</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5859,39 +5844,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528671</v>
+        <v>528631</v>
       </c>
       <c r="R46" t="n">
-        <v>6998337</v>
+        <v>6998473</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5924,11 +5904,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5955,10 +5930,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122818122</v>
+        <v>122818125</v>
       </c>
       <c r="B47" t="n">
-        <v>79844</v>
+        <v>78499</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5971,21 +5946,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5995,10 +5970,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528631</v>
+        <v>528687</v>
       </c>
       <c r="R47" t="n">
-        <v>6998473</v>
+        <v>6998489</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6028,9 +6003,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal tallstubbe i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6045,22 +6035,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122818125</v>
+        <v>122818759</v>
       </c>
       <c r="B48" t="n">
-        <v>78499</v>
+        <v>79843</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6073,21 +6063,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6097,10 +6087,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528687</v>
+        <v>528778</v>
       </c>
       <c r="R48" t="n">
-        <v>6998489</v>
+        <v>6998602</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6132,7 +6122,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6142,12 +6132,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal tallstubbe i gammal barrblandskog</t>
+          <t>På gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6174,10 +6164,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122817186</v>
+        <v>122818713</v>
       </c>
       <c r="B49" t="n">
-        <v>57428</v>
+        <v>90940</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6186,52 +6176,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>102621</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528689</v>
+        <v>528718</v>
       </c>
       <c r="R49" t="n">
-        <v>6998416</v>
+        <v>6998641</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6290,7 +6266,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122818759</v>
+        <v>122818126</v>
       </c>
       <c r="B50" t="n">
         <v>79843</v>
@@ -6330,10 +6306,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528778</v>
+        <v>528624</v>
       </c>
       <c r="R50" t="n">
-        <v>6998602</v>
+        <v>6998489</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6363,24 +6339,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6395,22 +6356,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122818713</v>
+        <v>122817413</v>
       </c>
       <c r="B51" t="n">
-        <v>90940</v>
+        <v>57478</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6423,34 +6384,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528718</v>
+        <v>528612</v>
       </c>
       <c r="R51" t="n">
-        <v>6998641</v>
+        <v>6998323</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6483,6 +6449,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6509,10 +6480,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122818126</v>
+        <v>122818040</v>
       </c>
       <c r="B52" t="n">
-        <v>79843</v>
+        <v>78762</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6525,21 +6496,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6549,13 +6520,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>528624</v>
+        <v>528621</v>
       </c>
       <c r="R52" t="n">
-        <v>6998489</v>
+        <v>6998383</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6595,6 +6566,31 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6611,10 +6607,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122818770</v>
+        <v>122817937</v>
       </c>
       <c r="B53" t="n">
-        <v>91231</v>
+        <v>90951</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6623,41 +6619,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>1205</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>528718</v>
+        <v>528686</v>
       </c>
       <c r="R53" t="n">
-        <v>6998641</v>
+        <v>6998446</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6684,9 +6680,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På död asp</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6701,19 +6712,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122817413</v>
+        <v>122817037</v>
       </c>
       <c r="B54" t="n">
         <v>57478</v>
@@ -6752,19 +6763,24 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>528612</v>
+        <v>528752</v>
       </c>
       <c r="R54" t="n">
-        <v>6998323</v>
+        <v>6998456</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6798,7 +6814,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6809,6 +6825,31 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6825,10 +6866,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122818040</v>
+        <v>122818770</v>
       </c>
       <c r="B55" t="n">
-        <v>78762</v>
+        <v>91231</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6841,37 +6882,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>528621</v>
+        <v>528718</v>
       </c>
       <c r="R55" t="n">
-        <v>6998383</v>
+        <v>6998641</v>
       </c>
       <c r="S55" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6911,31 +6952,6 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6952,10 +6968,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122817937</v>
+        <v>122818966</v>
       </c>
       <c r="B56" t="n">
-        <v>90951</v>
+        <v>79843</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6964,41 +6980,46 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>528686</v>
+        <v>528791</v>
       </c>
       <c r="R56" t="n">
-        <v>6998446</v>
+        <v>6998599</v>
       </c>
       <c r="S56" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7027,7 +7048,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7037,12 +7058,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På död asp</t>
+          <t>På bark på stam av levande gammal sälg (25 cm dbh) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7053,26 +7074,41 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122817037</v>
+        <v>122819397</v>
       </c>
       <c r="B57" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7085,16 +7121,16 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -7102,30 +7138,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>528752</v>
+        <v>528826</v>
       </c>
       <c r="R57" t="n">
-        <v>6998456</v>
+        <v>6998595</v>
       </c>
       <c r="S57" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7157,11 +7192,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7170,31 +7200,6 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7211,10 +7216,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122818966</v>
+        <v>122818613</v>
       </c>
       <c r="B58" t="n">
-        <v>79843</v>
+        <v>98347</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7223,31 +7228,40 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7256,13 +7270,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>528791</v>
+        <v>528723</v>
       </c>
       <c r="R58" t="n">
-        <v>6998599</v>
+        <v>6998554</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7291,7 +7305,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7301,12 +7315,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg (25 cm dbh) i gammal barrblandskog</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7317,21 +7331,6 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7348,10 +7347,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122819397</v>
+        <v>122818681</v>
       </c>
       <c r="B59" t="n">
-        <v>57494</v>
+        <v>78762</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7364,46 +7363,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>528826</v>
+        <v>528686</v>
       </c>
       <c r="R59" t="n">
-        <v>6998595</v>
+        <v>6998618</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7443,6 +7433,31 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7459,10 +7474,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122818613</v>
+        <v>122818503</v>
       </c>
       <c r="B60" t="n">
-        <v>98347</v>
+        <v>57478</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7471,55 +7486,46 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>528723</v>
+        <v>528652</v>
       </c>
       <c r="R60" t="n">
-        <v>6998554</v>
+        <v>6998555</v>
       </c>
       <c r="S60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7546,24 +7552,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7578,19 +7574,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122818681</v>
+        <v>122817110</v>
       </c>
       <c r="B61" t="n">
         <v>78762</v>
@@ -7626,14 +7622,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>528686</v>
+        <v>528711</v>
       </c>
       <c r="R61" t="n">
-        <v>6998618</v>
+        <v>6998430</v>
       </c>
       <c r="S61" t="n">
         <v>12</v>
@@ -7663,11 +7659,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7676,51 +7687,26 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122818503</v>
+        <v>122817219</v>
       </c>
       <c r="B62" t="n">
-        <v>57478</v>
+        <v>78762</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7733,42 +7719,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>528652</v>
+        <v>528684</v>
       </c>
       <c r="R62" t="n">
-        <v>6998555</v>
+        <v>6998437</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7802,7 +7783,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7813,6 +7794,31 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7829,10 +7835,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122817110</v>
+        <v>122817645</v>
       </c>
       <c r="B63" t="n">
-        <v>78762</v>
+        <v>57499</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7841,41 +7847,50 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100110</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>528711</v>
+        <v>528643</v>
       </c>
       <c r="R63" t="n">
-        <v>6998430</v>
+        <v>6998354</v>
       </c>
       <c r="S63" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7904,7 +7919,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7914,12 +7929,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:11</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7946,10 +7956,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122817219</v>
+        <v>122818534</v>
       </c>
       <c r="B64" t="n">
-        <v>78762</v>
+        <v>79809</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7958,41 +7968,46 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>528684</v>
+        <v>528727</v>
       </c>
       <c r="R64" t="n">
-        <v>6998437</v>
+        <v>6998595</v>
       </c>
       <c r="S64" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8019,14 +8034,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8037,51 +8062,26 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122817645</v>
+        <v>122817517</v>
       </c>
       <c r="B65" t="n">
-        <v>57499</v>
+        <v>78407</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8090,37 +8090,28 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100110</v>
+        <v>353</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
@@ -8133,7 +8124,7 @@
         <v>6998354</v>
       </c>
       <c r="S65" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8162,7 +8153,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8172,7 +8163,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På ved på gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8199,10 +8195,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122818534</v>
+        <v>122818675</v>
       </c>
       <c r="B66" t="n">
-        <v>79809</v>
+        <v>78762</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8211,31 +8207,35 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8244,13 +8244,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>528727</v>
+        <v>528722</v>
       </c>
       <c r="R66" t="n">
-        <v>6998595</v>
+        <v>6998660</v>
       </c>
       <c r="S66" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8279,7 +8279,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8289,12 +8289,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:23</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På gammal asp</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8321,10 +8316,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122817517</v>
+        <v>122818328</v>
       </c>
       <c r="B67" t="n">
-        <v>78407</v>
+        <v>77699</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8337,21 +8332,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>228579</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8361,13 +8356,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>528643</v>
+        <v>528800</v>
       </c>
       <c r="R67" t="n">
-        <v>6998354</v>
+        <v>6998633</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8396,7 +8391,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8406,12 +8401,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>På ved på gammal tallstubbe</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8426,19 +8421,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122818675</v>
+        <v>122817144</v>
       </c>
       <c r="B68" t="n">
         <v>78762</v>
@@ -8473,7 +8468,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8487,13 +8482,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>528722</v>
+        <v>528705</v>
       </c>
       <c r="R68" t="n">
-        <v>6998660</v>
+        <v>6998384</v>
       </c>
       <c r="S68" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8522,7 +8517,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8532,7 +8527,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8559,10 +8554,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122818328</v>
+        <v>122819379</v>
       </c>
       <c r="B69" t="n">
-        <v>77699</v>
+        <v>98347</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8571,41 +8566,50 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>528800</v>
+        <v>528802</v>
       </c>
       <c r="R69" t="n">
-        <v>6998633</v>
+        <v>6998594</v>
       </c>
       <c r="S69" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8634,7 +8638,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8644,12 +8648,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8664,19 +8668,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122817144</v>
+        <v>122819118</v>
       </c>
       <c r="B70" t="n">
         <v>78762</v>
@@ -8709,29 +8713,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>528705</v>
+        <v>528690</v>
       </c>
       <c r="R70" t="n">
-        <v>6998384</v>
+        <v>6998652</v>
       </c>
       <c r="S70" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8758,19 +8753,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>09:13</t>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8781,26 +8771,51 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122819379</v>
+        <v>122818036</v>
       </c>
       <c r="B71" t="n">
-        <v>98347</v>
+        <v>79747</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8809,50 +8824,41 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>528802</v>
+        <v>528686</v>
       </c>
       <c r="R71" t="n">
-        <v>6998594</v>
+        <v>6998471</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8881,7 +8887,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8891,12 +8897,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8923,7 +8929,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122819118</v>
+        <v>122819058</v>
       </c>
       <c r="B72" t="n">
         <v>78762</v>
@@ -8963,10 +8969,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>528690</v>
+        <v>528654</v>
       </c>
       <c r="R72" t="n">
-        <v>6998652</v>
+        <v>6998628</v>
       </c>
       <c r="S72" t="n">
         <v>9</v>
@@ -9001,11 +9007,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -9017,27 +9018,27 @@
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9055,10 +9056,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122818036</v>
+        <v>122817127</v>
       </c>
       <c r="B73" t="n">
-        <v>79747</v>
+        <v>57631</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9067,41 +9068,57 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6456</v>
+        <v>103021</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>528686</v>
+        <v>528700</v>
       </c>
       <c r="R73" t="n">
-        <v>6998471</v>
+        <v>6998476</v>
       </c>
       <c r="S73" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9128,24 +9145,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>Två observerade talltitor i flerskiktad gammal barrskog med flertalet murkna björkhögstubbar som lämpar sig för bobygge vid häckning.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9156,26 +9163,36 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>Gammal flerskiktad barrskog.</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122819058</v>
+        <v>122818930</v>
       </c>
       <c r="B74" t="n">
-        <v>78762</v>
+        <v>98347</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9184,41 +9201,51 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>528654</v>
+        <v>528680</v>
       </c>
       <c r="R74" t="n">
-        <v>6998628</v>
+        <v>6998601</v>
       </c>
       <c r="S74" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9250,6 +9277,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Minst 32 st skott/stjälkar och 10 st vinterståndare inom ca 1 m2. Finns troligen fler skott under barmarkssäsongen.</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -9261,27 +9293,7 @@
       </c>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>

--- a/artfynd/A 55431-2024 artfynd.xlsx
+++ b/artfynd/A 55431-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122817714</v>
+        <v>122817142</v>
       </c>
       <c r="B3" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,37 +802,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528625</v>
+        <v>528699</v>
       </c>
       <c r="R3" t="n">
-        <v>6998424</v>
+        <v>6998430</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,24 +864,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,22 +886,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122817546</v>
+        <v>122818165</v>
       </c>
       <c r="B4" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,21 +914,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528628</v>
+        <v>528594</v>
       </c>
       <c r="R4" t="n">
-        <v>6998367</v>
+        <v>6998419</v>
       </c>
       <c r="S4" t="n">
         <v>8</v>
@@ -976,26 +971,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1004,26 +984,51 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122817758</v>
+        <v>122817110</v>
       </c>
       <c r="B5" t="n">
-        <v>77699</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1041,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,13 +1065,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528610</v>
+        <v>528711</v>
       </c>
       <c r="R5" t="n">
-        <v>6998403</v>
+        <v>6998430</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,12 +1110,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,22 +1130,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122818536</v>
+        <v>122818026</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,39 +1158,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528665</v>
+        <v>528631</v>
       </c>
       <c r="R6" t="n">
-        <v>6998574</v>
+        <v>6998469</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,11 +1218,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122818165</v>
+        <v>122819448</v>
       </c>
       <c r="B7" t="n">
-        <v>78762</v>
+        <v>79876</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,41 +1256,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528594</v>
+        <v>528696</v>
       </c>
       <c r="R7" t="n">
-        <v>6998419</v>
+        <v>6998688</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1327,6 +1327,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Frodiga bålar.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1341,24 +1346,14 @@
           <t>Tallskog</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Sten/berg på land</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Stone/rock on land</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1376,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122819448</v>
+        <v>122819397</v>
       </c>
       <c r="B8" t="n">
-        <v>79872</v>
+        <v>57494</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,31 +1383,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1421,10 +1420,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528696</v>
+        <v>528826</v>
       </c>
       <c r="R8" t="n">
-        <v>6998688</v>
+        <v>6998595</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1459,11 +1458,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Frodiga bålar.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1472,21 +1466,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1503,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122819033</v>
+        <v>122818247</v>
       </c>
       <c r="B9" t="n">
-        <v>74675</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1515,25 +1494,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1543,13 +1522,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528798</v>
+        <v>528605</v>
       </c>
       <c r="R9" t="n">
-        <v>6998603</v>
+        <v>6998454</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1576,26 +1555,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal sälg i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1604,26 +1568,51 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122817142</v>
+        <v>122818770</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>91235</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1636,39 +1625,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528699</v>
+        <v>528718</v>
       </c>
       <c r="R10" t="n">
-        <v>6998430</v>
+        <v>6998641</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1701,11 +1685,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1732,7 +1711,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122817550</v>
+        <v>122817413</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1777,10 +1756,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528648</v>
+        <v>528612</v>
       </c>
       <c r="R11" t="n">
-        <v>6998358</v>
+        <v>6998323</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1817,7 +1796,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1844,10 +1823,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122817112</v>
+        <v>122818040</v>
       </c>
       <c r="B12" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1877,29 +1856,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528711</v>
+        <v>528621</v>
       </c>
       <c r="R12" t="n">
-        <v>6998411</v>
+        <v>6998383</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1926,26 +1896,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1954,26 +1909,51 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122816988</v>
+        <v>122817758</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>77699</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1986,47 +1966,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528756</v>
+        <v>528610</v>
       </c>
       <c r="R13" t="n">
-        <v>6998450</v>
+        <v>6998403</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2053,14 +2023,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en tall.</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2071,51 +2051,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122818654</v>
+        <v>122818168</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>79807</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2124,43 +2079,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528711</v>
+        <v>528669</v>
       </c>
       <c r="R14" t="n">
-        <v>6998632</v>
+        <v>6998500</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2190,14 +2140,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På bark på stam av död gammal asp (40 cm dbh) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2208,23 +2168,38 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122817942</v>
+        <v>122817550</v>
       </c>
       <c r="B15" t="n">
         <v>57478</v>
@@ -2269,10 +2244,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528655</v>
+        <v>528648</v>
       </c>
       <c r="R15" t="n">
-        <v>6998433</v>
+        <v>6998358</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2309,7 +2284,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2336,10 +2311,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122818032</v>
+        <v>122817714</v>
       </c>
       <c r="B16" t="n">
-        <v>79872</v>
+        <v>74863</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2348,25 +2323,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2376,13 +2351,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528631</v>
+        <v>528625</v>
       </c>
       <c r="R16" t="n">
-        <v>6998469</v>
+        <v>6998424</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2409,9 +2384,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2426,22 +2416,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122818026</v>
+        <v>122817054</v>
       </c>
       <c r="B17" t="n">
-        <v>79843</v>
+        <v>79751</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2450,25 +2440,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2478,10 +2468,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528631</v>
+        <v>528755</v>
       </c>
       <c r="R17" t="n">
-        <v>6998469</v>
+        <v>6998448</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2511,9 +2501,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2528,22 +2533,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122816979</v>
+        <v>122818966</v>
       </c>
       <c r="B18" t="n">
-        <v>78499</v>
+        <v>79847</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2556,34 +2561,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528730</v>
+        <v>528791</v>
       </c>
       <c r="R18" t="n">
-        <v>6998447</v>
+        <v>6998599</v>
       </c>
       <c r="S18" t="n">
         <v>8</v>
@@ -2615,7 +2625,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2625,12 +2635,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På kolad ved</t>
+          <t>På bark på stam av levande gammal sälg (25 cm dbh) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2641,26 +2651,41 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122818653</v>
+        <v>122818573</v>
       </c>
       <c r="B19" t="n">
-        <v>79843</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2673,37 +2698,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528732</v>
+        <v>528630</v>
       </c>
       <c r="R19" t="n">
-        <v>6998541</v>
+        <v>6998539</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2730,26 +2755,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På asplåga i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2758,26 +2768,51 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122818174</v>
+        <v>122818025</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2790,39 +2825,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528625</v>
+        <v>528631</v>
       </c>
       <c r="R20" t="n">
-        <v>6998500</v>
+        <v>6998469</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2855,11 +2885,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2886,10 +2911,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122818168</v>
+        <v>122818174</v>
       </c>
       <c r="B21" t="n">
-        <v>79803</v>
+        <v>57478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2898,35 +2923,40 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528669</v>
+        <v>528625</v>
       </c>
       <c r="R21" t="n">
         <v>6998500</v>
@@ -2959,24 +2989,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På bark på stam av död gammal asp (40 cm dbh) i gammal barrblandskog</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2987,41 +3007,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122817339</v>
+        <v>122817144</v>
       </c>
       <c r="B22" t="n">
-        <v>79380</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3034,34 +3039,43 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528649</v>
+        <v>528705</v>
       </c>
       <c r="R22" t="n">
-        <v>6998383</v>
+        <v>6998384</v>
       </c>
       <c r="S22" t="n">
         <v>11</v>
@@ -3093,7 +3107,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3103,12 +3117,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:26</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På gammal tallstubbe</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3135,10 +3144,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122818573</v>
+        <v>122818036</v>
       </c>
       <c r="B23" t="n">
-        <v>78762</v>
+        <v>79751</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3147,41 +3156,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528630</v>
+        <v>528686</v>
       </c>
       <c r="R23" t="n">
-        <v>6998539</v>
+        <v>6998471</v>
       </c>
       <c r="S23" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3208,11 +3217,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3221,51 +3245,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122818323</v>
+        <v>122817273</v>
       </c>
       <c r="B24" t="n">
-        <v>79843</v>
+        <v>78766</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3278,37 +3277,46 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528667</v>
+        <v>528623</v>
       </c>
       <c r="R24" t="n">
-        <v>6998534</v>
+        <v>6998311</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3337,7 +3345,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3347,12 +3355,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Rikligt på bark på stam av levande gammal sälg i gammal barrblandskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3367,22 +3375,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122818387</v>
+        <v>122819058</v>
       </c>
       <c r="B25" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3415,17 +3423,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528619</v>
+        <v>528654</v>
       </c>
       <c r="R25" t="n">
-        <v>6998495</v>
+        <v>6998628</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3468,27 +3476,27 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3506,10 +3514,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122817869</v>
+        <v>122818122</v>
       </c>
       <c r="B26" t="n">
-        <v>57499</v>
+        <v>79848</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3518,47 +3526,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100110</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528645</v>
+        <v>528631</v>
       </c>
       <c r="R26" t="n">
-        <v>6998384</v>
+        <v>6998473</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3617,10 +3616,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122817054</v>
+        <v>122818125</v>
       </c>
       <c r="B27" t="n">
-        <v>79747</v>
+        <v>78503</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3629,25 +3628,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6456</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3657,10 +3656,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528755</v>
+        <v>528687</v>
       </c>
       <c r="R27" t="n">
-        <v>6998448</v>
+        <v>6998489</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3692,7 +3691,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3702,12 +3701,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>På kolad ved på gammal tallstubbe i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3734,10 +3733,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122818247</v>
+        <v>122818328</v>
       </c>
       <c r="B28" t="n">
-        <v>78762</v>
+        <v>77699</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3750,21 +3749,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3774,13 +3773,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528605</v>
+        <v>528800</v>
       </c>
       <c r="R28" t="n">
-        <v>6998454</v>
+        <v>6998633</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3807,11 +3806,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3820,51 +3834,26 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122817289</v>
+        <v>122817278</v>
       </c>
       <c r="B29" t="n">
-        <v>79141</v>
+        <v>57478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3877,37 +3866,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>257107</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blek lundlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bacidia rosellizans</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>S.Ekman</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528632</v>
+        <v>528671</v>
       </c>
       <c r="R29" t="n">
-        <v>6998403</v>
+        <v>6998337</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3934,24 +3928,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>09:23</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>09:23</t>
-        </is>
-      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3966,22 +3950,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122818955</v>
+        <v>122817869</v>
       </c>
       <c r="B30" t="n">
-        <v>74786</v>
+        <v>57499</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3990,31 +3974,35 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1460</v>
+        <v>100110</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4023,10 +4011,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528791</v>
+        <v>528645</v>
       </c>
       <c r="R30" t="n">
-        <v>6998633</v>
+        <v>6998384</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4056,24 +4044,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4088,22 +4061,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122818321</v>
+        <v>122816988</v>
       </c>
       <c r="B31" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4116,37 +4089,47 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528805</v>
+        <v>528756</v>
       </c>
       <c r="R31" t="n">
-        <v>6998631</v>
+        <v>6998450</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4173,24 +4156,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Äldre ringhack på en tall.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4201,26 +4174,51 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122818864</v>
+        <v>122817339</v>
       </c>
       <c r="B32" t="n">
-        <v>74863</v>
+        <v>79384</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4233,21 +4231,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4257,13 +4255,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528732</v>
+        <v>528649</v>
       </c>
       <c r="R32" t="n">
-        <v>6998659</v>
+        <v>6998383</v>
       </c>
       <c r="S32" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4292,7 +4290,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4302,12 +4300,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4334,10 +4332,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122817657</v>
+        <v>122819118</v>
       </c>
       <c r="B33" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4370,14 +4368,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528650</v>
+        <v>528690</v>
       </c>
       <c r="R33" t="n">
-        <v>6998397</v>
+        <v>6998652</v>
       </c>
       <c r="S33" t="n">
         <v>9</v>
@@ -4466,10 +4464,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122817325</v>
+        <v>122818514</v>
       </c>
       <c r="B34" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4482,39 +4480,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528640</v>
+        <v>528635</v>
       </c>
       <c r="R34" t="n">
-        <v>6998336</v>
+        <v>6998546</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4547,11 +4540,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4578,10 +4566,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122817554</v>
+        <v>122818864</v>
       </c>
       <c r="B35" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4594,42 +4582,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528648</v>
+        <v>528732</v>
       </c>
       <c r="R35" t="n">
-        <v>6998359</v>
+        <v>6998659</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4656,14 +4639,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4678,22 +4671,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122819024</v>
+        <v>122818759</v>
       </c>
       <c r="B36" t="n">
-        <v>78762</v>
+        <v>79847</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4706,37 +4699,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528636</v>
+        <v>528778</v>
       </c>
       <c r="R36" t="n">
-        <v>6998609</v>
+        <v>6998602</v>
       </c>
       <c r="S36" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4763,11 +4756,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På gammal asp i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4776,51 +4784,26 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Dead branch  # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122818514</v>
+        <v>122818032</v>
       </c>
       <c r="B37" t="n">
-        <v>74863</v>
+        <v>79876</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4829,38 +4812,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528635</v>
+        <v>528631</v>
       </c>
       <c r="R37" t="n">
-        <v>6998546</v>
+        <v>6998469</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4919,10 +4902,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122817273</v>
+        <v>122818503</v>
       </c>
       <c r="B38" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4935,46 +4918,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528623</v>
+        <v>528652</v>
       </c>
       <c r="R38" t="n">
-        <v>6998311</v>
+        <v>6998555</v>
       </c>
       <c r="S38" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5001,24 +4980,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5033,22 +5002,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122817601</v>
+        <v>122817325</v>
       </c>
       <c r="B39" t="n">
-        <v>90960</v>
+        <v>57478</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5061,34 +5030,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528645</v>
+        <v>528640</v>
       </c>
       <c r="R39" t="n">
-        <v>6998384</v>
+        <v>6998336</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5121,6 +5095,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5147,10 +5126,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122818204</v>
+        <v>122817554</v>
       </c>
       <c r="B40" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5163,37 +5142,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528649</v>
+        <v>528648</v>
       </c>
       <c r="R40" t="n">
-        <v>6998490</v>
+        <v>6998359</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5220,24 +5204,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>10:09</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>10:09</t>
-        </is>
-      </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På innerbark på gammal björkhögstubbe i gammal barrblandskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5252,22 +5226,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122816987</v>
+        <v>122817601</v>
       </c>
       <c r="B41" t="n">
-        <v>79380</v>
+        <v>90964</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5280,21 +5254,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5304,13 +5278,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528755</v>
+        <v>528645</v>
       </c>
       <c r="R41" t="n">
-        <v>6998446</v>
+        <v>6998384</v>
       </c>
       <c r="S41" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5337,24 +5311,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>09:04</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>09:04</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På bränd jöttetallstubbe</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5369,22 +5328,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122818025</v>
+        <v>122818675</v>
       </c>
       <c r="B42" t="n">
-        <v>79844</v>
+        <v>78766</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5397,37 +5356,46 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528631</v>
+        <v>528722</v>
       </c>
       <c r="R42" t="n">
-        <v>6998469</v>
+        <v>6998660</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5454,9 +5422,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5471,22 +5449,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122818035</v>
+        <v>122818204</v>
       </c>
       <c r="B43" t="n">
-        <v>79803</v>
+        <v>79847</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5495,25 +5473,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5523,13 +5501,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528677</v>
+        <v>528649</v>
       </c>
       <c r="R43" t="n">
-        <v>6998487</v>
+        <v>6998490</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5558,7 +5536,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5568,12 +5546,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>På innerbark på gammal björkhögstubbe i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5588,22 +5566,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122817278</v>
+        <v>122817937</v>
       </c>
       <c r="B44" t="n">
-        <v>57478</v>
+        <v>90955</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5612,46 +5590,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528671</v>
+        <v>528686</v>
       </c>
       <c r="R44" t="n">
-        <v>6998337</v>
+        <v>6998446</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5678,14 +5651,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På död asp</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5700,22 +5683,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122817186</v>
+        <v>122817112</v>
       </c>
       <c r="B45" t="n">
-        <v>57428</v>
+        <v>78766</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5724,40 +5707,35 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>102621</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5766,13 +5744,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528689</v>
+        <v>528711</v>
       </c>
       <c r="R45" t="n">
-        <v>6998416</v>
+        <v>6998411</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5799,9 +5777,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5816,22 +5809,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122818122</v>
+        <v>122817942</v>
       </c>
       <c r="B46" t="n">
-        <v>79844</v>
+        <v>57478</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5844,34 +5837,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528631</v>
+        <v>528655</v>
       </c>
       <c r="R46" t="n">
-        <v>6998473</v>
+        <v>6998433</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5904,6 +5902,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5930,10 +5933,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122818125</v>
+        <v>122818536</v>
       </c>
       <c r="B47" t="n">
-        <v>78499</v>
+        <v>57478</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5946,34 +5949,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528687</v>
+        <v>528665</v>
       </c>
       <c r="R47" t="n">
-        <v>6998489</v>
+        <v>6998574</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6003,24 +6011,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal tallstubbe i gammal barrblandskog</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6035,22 +6033,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122818759</v>
+        <v>122819379</v>
       </c>
       <c r="B48" t="n">
-        <v>79843</v>
+        <v>98355</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6059,41 +6057,50 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528778</v>
+        <v>528802</v>
       </c>
       <c r="R48" t="n">
-        <v>6998602</v>
+        <v>6998594</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6122,7 +6129,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6132,12 +6139,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På gammal asp i gammal barrblandskog</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6164,10 +6171,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122818713</v>
+        <v>122816987</v>
       </c>
       <c r="B49" t="n">
-        <v>90940</v>
+        <v>79384</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6180,37 +6187,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528718</v>
+        <v>528755</v>
       </c>
       <c r="R49" t="n">
-        <v>6998641</v>
+        <v>6998446</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6237,9 +6244,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På bränd jöttetallstubbe</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6254,22 +6276,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122818126</v>
+        <v>122817186</v>
       </c>
       <c r="B50" t="n">
-        <v>79843</v>
+        <v>57428</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6278,38 +6300,52 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>102621</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528624</v>
+        <v>528689</v>
       </c>
       <c r="R50" t="n">
-        <v>6998489</v>
+        <v>6998416</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6368,10 +6404,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122817413</v>
+        <v>122817645</v>
       </c>
       <c r="B51" t="n">
-        <v>57478</v>
+        <v>57499</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6380,31 +6416,35 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>100110</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6413,13 +6453,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528612</v>
+        <v>528643</v>
       </c>
       <c r="R51" t="n">
-        <v>6998323</v>
+        <v>6998354</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6446,14 +6486,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6468,22 +6513,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122818040</v>
+        <v>122817037</v>
       </c>
       <c r="B52" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6496,37 +6541,47 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>528621</v>
+        <v>528752</v>
       </c>
       <c r="R52" t="n">
-        <v>6998383</v>
+        <v>6998456</v>
       </c>
       <c r="S52" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6558,6 +6613,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6574,22 +6634,22 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6607,10 +6667,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122817937</v>
+        <v>122818713</v>
       </c>
       <c r="B53" t="n">
-        <v>90951</v>
+        <v>90944</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6619,41 +6679,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>528686</v>
+        <v>528718</v>
       </c>
       <c r="R53" t="n">
-        <v>6998446</v>
+        <v>6998641</v>
       </c>
       <c r="S53" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6680,24 +6740,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>På död asp</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6712,22 +6757,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122817037</v>
+        <v>122818387</v>
       </c>
       <c r="B54" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6740,47 +6785,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>528752</v>
+        <v>528619</v>
       </c>
       <c r="R54" t="n">
-        <v>6998456</v>
+        <v>6998495</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6812,11 +6847,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6833,22 +6863,22 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6866,10 +6896,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122818770</v>
+        <v>122818035</v>
       </c>
       <c r="B55" t="n">
-        <v>91231</v>
+        <v>79807</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6878,38 +6908,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>229497</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>528718</v>
+        <v>528677</v>
       </c>
       <c r="R55" t="n">
-        <v>6998641</v>
+        <v>6998487</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6939,9 +6969,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6956,22 +7001,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122818966</v>
+        <v>122817219</v>
       </c>
       <c r="B56" t="n">
-        <v>79843</v>
+        <v>78766</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6984,39 +7029,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>528791</v>
+        <v>528684</v>
       </c>
       <c r="R56" t="n">
-        <v>6998599</v>
+        <v>6998437</v>
       </c>
       <c r="S56" t="n">
         <v>8</v>
@@ -7046,24 +7086,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg (25 cm dbh) i gammal barrblandskog</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7075,40 +7105,50 @@
       <c r="AG56" t="b">
         <v>0</v>
       </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122819397</v>
+        <v>122818955</v>
       </c>
       <c r="B57" t="n">
-        <v>57494</v>
+        <v>74786</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7121,43 +7161,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>1460</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>528826</v>
+        <v>528791</v>
       </c>
       <c r="R57" t="n">
-        <v>6998595</v>
+        <v>6998633</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7187,9 +7223,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7204,22 +7255,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122818613</v>
+        <v>122817517</v>
       </c>
       <c r="B58" t="n">
-        <v>98347</v>
+        <v>78411</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7228,55 +7279,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>528723</v>
+        <v>528643</v>
       </c>
       <c r="R58" t="n">
-        <v>6998554</v>
+        <v>6998354</v>
       </c>
       <c r="S58" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7305,7 +7342,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7315,12 +7352,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>På ved på gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7347,10 +7384,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122818681</v>
+        <v>122817546</v>
       </c>
       <c r="B59" t="n">
-        <v>78762</v>
+        <v>74863</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7363,37 +7400,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>528686</v>
+        <v>528628</v>
       </c>
       <c r="R59" t="n">
-        <v>6998618</v>
+        <v>6998367</v>
       </c>
       <c r="S59" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7420,11 +7457,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -7433,51 +7485,26 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122818503</v>
+        <v>122818613</v>
       </c>
       <c r="B60" t="n">
-        <v>57478</v>
+        <v>98355</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7486,46 +7513,55 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>528652</v>
+        <v>528723</v>
       </c>
       <c r="R60" t="n">
-        <v>6998555</v>
+        <v>6998554</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7552,14 +7588,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7574,22 +7620,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122817110</v>
+        <v>122816979</v>
       </c>
       <c r="B61" t="n">
-        <v>78762</v>
+        <v>78503</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7602,21 +7648,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7626,13 +7672,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>528711</v>
+        <v>528730</v>
       </c>
       <c r="R61" t="n">
-        <v>6998430</v>
+        <v>6998447</v>
       </c>
       <c r="S61" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7661,7 +7707,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7671,12 +7717,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På kolad ved</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7691,22 +7737,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122817219</v>
+        <v>122818323</v>
       </c>
       <c r="B62" t="n">
-        <v>78762</v>
+        <v>79847</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7719,21 +7765,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7743,13 +7789,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>528684</v>
+        <v>528667</v>
       </c>
       <c r="R62" t="n">
-        <v>6998437</v>
+        <v>6998534</v>
       </c>
       <c r="S62" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7776,14 +7822,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Rikligt på bark på stam av levande gammal sälg i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7794,51 +7850,26 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122817645</v>
+        <v>122818126</v>
       </c>
       <c r="B63" t="n">
-        <v>57499</v>
+        <v>79847</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7847,50 +7878,41 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100110</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>528643</v>
+        <v>528624</v>
       </c>
       <c r="R63" t="n">
-        <v>6998354</v>
+        <v>6998489</v>
       </c>
       <c r="S63" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7917,19 +7939,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7944,22 +7956,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122818534</v>
+        <v>122818681</v>
       </c>
       <c r="B64" t="n">
-        <v>79809</v>
+        <v>78766</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7968,46 +7980,41 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>528727</v>
+        <v>528686</v>
       </c>
       <c r="R64" t="n">
-        <v>6998595</v>
+        <v>6998618</v>
       </c>
       <c r="S64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8034,26 +8041,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På gammal asp</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8062,26 +8054,51 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122817517</v>
+        <v>122817657</v>
       </c>
       <c r="B65" t="n">
-        <v>78407</v>
+        <v>78766</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8094,21 +8111,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8118,13 +8135,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>528643</v>
+        <v>528650</v>
       </c>
       <c r="R65" t="n">
-        <v>6998354</v>
+        <v>6998397</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8151,24 +8168,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På ved på gammal tallstubbe</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8179,26 +8186,51 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122818675</v>
+        <v>122819024</v>
       </c>
       <c r="B66" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8228,26 +8260,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>528722</v>
+        <v>528636</v>
       </c>
       <c r="R66" t="n">
-        <v>6998660</v>
+        <v>6998609</v>
       </c>
       <c r="S66" t="n">
         <v>12</v>
@@ -8277,21 +8300,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>10:31</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>10:31</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -8300,26 +8313,51 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Dead branch  # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122818328</v>
+        <v>122818653</v>
       </c>
       <c r="B67" t="n">
-        <v>77699</v>
+        <v>79847</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8332,21 +8370,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8356,13 +8394,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>528800</v>
+        <v>528732</v>
       </c>
       <c r="R67" t="n">
-        <v>6998633</v>
+        <v>6998541</v>
       </c>
       <c r="S67" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8391,7 +8429,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8401,12 +8439,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På asplåga i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8421,22 +8459,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122817144</v>
+        <v>122819033</v>
       </c>
       <c r="B68" t="n">
-        <v>78762</v>
+        <v>74675</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8445,50 +8483,41 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>528705</v>
+        <v>528798</v>
       </c>
       <c r="R68" t="n">
-        <v>6998384</v>
+        <v>6998603</v>
       </c>
       <c r="S68" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8517,7 +8546,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8527,7 +8556,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal sälg i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8542,22 +8576,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122819379</v>
+        <v>122818321</v>
       </c>
       <c r="B69" t="n">
-        <v>98347</v>
+        <v>74863</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8566,50 +8600,41 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>528802</v>
+        <v>528805</v>
       </c>
       <c r="R69" t="n">
-        <v>6998594</v>
+        <v>6998631</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8638,7 +8663,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8648,12 +8673,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8668,22 +8693,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122819118</v>
+        <v>122818654</v>
       </c>
       <c r="B70" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8696,37 +8721,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>528690</v>
+        <v>528711</v>
       </c>
       <c r="R70" t="n">
-        <v>6998652</v>
+        <v>6998632</v>
       </c>
       <c r="S70" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8760,7 +8790,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8771,31 +8801,6 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -8812,10 +8817,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122818036</v>
+        <v>122817289</v>
       </c>
       <c r="B71" t="n">
-        <v>79747</v>
+        <v>79145</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8824,25 +8829,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6456</v>
+        <v>257107</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blek lundlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Bacidia rosellizans</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>S.Ekman</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8852,13 +8857,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>528686</v>
+        <v>528632</v>
       </c>
       <c r="R71" t="n">
-        <v>6998471</v>
+        <v>6998403</v>
       </c>
       <c r="S71" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8887,7 +8892,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8897,7 +8902,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -8929,10 +8934,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122819058</v>
+        <v>122818534</v>
       </c>
       <c r="B72" t="n">
-        <v>78762</v>
+        <v>79813</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8941,41 +8946,46 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>528654</v>
+        <v>528727</v>
       </c>
       <c r="R72" t="n">
-        <v>6998628</v>
+        <v>6998595</v>
       </c>
       <c r="S72" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9002,11 +9012,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På gammal asp</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -9015,41 +9040,16 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -9192,7 +9192,7 @@
         <v>122818930</v>
       </c>
       <c r="B74" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>

--- a/artfynd/A 55431-2024 artfynd.xlsx
+++ b/artfynd/A 55431-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122817142</v>
+        <v>122818165</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,42 +802,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528699</v>
+        <v>528594</v>
       </c>
       <c r="R3" t="n">
-        <v>6998430</v>
+        <v>6998419</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,11 +864,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -882,6 +872,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -898,7 +913,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122818165</v>
+        <v>122817110</v>
       </c>
       <c r="B4" t="n">
         <v>78766</v>
@@ -938,13 +953,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528594</v>
+        <v>528711</v>
       </c>
       <c r="R4" t="n">
-        <v>6998419</v>
+        <v>6998430</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,11 +986,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -984,51 +1014,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122817110</v>
+        <v>122818026</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,21 +1046,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1065,13 +1070,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528711</v>
+        <v>528631</v>
       </c>
       <c r="R5" t="n">
-        <v>6998430</v>
+        <v>6998469</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,24 +1103,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:11</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,22 +1120,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122818026</v>
+        <v>122819448</v>
       </c>
       <c r="B6" t="n">
-        <v>79847</v>
+        <v>79876</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,38 +1144,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528631</v>
+        <v>528696</v>
       </c>
       <c r="R6" t="n">
-        <v>6998469</v>
+        <v>6998688</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,6 +1215,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Frodiga bålar.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1228,6 +1228,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stone/rock on land</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1244,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122819448</v>
+        <v>122819397</v>
       </c>
       <c r="B7" t="n">
-        <v>79876</v>
+        <v>57494</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,31 +1271,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1289,10 +1308,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528696</v>
+        <v>528826</v>
       </c>
       <c r="R7" t="n">
-        <v>6998688</v>
+        <v>6998595</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,11 +1346,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Frodiga bålar.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1340,21 +1354,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1371,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122819397</v>
+        <v>122817142</v>
       </c>
       <c r="B8" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,16 +1386,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1404,26 +1403,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528826</v>
+        <v>528699</v>
       </c>
       <c r="R8" t="n">
-        <v>6998595</v>
+        <v>6998430</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1456,6 +1451,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1950,10 +1950,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122817758</v>
+        <v>122817550</v>
       </c>
       <c r="B13" t="n">
-        <v>77699</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1966,34 +1966,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528610</v>
+        <v>528648</v>
       </c>
       <c r="R13" t="n">
-        <v>6998403</v>
+        <v>6998358</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2023,24 +2028,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2055,22 +2050,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122818168</v>
+        <v>122817714</v>
       </c>
       <c r="B14" t="n">
-        <v>79807</v>
+        <v>74863</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2079,25 +2074,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229497</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2107,13 +2102,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528669</v>
+        <v>528625</v>
       </c>
       <c r="R14" t="n">
-        <v>6998500</v>
+        <v>6998424</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2142,7 +2137,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2152,12 +2147,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På bark på stam av död gammal asp (40 cm dbh) i gammal barrblandskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2168,41 +2163,26 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122817550</v>
+        <v>122817054</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>79751</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2211,43 +2191,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528648</v>
+        <v>528755</v>
       </c>
       <c r="R15" t="n">
-        <v>6998358</v>
+        <v>6998448</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2277,14 +2252,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2299,22 +2284,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122817714</v>
+        <v>122818966</v>
       </c>
       <c r="B16" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2327,37 +2312,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528625</v>
+        <v>528791</v>
       </c>
       <c r="R16" t="n">
-        <v>6998424</v>
+        <v>6998599</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2386,7 +2376,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2396,12 +2386,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal sälg (25 cm dbh) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2412,26 +2402,41 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122817054</v>
+        <v>122817758</v>
       </c>
       <c r="B17" t="n">
-        <v>79751</v>
+        <v>77699</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2440,25 +2445,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6456</v>
+        <v>228579</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2468,10 +2473,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528755</v>
+        <v>528610</v>
       </c>
       <c r="R17" t="n">
-        <v>6998448</v>
+        <v>6998403</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2503,7 +2508,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2513,12 +2518,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2533,22 +2538,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122818966</v>
+        <v>122818168</v>
       </c>
       <c r="B18" t="n">
-        <v>79847</v>
+        <v>79807</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2557,46 +2562,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528791</v>
+        <v>528669</v>
       </c>
       <c r="R18" t="n">
-        <v>6998599</v>
+        <v>6998500</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg (25 cm dbh) i gammal barrblandskog</t>
+          <t>På bark på stam av död gammal asp (40 cm dbh) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2654,17 +2654,17 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -4566,10 +4566,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122818864</v>
+        <v>122818503</v>
       </c>
       <c r="B35" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4582,37 +4582,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528732</v>
+        <v>528652</v>
       </c>
       <c r="R35" t="n">
-        <v>6998659</v>
+        <v>6998555</v>
       </c>
       <c r="S35" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4639,24 +4644,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4671,22 +4666,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122818759</v>
+        <v>122817325</v>
       </c>
       <c r="B36" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4699,34 +4694,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528778</v>
+        <v>528640</v>
       </c>
       <c r="R36" t="n">
-        <v>6998602</v>
+        <v>6998336</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4756,24 +4756,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På gammal asp i gammal barrblandskog</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4788,22 +4778,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122818032</v>
+        <v>122817554</v>
       </c>
       <c r="B37" t="n">
-        <v>79876</v>
+        <v>57478</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4812,38 +4802,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528631</v>
+        <v>528648</v>
       </c>
       <c r="R37" t="n">
-        <v>6998469</v>
+        <v>6998359</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4876,6 +4871,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4902,10 +4902,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122818503</v>
+        <v>122818864</v>
       </c>
       <c r="B38" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4918,42 +4918,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528652</v>
+        <v>528732</v>
       </c>
       <c r="R38" t="n">
-        <v>6998555</v>
+        <v>6998659</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4980,14 +4975,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5002,22 +5007,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122817325</v>
+        <v>122818759</v>
       </c>
       <c r="B39" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5030,39 +5035,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528640</v>
+        <v>528778</v>
       </c>
       <c r="R39" t="n">
-        <v>6998336</v>
+        <v>6998602</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5092,14 +5092,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5114,22 +5124,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122817554</v>
+        <v>122818032</v>
       </c>
       <c r="B40" t="n">
-        <v>57478</v>
+        <v>79876</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5138,43 +5148,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528648</v>
+        <v>528631</v>
       </c>
       <c r="R40" t="n">
-        <v>6998359</v>
+        <v>6998469</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5207,11 +5212,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5238,10 +5238,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122817601</v>
+        <v>122818675</v>
       </c>
       <c r="B41" t="n">
-        <v>90964</v>
+        <v>78766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5254,37 +5254,46 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528645</v>
+        <v>528722</v>
       </c>
       <c r="R41" t="n">
-        <v>6998384</v>
+        <v>6998660</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5311,9 +5320,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5328,22 +5347,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122818675</v>
+        <v>122818204</v>
       </c>
       <c r="B42" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5356,46 +5375,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528722</v>
+        <v>528649</v>
       </c>
       <c r="R42" t="n">
-        <v>6998660</v>
+        <v>6998490</v>
       </c>
       <c r="S42" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5424,7 +5434,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5434,7 +5444,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På innerbark på gammal björkhögstubbe i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5449,22 +5464,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122818204</v>
+        <v>122817601</v>
       </c>
       <c r="B43" t="n">
-        <v>79847</v>
+        <v>90964</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5477,21 +5492,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5501,13 +5516,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528649</v>
+        <v>528645</v>
       </c>
       <c r="R43" t="n">
-        <v>6998490</v>
+        <v>6998384</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5534,24 +5549,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>10:09</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>10:09</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På innerbark på gammal björkhögstubbe i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5566,12 +5566,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -6404,10 +6404,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122817645</v>
+        <v>122818713</v>
       </c>
       <c r="B51" t="n">
-        <v>57499</v>
+        <v>90944</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6416,50 +6416,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100110</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528643</v>
+        <v>528718</v>
       </c>
       <c r="R51" t="n">
-        <v>6998354</v>
+        <v>6998641</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6486,19 +6477,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6513,22 +6494,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122817037</v>
+        <v>122817645</v>
       </c>
       <c r="B52" t="n">
-        <v>57478</v>
+        <v>57499</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6537,36 +6518,35 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>100110</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6575,13 +6555,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>528752</v>
+        <v>528643</v>
       </c>
       <c r="R52" t="n">
-        <v>6998456</v>
+        <v>6998354</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6608,14 +6588,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6626,51 +6611,26 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122818713</v>
+        <v>122817037</v>
       </c>
       <c r="B53" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6683,37 +6643,47 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>528718</v>
+        <v>528752</v>
       </c>
       <c r="R53" t="n">
-        <v>6998641</v>
+        <v>6998456</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6745,6 +6715,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6753,6 +6728,31 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">

--- a/artfynd/A 55431-2024 artfynd.xlsx
+++ b/artfynd/A 55431-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122818165</v>
+        <v>122818955</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>74786</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,37 +802,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1460</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528594</v>
+        <v>528791</v>
       </c>
       <c r="R3" t="n">
-        <v>6998419</v>
+        <v>6998633</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,11 +864,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -872,51 +892,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122817110</v>
+        <v>122818126</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,21 +924,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,13 +948,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528711</v>
+        <v>528624</v>
       </c>
       <c r="R4" t="n">
-        <v>6998430</v>
+        <v>6998489</v>
       </c>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,24 +981,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:11</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:11</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,22 +998,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122818026</v>
+        <v>122818168</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>79807</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,25 +1022,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1070,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528631</v>
+        <v>528669</v>
       </c>
       <c r="R5" t="n">
-        <v>6998469</v>
+        <v>6998500</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,11 +1083,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På bark på stam av död gammal asp (40 cm dbh) i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1116,26 +1111,41 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122819448</v>
+        <v>122818864</v>
       </c>
       <c r="B6" t="n">
-        <v>79876</v>
+        <v>74863</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,46 +1154,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528696</v>
+        <v>528732</v>
       </c>
       <c r="R6" t="n">
-        <v>6998688</v>
+        <v>6998659</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1210,14 +1215,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Frodiga bålar.</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,41 +1243,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122819397</v>
+        <v>122817657</v>
       </c>
       <c r="B7" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,46 +1275,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528826</v>
+        <v>528650</v>
       </c>
       <c r="R7" t="n">
-        <v>6998595</v>
+        <v>6998397</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1346,6 +1337,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1354,6 +1350,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1482,10 +1503,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122818247</v>
+        <v>122819448</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,38 +1515,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528605</v>
+        <v>528696</v>
       </c>
       <c r="R9" t="n">
-        <v>6998454</v>
+        <v>6998688</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1560,6 +1586,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Frodiga bålar.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1574,24 +1605,14 @@
           <t>Tallskog</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Sten/berg på land</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stone/rock on land</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1609,10 +1630,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122818770</v>
+        <v>122818573</v>
       </c>
       <c r="B10" t="n">
-        <v>91235</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1625,21 +1646,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1649,13 +1670,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528718</v>
+        <v>528630</v>
       </c>
       <c r="R10" t="n">
-        <v>6998641</v>
+        <v>6998539</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1695,6 +1716,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1711,10 +1757,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122817413</v>
+        <v>122818025</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1727,39 +1773,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528612</v>
+        <v>528631</v>
       </c>
       <c r="R11" t="n">
-        <v>6998323</v>
+        <v>6998469</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1792,11 +1833,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1823,10 +1859,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122818040</v>
+        <v>122817325</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1839,37 +1875,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528621</v>
+        <v>528640</v>
       </c>
       <c r="R12" t="n">
-        <v>6998383</v>
+        <v>6998336</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1901,6 +1942,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1909,31 +1955,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1950,10 +1971,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122817550</v>
+        <v>122817054</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>79751</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1962,43 +1983,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528648</v>
+        <v>528755</v>
       </c>
       <c r="R13" t="n">
-        <v>6998358</v>
+        <v>6998448</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2028,14 +2044,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2050,22 +2076,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122817714</v>
+        <v>122818328</v>
       </c>
       <c r="B14" t="n">
-        <v>74863</v>
+        <v>77699</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2078,21 +2104,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2102,10 +2128,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528625</v>
+        <v>528800</v>
       </c>
       <c r="R14" t="n">
-        <v>6998424</v>
+        <v>6998633</v>
       </c>
       <c r="S14" t="n">
         <v>9</v>
@@ -2137,7 +2163,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2147,7 +2173,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2179,10 +2205,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122817054</v>
+        <v>122818165</v>
       </c>
       <c r="B15" t="n">
-        <v>79751</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2191,25 +2217,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2219,13 +2245,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528755</v>
+        <v>528594</v>
       </c>
       <c r="R15" t="n">
-        <v>6998448</v>
+        <v>6998419</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2252,26 +2278,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>09:08</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>09:08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2280,26 +2291,51 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122818966</v>
+        <v>122817219</v>
       </c>
       <c r="B16" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2312,39 +2348,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528791</v>
+        <v>528684</v>
       </c>
       <c r="R16" t="n">
-        <v>6998599</v>
+        <v>6998437</v>
       </c>
       <c r="S16" t="n">
         <v>8</v>
@@ -2374,24 +2405,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg (25 cm dbh) i gammal barrblandskog</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2403,40 +2424,50 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122817758</v>
+        <v>122817554</v>
       </c>
       <c r="B17" t="n">
-        <v>77699</v>
+        <v>57478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2449,34 +2480,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528610</v>
+        <v>528648</v>
       </c>
       <c r="R17" t="n">
-        <v>6998403</v>
+        <v>6998359</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2506,24 +2542,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2538,22 +2564,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122818168</v>
+        <v>122817550</v>
       </c>
       <c r="B18" t="n">
-        <v>79807</v>
+        <v>57478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2562,38 +2588,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528669</v>
+        <v>528648</v>
       </c>
       <c r="R18" t="n">
-        <v>6998500</v>
+        <v>6998358</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2623,24 +2654,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På bark på stam av död gammal asp (40 cm dbh) i gammal barrblandskog</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2651,41 +2672,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122818573</v>
+        <v>122818770</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>91235</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2698,21 +2704,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2722,13 +2728,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528630</v>
+        <v>528718</v>
       </c>
       <c r="R19" t="n">
-        <v>6998539</v>
+        <v>6998641</v>
       </c>
       <c r="S19" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2768,31 +2774,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2809,10 +2790,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122818025</v>
+        <v>122818204</v>
       </c>
       <c r="B20" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2825,21 +2806,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2849,13 +2830,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528631</v>
+        <v>528649</v>
       </c>
       <c r="R20" t="n">
-        <v>6998469</v>
+        <v>6998490</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2882,9 +2863,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På innerbark på gammal björkhögstubbe i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2899,19 +2895,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122818174</v>
+        <v>122818503</v>
       </c>
       <c r="B21" t="n">
         <v>57478</v>
@@ -2952,14 +2948,14 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528625</v>
+        <v>528652</v>
       </c>
       <c r="R21" t="n">
-        <v>6998500</v>
+        <v>6998555</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2996,7 +2992,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3023,10 +3019,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122817144</v>
+        <v>122818174</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3039,31 +3035,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3072,13 +3064,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528705</v>
+        <v>528625</v>
       </c>
       <c r="R22" t="n">
-        <v>6998384</v>
+        <v>6998500</v>
       </c>
       <c r="S22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3105,19 +3097,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>09:13</t>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3132,22 +3119,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122818036</v>
+        <v>122817601</v>
       </c>
       <c r="B23" t="n">
-        <v>79751</v>
+        <v>90964</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3156,25 +3143,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6456</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3184,13 +3171,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528686</v>
+        <v>528645</v>
       </c>
       <c r="R23" t="n">
-        <v>6998471</v>
+        <v>6998384</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3217,24 +3204,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3249,19 +3221,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122817273</v>
+        <v>122818675</v>
       </c>
       <c r="B24" t="n">
         <v>78766</v>
@@ -3296,7 +3268,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3310,13 +3282,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528623</v>
+        <v>528722</v>
       </c>
       <c r="R24" t="n">
-        <v>6998311</v>
+        <v>6998660</v>
       </c>
       <c r="S24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3345,7 +3317,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3355,12 +3327,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:22</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3387,10 +3354,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122819058</v>
+        <v>122816988</v>
       </c>
       <c r="B25" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3403,37 +3370,47 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528654</v>
+        <v>528756</v>
       </c>
       <c r="R25" t="n">
-        <v>6998628</v>
+        <v>6998450</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3465,6 +3442,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en tall.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3476,7 +3458,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -3491,12 +3473,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3514,10 +3496,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122818122</v>
+        <v>122818536</v>
       </c>
       <c r="B26" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3530,34 +3512,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528631</v>
+        <v>528665</v>
       </c>
       <c r="R26" t="n">
-        <v>6998473</v>
+        <v>6998574</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3590,6 +3577,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3616,10 +3608,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122818125</v>
+        <v>122818035</v>
       </c>
       <c r="B27" t="n">
-        <v>78503</v>
+        <v>79807</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3628,25 +3620,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>229497</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3656,10 +3648,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528687</v>
+        <v>528677</v>
       </c>
       <c r="R27" t="n">
-        <v>6998489</v>
+        <v>6998487</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3691,7 +3683,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3701,12 +3693,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal tallstubbe i gammal barrblandskog</t>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3721,22 +3713,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122818328</v>
+        <v>122818613</v>
       </c>
       <c r="B28" t="n">
-        <v>77699</v>
+        <v>98355</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3745,38 +3737,52 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528800</v>
+        <v>528723</v>
       </c>
       <c r="R28" t="n">
-        <v>6998633</v>
+        <v>6998554</v>
       </c>
       <c r="S28" t="n">
         <v>9</v>
@@ -3808,7 +3814,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3818,12 +3824,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3838,22 +3844,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122817278</v>
+        <v>122817714</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3866,42 +3872,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528671</v>
+        <v>528625</v>
       </c>
       <c r="R29" t="n">
-        <v>6998337</v>
+        <v>6998424</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3928,14 +3929,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3950,22 +3961,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122817869</v>
+        <v>122818032</v>
       </c>
       <c r="B30" t="n">
-        <v>57499</v>
+        <v>79876</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3978,43 +3989,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100110</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528645</v>
+        <v>528631</v>
       </c>
       <c r="R30" t="n">
-        <v>6998384</v>
+        <v>6998469</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4073,10 +4075,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122816988</v>
+        <v>122819033</v>
       </c>
       <c r="B31" t="n">
-        <v>57478</v>
+        <v>74675</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4085,51 +4087,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6428</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528756</v>
+        <v>528798</v>
       </c>
       <c r="R31" t="n">
-        <v>6998450</v>
+        <v>6998603</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4156,14 +4148,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en tall.</t>
+          <t>På bark på stam av levande gammal sälg i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4174,51 +4176,26 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122817339</v>
+        <v>122817144</v>
       </c>
       <c r="B32" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4231,34 +4208,43 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528649</v>
+        <v>528705</v>
       </c>
       <c r="R32" t="n">
-        <v>6998383</v>
+        <v>6998384</v>
       </c>
       <c r="S32" t="n">
         <v>11</v>
@@ -4290,7 +4276,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4300,12 +4286,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:26</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På gammal tallstubbe</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4332,10 +4313,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122819118</v>
+        <v>122819379</v>
       </c>
       <c r="B33" t="n">
-        <v>78766</v>
+        <v>98355</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4344,41 +4325,50 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528690</v>
+        <v>528802</v>
       </c>
       <c r="R33" t="n">
-        <v>6998652</v>
+        <v>6998594</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4405,14 +4395,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4423,51 +4423,26 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122818514</v>
+        <v>122819397</v>
       </c>
       <c r="B34" t="n">
-        <v>74863</v>
+        <v>57494</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4480,34 +4455,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528635</v>
+        <v>528826</v>
       </c>
       <c r="R34" t="n">
-        <v>6998546</v>
+        <v>6998595</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4566,10 +4550,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122818503</v>
+        <v>122817869</v>
       </c>
       <c r="B35" t="n">
-        <v>57478</v>
+        <v>57499</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4578,43 +4562,47 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>100110</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528652</v>
+        <v>528645</v>
       </c>
       <c r="R35" t="n">
-        <v>6998555</v>
+        <v>6998384</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4647,11 +4635,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4678,10 +4661,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122817325</v>
+        <v>122816979</v>
       </c>
       <c r="B36" t="n">
-        <v>57478</v>
+        <v>78503</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4694,42 +4677,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528640</v>
+        <v>528730</v>
       </c>
       <c r="R36" t="n">
-        <v>6998336</v>
+        <v>6998447</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4756,14 +4734,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På kolad ved</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4778,22 +4766,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122817554</v>
+        <v>122818125</v>
       </c>
       <c r="B37" t="n">
-        <v>57478</v>
+        <v>78503</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4806,39 +4794,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528648</v>
+        <v>528687</v>
       </c>
       <c r="R37" t="n">
-        <v>6998359</v>
+        <v>6998489</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4868,14 +4851,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På kolad ved på gammal tallstubbe i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4890,22 +4883,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122818864</v>
+        <v>122817289</v>
       </c>
       <c r="B38" t="n">
-        <v>74863</v>
+        <v>79145</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4918,21 +4911,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>257107</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blek lundlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bacidia rosellizans</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>S.Ekman</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4942,13 +4935,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528732</v>
+        <v>528632</v>
       </c>
       <c r="R38" t="n">
-        <v>6998659</v>
+        <v>6998403</v>
       </c>
       <c r="S38" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4977,7 +4970,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4987,12 +4980,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5007,22 +5000,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122818759</v>
+        <v>122817942</v>
       </c>
       <c r="B39" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5035,34 +5028,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528778</v>
+        <v>528655</v>
       </c>
       <c r="R39" t="n">
-        <v>6998602</v>
+        <v>6998433</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5092,24 +5090,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På gammal asp i gammal barrblandskog</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5124,22 +5112,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122818032</v>
+        <v>122817645</v>
       </c>
       <c r="B40" t="n">
-        <v>79876</v>
+        <v>57499</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5152,37 +5140,46 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>100110</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528631</v>
+        <v>528643</v>
       </c>
       <c r="R40" t="n">
-        <v>6998469</v>
+        <v>6998354</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5209,9 +5206,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5226,22 +5233,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122818675</v>
+        <v>122818653</v>
       </c>
       <c r="B41" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5254,46 +5261,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528722</v>
+        <v>528732</v>
       </c>
       <c r="R41" t="n">
-        <v>6998660</v>
+        <v>6998541</v>
       </c>
       <c r="S41" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5322,7 +5320,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5332,7 +5330,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På asplåga i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5347,22 +5350,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122818204</v>
+        <v>122818514</v>
       </c>
       <c r="B42" t="n">
-        <v>79847</v>
+        <v>74863</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5375,37 +5378,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528649</v>
+        <v>528635</v>
       </c>
       <c r="R42" t="n">
-        <v>6998490</v>
+        <v>6998546</v>
       </c>
       <c r="S42" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5432,24 +5435,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>10:09</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>10:09</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På innerbark på gammal björkhögstubbe i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5464,22 +5452,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122817601</v>
+        <v>122819058</v>
       </c>
       <c r="B43" t="n">
-        <v>90964</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5492,37 +5480,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528645</v>
+        <v>528654</v>
       </c>
       <c r="R43" t="n">
-        <v>6998384</v>
+        <v>6998628</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5562,6 +5550,31 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5578,10 +5591,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122817937</v>
+        <v>122819024</v>
       </c>
       <c r="B44" t="n">
-        <v>90955</v>
+        <v>78766</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5590,38 +5603,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528686</v>
+        <v>528636</v>
       </c>
       <c r="R44" t="n">
-        <v>6998446</v>
+        <v>6998609</v>
       </c>
       <c r="S44" t="n">
         <v>12</v>
@@ -5651,26 +5664,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På död asp</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5679,26 +5677,51 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Dead branch  # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122817112</v>
+        <v>122818759</v>
       </c>
       <c r="B45" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5711,46 +5734,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528711</v>
+        <v>528778</v>
       </c>
       <c r="R45" t="n">
-        <v>6998411</v>
+        <v>6998602</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5779,7 +5793,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5789,12 +5803,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5809,22 +5823,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122817942</v>
+        <v>122817110</v>
       </c>
       <c r="B46" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5837,42 +5851,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528655</v>
+        <v>528711</v>
       </c>
       <c r="R46" t="n">
-        <v>6998433</v>
+        <v>6998430</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5899,14 +5908,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5921,19 +5940,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122818536</v>
+        <v>122817037</v>
       </c>
       <c r="B47" t="n">
         <v>57478</v>
@@ -5972,19 +5991,24 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528665</v>
+        <v>528752</v>
       </c>
       <c r="R47" t="n">
-        <v>6998574</v>
+        <v>6998456</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6018,7 +6042,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6029,6 +6053,31 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6045,10 +6094,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122819379</v>
+        <v>122817546</v>
       </c>
       <c r="B48" t="n">
-        <v>98355</v>
+        <v>74863</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6057,50 +6106,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528802</v>
+        <v>528628</v>
       </c>
       <c r="R48" t="n">
-        <v>6998594</v>
+        <v>6998367</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6129,7 +6169,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6139,12 +6179,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6159,22 +6199,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122816987</v>
+        <v>122818040</v>
       </c>
       <c r="B49" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6187,21 +6227,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6211,13 +6251,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528755</v>
+        <v>528621</v>
       </c>
       <c r="R49" t="n">
-        <v>6998446</v>
+        <v>6998383</v>
       </c>
       <c r="S49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6244,26 +6284,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>09:04</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>09:04</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På bränd jöttetallstubbe</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6272,26 +6297,51 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122817186</v>
+        <v>122819118</v>
       </c>
       <c r="B50" t="n">
-        <v>57428</v>
+        <v>78766</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6300,55 +6350,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>102621</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528689</v>
+        <v>528690</v>
       </c>
       <c r="R50" t="n">
-        <v>6998416</v>
+        <v>6998652</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6380,6 +6416,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6388,6 +6429,31 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6404,10 +6470,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122818713</v>
+        <v>122817339</v>
       </c>
       <c r="B51" t="n">
-        <v>90944</v>
+        <v>79384</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6420,37 +6486,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528718</v>
+        <v>528649</v>
       </c>
       <c r="R51" t="n">
-        <v>6998641</v>
+        <v>6998383</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6477,9 +6543,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6494,22 +6575,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122817645</v>
+        <v>122816987</v>
       </c>
       <c r="B52" t="n">
-        <v>57499</v>
+        <v>79384</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6518,50 +6599,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100110</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>528643</v>
+        <v>528755</v>
       </c>
       <c r="R52" t="n">
-        <v>6998354</v>
+        <v>6998446</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6590,7 +6662,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6600,7 +6672,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På bränd jöttetallstubbe</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6627,10 +6704,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122817037</v>
+        <v>122817112</v>
       </c>
       <c r="B53" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6643,32 +6720,31 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6677,10 +6753,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>528752</v>
+        <v>528711</v>
       </c>
       <c r="R53" t="n">
-        <v>6998456</v>
+        <v>6998411</v>
       </c>
       <c r="S53" t="n">
         <v>9</v>
@@ -6710,14 +6786,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall.</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6728,51 +6814,26 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122818387</v>
+        <v>122818534</v>
       </c>
       <c r="B54" t="n">
-        <v>78766</v>
+        <v>79813</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6781,41 +6842,46 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>528619</v>
+        <v>528727</v>
       </c>
       <c r="R54" t="n">
-        <v>6998495</v>
+        <v>6998595</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6842,11 +6908,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>På gammal asp</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6855,51 +6936,26 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122818035</v>
+        <v>122818387</v>
       </c>
       <c r="B55" t="n">
-        <v>79807</v>
+        <v>78766</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6908,25 +6964,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6936,10 +6992,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>528677</v>
+        <v>528619</v>
       </c>
       <c r="R55" t="n">
-        <v>6998487</v>
+        <v>6998495</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6969,26 +7025,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>På gammal asp</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6997,26 +7038,51 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122817219</v>
+        <v>122817937</v>
       </c>
       <c r="B56" t="n">
-        <v>78766</v>
+        <v>90955</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7025,25 +7091,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7053,13 +7119,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>528684</v>
+        <v>528686</v>
       </c>
       <c r="R56" t="n">
-        <v>6998437</v>
+        <v>6998446</v>
       </c>
       <c r="S56" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7086,14 +7152,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På död asp</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7104,51 +7180,26 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122818955</v>
+        <v>122818036</v>
       </c>
       <c r="B57" t="n">
-        <v>74786</v>
+        <v>79751</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7157,46 +7208,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1460</v>
+        <v>6456</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>528791</v>
+        <v>528686</v>
       </c>
       <c r="R57" t="n">
-        <v>6998633</v>
+        <v>6998471</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7225,7 +7271,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7235,12 +7281,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7255,22 +7301,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122817517</v>
+        <v>122818966</v>
       </c>
       <c r="B58" t="n">
-        <v>78411</v>
+        <v>79847</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7283,37 +7329,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>528643</v>
+        <v>528791</v>
       </c>
       <c r="R58" t="n">
-        <v>6998354</v>
+        <v>6998599</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7342,7 +7393,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7352,12 +7403,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På ved på gammal tallstubbe</t>
+          <t>På bark på stam av levande gammal sälg (25 cm dbh) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7368,6 +7419,21 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7384,10 +7450,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122817546</v>
+        <v>122817278</v>
       </c>
       <c r="B59" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7400,37 +7466,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>528628</v>
+        <v>528671</v>
       </c>
       <c r="R59" t="n">
-        <v>6998367</v>
+        <v>6998337</v>
       </c>
       <c r="S59" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7457,24 +7528,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7489,22 +7550,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122818613</v>
+        <v>122818122</v>
       </c>
       <c r="B60" t="n">
-        <v>98355</v>
+        <v>79848</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7513,55 +7574,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>528723</v>
+        <v>528631</v>
       </c>
       <c r="R60" t="n">
-        <v>6998554</v>
+        <v>6998473</v>
       </c>
       <c r="S60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7588,24 +7635,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7620,22 +7652,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122816979</v>
+        <v>122817758</v>
       </c>
       <c r="B61" t="n">
-        <v>78503</v>
+        <v>77699</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7648,21 +7680,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>228579</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7672,13 +7704,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>528730</v>
+        <v>528610</v>
       </c>
       <c r="R61" t="n">
-        <v>6998447</v>
+        <v>6998403</v>
       </c>
       <c r="S61" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7707,7 +7739,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7717,12 +7749,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På kolad ved</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7749,10 +7781,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122818323</v>
+        <v>122817413</v>
       </c>
       <c r="B62" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7765,37 +7797,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>528667</v>
+        <v>528612</v>
       </c>
       <c r="R62" t="n">
-        <v>6998534</v>
+        <v>6998323</v>
       </c>
       <c r="S62" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7822,24 +7859,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Rikligt på bark på stam av levande gammal sälg i gammal barrblandskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7854,19 +7881,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122818126</v>
+        <v>122818026</v>
       </c>
       <c r="B63" t="n">
         <v>79847</v>
@@ -7906,10 +7933,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>528624</v>
+        <v>528631</v>
       </c>
       <c r="R63" t="n">
-        <v>6998489</v>
+        <v>6998469</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7968,10 +7995,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122818681</v>
+        <v>122818321</v>
       </c>
       <c r="B64" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7984,37 +8011,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>528686</v>
+        <v>528805</v>
       </c>
       <c r="R64" t="n">
-        <v>6998618</v>
+        <v>6998631</v>
       </c>
       <c r="S64" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8041,11 +8068,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8054,48 +8096,23 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122817657</v>
+        <v>122817273</v>
       </c>
       <c r="B65" t="n">
         <v>78766</v>
@@ -8128,20 +8145,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>528650</v>
+        <v>528623</v>
       </c>
       <c r="R65" t="n">
-        <v>6998397</v>
+        <v>6998311</v>
       </c>
       <c r="S65" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8168,14 +8194,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8186,51 +8222,26 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122819024</v>
+        <v>122818654</v>
       </c>
       <c r="B66" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8243,37 +8254,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>528636</v>
+        <v>528711</v>
       </c>
       <c r="R66" t="n">
-        <v>6998609</v>
+        <v>6998632</v>
       </c>
       <c r="S66" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8305,6 +8321,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -8313,31 +8334,6 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Dead branch  # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8354,10 +8350,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122818653</v>
+        <v>122817517</v>
       </c>
       <c r="B67" t="n">
-        <v>79847</v>
+        <v>78411</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8370,21 +8366,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8394,13 +8390,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>528732</v>
+        <v>528643</v>
       </c>
       <c r="R67" t="n">
-        <v>6998541</v>
+        <v>6998354</v>
       </c>
       <c r="S67" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8429,7 +8425,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8439,12 +8435,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>På asplåga i gammal barrblandskog</t>
+          <t>På ved på gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8471,10 +8467,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122819033</v>
+        <v>122818681</v>
       </c>
       <c r="B68" t="n">
-        <v>74675</v>
+        <v>78766</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8483,41 +8479,41 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>528798</v>
+        <v>528686</v>
       </c>
       <c r="R68" t="n">
-        <v>6998603</v>
+        <v>6998618</v>
       </c>
       <c r="S68" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8544,26 +8540,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal sälg i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8572,26 +8553,51 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122818321</v>
+        <v>122818713</v>
       </c>
       <c r="B69" t="n">
-        <v>74863</v>
+        <v>90944</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8604,34 +8610,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>528805</v>
+        <v>528718</v>
       </c>
       <c r="R69" t="n">
-        <v>6998631</v>
+        <v>6998641</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8661,24 +8667,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8693,22 +8684,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122818654</v>
+        <v>122817186</v>
       </c>
       <c r="B70" t="n">
-        <v>57478</v>
+        <v>57428</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8717,20 +8708,20 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -8738,22 +8729,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>528711</v>
+        <v>528689</v>
       </c>
       <c r="R70" t="n">
-        <v>6998632</v>
+        <v>6998416</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8786,11 +8786,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8817,10 +8812,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122817289</v>
+        <v>122818323</v>
       </c>
       <c r="B71" t="n">
-        <v>79145</v>
+        <v>79847</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8833,21 +8828,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>257107</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blek lundlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bacidia rosellizans</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>S.Ekman</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8857,13 +8852,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>528632</v>
+        <v>528667</v>
       </c>
       <c r="R71" t="n">
-        <v>6998403</v>
+        <v>6998534</v>
       </c>
       <c r="S71" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8892,7 +8887,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8902,12 +8897,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>Rikligt på bark på stam av levande gammal sälg i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8934,10 +8929,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122818534</v>
+        <v>122818247</v>
       </c>
       <c r="B72" t="n">
-        <v>79813</v>
+        <v>78766</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8946,46 +8941,41 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>528727</v>
+        <v>528605</v>
       </c>
       <c r="R72" t="n">
-        <v>6998595</v>
+        <v>6998454</v>
       </c>
       <c r="S72" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9012,26 +9002,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På gammal asp</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -9040,16 +9015,41 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>

--- a/artfynd/A 55431-2024 artfynd.xlsx
+++ b/artfynd/A 55431-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122818955</v>
+        <v>122818759</v>
       </c>
       <c r="B3" t="n">
-        <v>74786</v>
+        <v>79847</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,39 +802,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1460</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528791</v>
+        <v>528778</v>
       </c>
       <c r="R3" t="n">
-        <v>6998633</v>
+        <v>6998602</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,12 +871,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,22 +891,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122818126</v>
+        <v>122818035</v>
       </c>
       <c r="B4" t="n">
-        <v>79847</v>
+        <v>79807</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,25 +915,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528624</v>
+        <v>528677</v>
       </c>
       <c r="R4" t="n">
-        <v>6998489</v>
+        <v>6998487</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,9 +976,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,22 +1008,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122818168</v>
+        <v>122817289</v>
       </c>
       <c r="B5" t="n">
-        <v>79807</v>
+        <v>79145</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,25 +1032,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229497</v>
+        <v>257107</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blek lundlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Bacidia rosellizans</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>S.Ekman</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1050,13 +1060,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528669</v>
+        <v>528632</v>
       </c>
       <c r="R5" t="n">
-        <v>6998500</v>
+        <v>6998403</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,12 +1105,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På bark på stam av död gammal asp (40 cm dbh) i gammal barrblandskog</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,21 +1121,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1142,7 +1137,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122818864</v>
+        <v>122818321</v>
       </c>
       <c r="B6" t="n">
         <v>74863</v>
@@ -1182,13 +1177,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528732</v>
+        <v>528805</v>
       </c>
       <c r="R6" t="n">
-        <v>6998659</v>
+        <v>6998631</v>
       </c>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1217,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1259,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122817657</v>
+        <v>122818613</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>98357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,38 +1266,52 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528650</v>
+        <v>528723</v>
       </c>
       <c r="R7" t="n">
-        <v>6998397</v>
+        <v>6998554</v>
       </c>
       <c r="S7" t="n">
         <v>9</v>
@@ -1332,14 +1341,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,48 +1369,23 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122817142</v>
+        <v>122818536</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1432,14 +1426,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528699</v>
+        <v>528665</v>
       </c>
       <c r="R8" t="n">
-        <v>6998430</v>
+        <v>6998574</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,7 +1470,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1503,10 +1497,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122819448</v>
+        <v>122818204</v>
       </c>
       <c r="B9" t="n">
-        <v>79876</v>
+        <v>79847</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1515,46 +1509,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528696</v>
+        <v>528649</v>
       </c>
       <c r="R9" t="n">
-        <v>6998688</v>
+        <v>6998490</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1581,14 +1570,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Frodiga bålar.</t>
+          <t>På innerbark på gammal björkhögstubbe i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1599,41 +1598,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122818573</v>
+        <v>122818966</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1646,37 +1630,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528630</v>
+        <v>528791</v>
       </c>
       <c r="R10" t="n">
-        <v>6998539</v>
+        <v>6998599</v>
       </c>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1703,11 +1692,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal sälg (25 cm dbh) i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1717,50 +1721,40 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122818025</v>
+        <v>122817758</v>
       </c>
       <c r="B11" t="n">
-        <v>79848</v>
+        <v>77699</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1773,21 +1767,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1797,10 +1791,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528631</v>
+        <v>528610</v>
       </c>
       <c r="R11" t="n">
-        <v>6998469</v>
+        <v>6998403</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1830,9 +1824,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1847,22 +1856,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122817325</v>
+        <v>122818955</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>74786</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1875,27 +1884,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1460</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1904,10 +1913,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528640</v>
+        <v>528791</v>
       </c>
       <c r="R12" t="n">
-        <v>6998336</v>
+        <v>6998633</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1937,14 +1946,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1959,22 +1978,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122817054</v>
+        <v>122817413</v>
       </c>
       <c r="B13" t="n">
-        <v>79751</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1983,38 +2002,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528755</v>
+        <v>528612</v>
       </c>
       <c r="R13" t="n">
-        <v>6998448</v>
+        <v>6998323</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2044,24 +2068,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>09:08</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>09:08</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2076,22 +2090,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122818328</v>
+        <v>122818387</v>
       </c>
       <c r="B14" t="n">
-        <v>77699</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2104,21 +2118,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2128,13 +2142,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528800</v>
+        <v>528619</v>
       </c>
       <c r="R14" t="n">
-        <v>6998633</v>
+        <v>6998495</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2161,26 +2175,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2189,26 +2188,51 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122818165</v>
+        <v>122818653</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2221,21 +2245,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2245,10 +2269,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528594</v>
+        <v>528732</v>
       </c>
       <c r="R15" t="n">
-        <v>6998419</v>
+        <v>6998541</v>
       </c>
       <c r="S15" t="n">
         <v>8</v>
@@ -2278,11 +2302,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På asplåga i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2291,48 +2330,23 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122817219</v>
+        <v>122817110</v>
       </c>
       <c r="B16" t="n">
         <v>78766</v>
@@ -2372,13 +2386,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528684</v>
+        <v>528711</v>
       </c>
       <c r="R16" t="n">
-        <v>6998437</v>
+        <v>6998430</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2405,14 +2419,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2423,51 +2447,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122817554</v>
+        <v>122818026</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2480,39 +2479,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528648</v>
+        <v>528631</v>
       </c>
       <c r="R17" t="n">
-        <v>6998359</v>
+        <v>6998469</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2545,11 +2539,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2576,10 +2565,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122817550</v>
+        <v>122818323</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2592,42 +2581,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528648</v>
+        <v>528667</v>
       </c>
       <c r="R18" t="n">
-        <v>6998358</v>
+        <v>6998534</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2654,14 +2638,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Rikligt på bark på stam av levande gammal sälg i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2676,22 +2670,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122818770</v>
+        <v>122817657</v>
       </c>
       <c r="B19" t="n">
-        <v>91235</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2704,37 +2698,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528718</v>
+        <v>528650</v>
       </c>
       <c r="R19" t="n">
-        <v>6998641</v>
+        <v>6998397</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2766,6 +2760,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2774,6 +2773,31 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2790,10 +2814,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122818204</v>
+        <v>122817339</v>
       </c>
       <c r="B20" t="n">
-        <v>79847</v>
+        <v>79384</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2806,21 +2830,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2833,10 +2857,10 @@
         <v>528649</v>
       </c>
       <c r="R20" t="n">
-        <v>6998490</v>
+        <v>6998383</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2865,7 +2889,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2875,12 +2899,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På innerbark på gammal björkhögstubbe i gammal barrblandskog</t>
+          <t>På gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2895,22 +2919,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122818503</v>
+        <v>122818125</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>78503</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2923,39 +2947,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528652</v>
+        <v>528687</v>
       </c>
       <c r="R21" t="n">
-        <v>6998555</v>
+        <v>6998489</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2985,14 +3004,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>På kolad ved på gammal tallstubbe i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3007,22 +3036,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122818174</v>
+        <v>122817601</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>90964</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3035,39 +3064,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528625</v>
+        <v>528645</v>
       </c>
       <c r="R22" t="n">
-        <v>6998500</v>
+        <v>6998384</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3100,11 +3124,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3131,10 +3150,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122817601</v>
+        <v>122817869</v>
       </c>
       <c r="B23" t="n">
-        <v>90964</v>
+        <v>57499</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3143,28 +3162,37 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5442</v>
+        <v>100110</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
@@ -3233,10 +3261,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122818675</v>
+        <v>122816979</v>
       </c>
       <c r="B24" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3249,46 +3277,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528722</v>
+        <v>528730</v>
       </c>
       <c r="R24" t="n">
-        <v>6998660</v>
+        <v>6998447</v>
       </c>
       <c r="S24" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3317,7 +3336,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3327,7 +3346,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På kolad ved</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3354,10 +3378,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122816988</v>
+        <v>122816987</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>79384</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3370,47 +3394,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528756</v>
+        <v>528755</v>
       </c>
       <c r="R25" t="n">
-        <v>6998450</v>
+        <v>6998446</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3437,14 +3451,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en tall.</t>
+          <t>På bränd jöttetallstubbe</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3455,51 +3479,26 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122818536</v>
+        <v>122817937</v>
       </c>
       <c r="B26" t="n">
-        <v>57478</v>
+        <v>90955</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3508,46 +3507,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528665</v>
+        <v>528686</v>
       </c>
       <c r="R26" t="n">
-        <v>6998574</v>
+        <v>6998446</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3574,14 +3568,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>På död asp</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3596,22 +3600,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122818035</v>
+        <v>122817645</v>
       </c>
       <c r="B27" t="n">
-        <v>79807</v>
+        <v>57499</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3624,37 +3628,46 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229497</v>
+        <v>100110</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528677</v>
+        <v>528643</v>
       </c>
       <c r="R27" t="n">
-        <v>6998487</v>
+        <v>6998354</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3683,7 +3696,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3693,12 +3706,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På gammal asp</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3713,22 +3721,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122818613</v>
+        <v>122817186</v>
       </c>
       <c r="B28" t="n">
-        <v>98355</v>
+        <v>57428</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3737,40 +3745,40 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>102621</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3779,13 +3787,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528723</v>
+        <v>528689</v>
       </c>
       <c r="R28" t="n">
-        <v>6998554</v>
+        <v>6998416</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3812,24 +3820,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3844,22 +3837,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122817714</v>
+        <v>122817144</v>
       </c>
       <c r="B29" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3872,37 +3865,46 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528625</v>
+        <v>528705</v>
       </c>
       <c r="R29" t="n">
-        <v>6998424</v>
+        <v>6998384</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3931,7 +3933,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3941,12 +3943,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:48</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3973,10 +3970,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122818032</v>
+        <v>122817546</v>
       </c>
       <c r="B30" t="n">
-        <v>79876</v>
+        <v>74863</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3985,25 +3982,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4013,13 +4010,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528631</v>
+        <v>528628</v>
       </c>
       <c r="R30" t="n">
-        <v>6998469</v>
+        <v>6998367</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4046,9 +4043,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4063,12 +4075,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4192,7 +4204,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122817144</v>
+        <v>122819024</v>
       </c>
       <c r="B32" t="n">
         <v>78766</v>
@@ -4225,29 +4237,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528705</v>
+        <v>528636</v>
       </c>
       <c r="R32" t="n">
-        <v>6998384</v>
+        <v>6998609</v>
       </c>
       <c r="S32" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4274,21 +4277,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4297,26 +4290,51 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Dead branch  # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122819379</v>
+        <v>122817142</v>
       </c>
       <c r="B33" t="n">
-        <v>98355</v>
+        <v>57478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4325,35 +4343,31 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4362,13 +4376,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528802</v>
+        <v>528699</v>
       </c>
       <c r="R33" t="n">
-        <v>6998594</v>
+        <v>6998430</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4395,24 +4409,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4427,22 +4431,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122819397</v>
+        <v>122816988</v>
       </c>
       <c r="B34" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4455,16 +4459,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4472,29 +4476,30 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528826</v>
+        <v>528756</v>
       </c>
       <c r="R34" t="n">
-        <v>6998595</v>
+        <v>6998450</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4526,6 +4531,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en tall.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4534,6 +4544,31 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4550,10 +4585,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122817869</v>
+        <v>122819118</v>
       </c>
       <c r="B35" t="n">
-        <v>57499</v>
+        <v>78766</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4562,50 +4597,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100110</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528645</v>
+        <v>528690</v>
       </c>
       <c r="R35" t="n">
-        <v>6998384</v>
+        <v>6998652</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4637,6 +4663,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4645,6 +4676,31 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4661,10 +4717,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122816979</v>
+        <v>122818328</v>
       </c>
       <c r="B36" t="n">
-        <v>78503</v>
+        <v>77699</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4677,21 +4733,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>228579</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4701,13 +4757,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528730</v>
+        <v>528800</v>
       </c>
       <c r="R36" t="n">
-        <v>6998447</v>
+        <v>6998633</v>
       </c>
       <c r="S36" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4736,7 +4792,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4746,12 +4802,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På kolad ved</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4778,10 +4834,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122818125</v>
+        <v>122818247</v>
       </c>
       <c r="B37" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4794,21 +4850,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4818,10 +4874,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528687</v>
+        <v>528605</v>
       </c>
       <c r="R37" t="n">
-        <v>6998489</v>
+        <v>6998454</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4851,26 +4907,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På kolad ved på gammal tallstubbe i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4879,26 +4920,51 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122817289</v>
+        <v>122818534</v>
       </c>
       <c r="B38" t="n">
-        <v>79145</v>
+        <v>79813</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4907,41 +4973,46 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>257107</v>
+        <v>229748</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blek lundlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bacidia rosellizans</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>S.Ekman</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528632</v>
+        <v>528727</v>
       </c>
       <c r="R38" t="n">
-        <v>6998403</v>
+        <v>6998595</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4970,7 +5041,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4980,12 +5051,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5000,22 +5071,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122817942</v>
+        <v>122818036</v>
       </c>
       <c r="B39" t="n">
-        <v>57478</v>
+        <v>79751</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5024,46 +5095,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528655</v>
+        <v>528686</v>
       </c>
       <c r="R39" t="n">
-        <v>6998433</v>
+        <v>6998471</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5090,14 +5156,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5112,22 +5188,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122817645</v>
+        <v>122817219</v>
       </c>
       <c r="B40" t="n">
-        <v>57499</v>
+        <v>78766</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5136,50 +5212,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100110</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528643</v>
+        <v>528684</v>
       </c>
       <c r="R40" t="n">
-        <v>6998354</v>
+        <v>6998437</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5206,19 +5273,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>09:45</t>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5229,26 +5291,51 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122818653</v>
+        <v>122817112</v>
       </c>
       <c r="B41" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5261,37 +5348,46 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528732</v>
+        <v>528711</v>
       </c>
       <c r="R41" t="n">
-        <v>6998541</v>
+        <v>6998411</v>
       </c>
       <c r="S41" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5320,7 +5416,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5330,12 +5426,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På asplåga i gammal barrblandskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5350,22 +5446,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122818514</v>
+        <v>122818025</v>
       </c>
       <c r="B42" t="n">
-        <v>74863</v>
+        <v>79848</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5378,34 +5474,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528635</v>
+        <v>528631</v>
       </c>
       <c r="R42" t="n">
-        <v>6998546</v>
+        <v>6998469</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5464,10 +5560,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122819058</v>
+        <v>122818122</v>
       </c>
       <c r="B43" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5480,37 +5576,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528654</v>
+        <v>528631</v>
       </c>
       <c r="R43" t="n">
-        <v>6998628</v>
+        <v>6998473</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5550,31 +5646,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5591,10 +5662,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122819024</v>
+        <v>122818713</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
+        <v>90944</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5607,21 +5678,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5631,13 +5702,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528636</v>
+        <v>528718</v>
       </c>
       <c r="R44" t="n">
-        <v>6998609</v>
+        <v>6998641</v>
       </c>
       <c r="S44" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5677,31 +5748,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Dead branch  # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5718,10 +5764,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122818759</v>
+        <v>122819397</v>
       </c>
       <c r="B45" t="n">
-        <v>79847</v>
+        <v>57494</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5734,34 +5780,43 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528778</v>
+        <v>528826</v>
       </c>
       <c r="R45" t="n">
-        <v>6998602</v>
+        <v>6998595</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5791,24 +5846,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5823,22 +5863,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122817110</v>
+        <v>122818654</v>
       </c>
       <c r="B46" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5851,37 +5891,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
         <v>528711</v>
       </c>
       <c r="R46" t="n">
-        <v>6998430</v>
+        <v>6998632</v>
       </c>
       <c r="S46" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5908,24 +5953,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>09:11</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>09:11</t>
-        </is>
-      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5940,19 +5975,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122817037</v>
+        <v>122818503</v>
       </c>
       <c r="B47" t="n">
         <v>57478</v>
@@ -5991,24 +6026,19 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528752</v>
+        <v>528652</v>
       </c>
       <c r="R47" t="n">
-        <v>6998456</v>
+        <v>6998555</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6042,7 +6072,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall.</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6053,31 +6083,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6094,10 +6099,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122817546</v>
+        <v>122818681</v>
       </c>
       <c r="B48" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6110,37 +6115,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528628</v>
+        <v>528686</v>
       </c>
       <c r="R48" t="n">
-        <v>6998367</v>
+        <v>6998618</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6167,26 +6172,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6195,23 +6185,48 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122818040</v>
+        <v>122817273</v>
       </c>
       <c r="B49" t="n">
         <v>78766</v>
@@ -6244,20 +6259,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528621</v>
+        <v>528623</v>
       </c>
       <c r="R49" t="n">
-        <v>6998383</v>
+        <v>6998311</v>
       </c>
       <c r="S49" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6284,11 +6308,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6297,51 +6336,26 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122819118</v>
+        <v>122818514</v>
       </c>
       <c r="B50" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6354,21 +6368,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6378,13 +6392,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528690</v>
+        <v>528635</v>
       </c>
       <c r="R50" t="n">
-        <v>6998652</v>
+        <v>6998546</v>
       </c>
       <c r="S50" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6416,11 +6430,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6429,31 +6438,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6470,10 +6454,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122817339</v>
+        <v>122818126</v>
       </c>
       <c r="B51" t="n">
-        <v>79384</v>
+        <v>79847</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6486,21 +6470,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6510,13 +6494,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528649</v>
+        <v>528624</v>
       </c>
       <c r="R51" t="n">
-        <v>6998383</v>
+        <v>6998489</v>
       </c>
       <c r="S51" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6543,24 +6527,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6575,22 +6544,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122816987</v>
+        <v>122819448</v>
       </c>
       <c r="B52" t="n">
-        <v>79384</v>
+        <v>79876</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6599,41 +6568,46 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>528755</v>
+        <v>528696</v>
       </c>
       <c r="R52" t="n">
-        <v>6998446</v>
+        <v>6998688</v>
       </c>
       <c r="S52" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6660,24 +6634,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>09:04</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>09:04</t>
-        </is>
-      </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På bränd jöttetallstubbe</t>
+          <t>Frodiga bålar.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6688,26 +6652,41 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Stone/rock on land</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122817112</v>
+        <v>122818770</v>
       </c>
       <c r="B53" t="n">
-        <v>78766</v>
+        <v>91235</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6720,46 +6699,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>528711</v>
+        <v>528718</v>
       </c>
       <c r="R53" t="n">
-        <v>6998411</v>
+        <v>6998641</v>
       </c>
       <c r="S53" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6786,24 +6756,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6818,22 +6773,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122818534</v>
+        <v>122819058</v>
       </c>
       <c r="B54" t="n">
-        <v>79813</v>
+        <v>78766</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6842,46 +6797,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>528727</v>
+        <v>528654</v>
       </c>
       <c r="R54" t="n">
-        <v>6998595</v>
+        <v>6998628</v>
       </c>
       <c r="S54" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6908,26 +6858,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>På gammal asp</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6936,23 +6871,48 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122818387</v>
+        <v>122818040</v>
       </c>
       <c r="B55" t="n">
         <v>78766</v>
@@ -6992,13 +6952,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>528619</v>
+        <v>528621</v>
       </c>
       <c r="R55" t="n">
-        <v>6998495</v>
+        <v>6998383</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7079,10 +7039,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122817937</v>
+        <v>122817278</v>
       </c>
       <c r="B56" t="n">
-        <v>90955</v>
+        <v>57478</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7091,41 +7051,46 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>528686</v>
+        <v>528671</v>
       </c>
       <c r="R56" t="n">
-        <v>6998446</v>
+        <v>6998337</v>
       </c>
       <c r="S56" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7152,24 +7117,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På död asp</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7184,22 +7139,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122818036</v>
+        <v>122817942</v>
       </c>
       <c r="B57" t="n">
-        <v>79751</v>
+        <v>57478</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7208,41 +7163,46 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>528686</v>
+        <v>528655</v>
       </c>
       <c r="R57" t="n">
-        <v>6998471</v>
+        <v>6998433</v>
       </c>
       <c r="S57" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7269,24 +7229,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7301,22 +7251,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122818966</v>
+        <v>122817325</v>
       </c>
       <c r="B58" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7329,27 +7279,27 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7358,13 +7308,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>528791</v>
+        <v>528640</v>
       </c>
       <c r="R58" t="n">
-        <v>6998599</v>
+        <v>6998336</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7391,24 +7341,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg (25 cm dbh) i gammal barrblandskog</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7419,38 +7359,23 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122817278</v>
+        <v>122817037</v>
       </c>
       <c r="B59" t="n">
         <v>57478</v>
@@ -7489,19 +7414,24 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>528671</v>
+        <v>528752</v>
       </c>
       <c r="R59" t="n">
-        <v>6998337</v>
+        <v>6998456</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7535,7 +7465,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7546,6 +7476,31 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7562,10 +7517,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122818122</v>
+        <v>122818174</v>
       </c>
       <c r="B60" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7578,34 +7533,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>528631</v>
+        <v>528625</v>
       </c>
       <c r="R60" t="n">
-        <v>6998473</v>
+        <v>6998500</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7638,6 +7598,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7664,10 +7629,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122817758</v>
+        <v>122817517</v>
       </c>
       <c r="B61" t="n">
-        <v>77699</v>
+        <v>78411</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7680,21 +7645,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228579</v>
+        <v>353</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7704,10 +7669,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>528610</v>
+        <v>528643</v>
       </c>
       <c r="R61" t="n">
-        <v>6998403</v>
+        <v>6998354</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7739,7 +7704,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7749,12 +7714,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På ved på gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7769,22 +7734,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122817413</v>
+        <v>122817714</v>
       </c>
       <c r="B62" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7797,42 +7762,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>528612</v>
+        <v>528625</v>
       </c>
       <c r="R62" t="n">
-        <v>6998323</v>
+        <v>6998424</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7859,14 +7819,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7881,22 +7851,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122818026</v>
+        <v>122818032</v>
       </c>
       <c r="B63" t="n">
-        <v>79847</v>
+        <v>79876</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7905,25 +7875,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7995,10 +7965,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122818321</v>
+        <v>122817554</v>
       </c>
       <c r="B64" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8011,34 +7981,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>528805</v>
+        <v>528648</v>
       </c>
       <c r="R64" t="n">
-        <v>6998631</v>
+        <v>6998359</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8068,24 +8043,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8100,22 +8065,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122817273</v>
+        <v>122817550</v>
       </c>
       <c r="B65" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8128,31 +8093,27 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -8161,13 +8122,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>528623</v>
+        <v>528648</v>
       </c>
       <c r="R65" t="n">
-        <v>6998311</v>
+        <v>6998358</v>
       </c>
       <c r="S65" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8194,24 +8155,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8226,22 +8177,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122818654</v>
+        <v>122819379</v>
       </c>
       <c r="B66" t="n">
-        <v>57478</v>
+        <v>98357</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8250,46 +8201,50 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>528711</v>
+        <v>528802</v>
       </c>
       <c r="R66" t="n">
-        <v>6998632</v>
+        <v>6998594</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8316,14 +8271,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8338,22 +8303,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122817517</v>
+        <v>122818168</v>
       </c>
       <c r="B67" t="n">
-        <v>78411</v>
+        <v>79807</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8362,25 +8327,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>229497</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8390,10 +8355,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>528643</v>
+        <v>528669</v>
       </c>
       <c r="R67" t="n">
-        <v>6998354</v>
+        <v>6998500</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8425,7 +8390,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8435,12 +8400,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>På ved på gammal tallstubbe</t>
+          <t>På bark på stam av död gammal asp (40 cm dbh) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8451,6 +8416,21 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -8467,7 +8447,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122818681</v>
+        <v>122818165</v>
       </c>
       <c r="B68" t="n">
         <v>78766</v>
@@ -8503,17 +8483,17 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>528686</v>
+        <v>528594</v>
       </c>
       <c r="R68" t="n">
-        <v>6998618</v>
+        <v>6998419</v>
       </c>
       <c r="S68" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8556,27 +8536,27 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8594,10 +8574,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122818713</v>
+        <v>122818675</v>
       </c>
       <c r="B69" t="n">
-        <v>90944</v>
+        <v>78766</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8610,37 +8590,46 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>528718</v>
+        <v>528722</v>
       </c>
       <c r="R69" t="n">
-        <v>6998641</v>
+        <v>6998660</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8667,9 +8656,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8684,22 +8683,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122817186</v>
+        <v>122818864</v>
       </c>
       <c r="B70" t="n">
-        <v>57428</v>
+        <v>74863</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8708,55 +8707,41 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>102621</v>
+        <v>6440</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>528689</v>
+        <v>528732</v>
       </c>
       <c r="R70" t="n">
-        <v>6998416</v>
+        <v>6998659</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8783,9 +8768,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8800,22 +8800,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122818323</v>
+        <v>122817054</v>
       </c>
       <c r="B71" t="n">
-        <v>79847</v>
+        <v>79751</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8824,25 +8824,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8852,13 +8852,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>528667</v>
+        <v>528755</v>
       </c>
       <c r="R71" t="n">
-        <v>6998534</v>
+        <v>6998448</v>
       </c>
       <c r="S71" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Rikligt på bark på stam av levande gammal sälg i gammal barrblandskog</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8929,7 +8929,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122818247</v>
+        <v>122818573</v>
       </c>
       <c r="B72" t="n">
         <v>78766</v>
@@ -8965,17 +8965,17 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>528605</v>
+        <v>528630</v>
       </c>
       <c r="R72" t="n">
-        <v>6998454</v>
+        <v>6998539</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
@@ -9192,7 +9192,7 @@
         <v>122818930</v>
       </c>
       <c r="B74" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>

--- a/artfynd/A 55431-2024 artfynd.xlsx
+++ b/artfynd/A 55431-2024 artfynd.xlsx
@@ -1254,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122818613</v>
+        <v>122818536</v>
       </c>
       <c r="B7" t="n">
-        <v>98357</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,55 +1266,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528723</v>
+        <v>528665</v>
       </c>
       <c r="R7" t="n">
-        <v>6998554</v>
+        <v>6998574</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1341,24 +1332,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1373,22 +1354,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122818536</v>
+        <v>122818613</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>98357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,46 +1378,55 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528665</v>
+        <v>528723</v>
       </c>
       <c r="R8" t="n">
-        <v>6998574</v>
+        <v>6998554</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1463,14 +1453,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1485,12 +1485,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -2565,10 +2565,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122818323</v>
+        <v>122818125</v>
       </c>
       <c r="B18" t="n">
-        <v>79847</v>
+        <v>78503</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2581,21 +2581,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2605,13 +2605,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528667</v>
+        <v>528687</v>
       </c>
       <c r="R18" t="n">
-        <v>6998534</v>
+        <v>6998489</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2650,12 +2650,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt på bark på stam av levande gammal sälg i gammal barrblandskog</t>
+          <t>På kolad ved på gammal tallstubbe i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2682,10 +2682,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122817657</v>
+        <v>122818323</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2698,21 +2698,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2722,13 +2722,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528650</v>
+        <v>528667</v>
       </c>
       <c r="R19" t="n">
-        <v>6998397</v>
+        <v>6998534</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2755,14 +2755,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Rikligt på bark på stam av levande gammal sälg i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2773,51 +2783,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122817339</v>
+        <v>122817657</v>
       </c>
       <c r="B20" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2830,21 +2815,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2854,13 +2839,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528649</v>
+        <v>528650</v>
       </c>
       <c r="R20" t="n">
-        <v>6998383</v>
+        <v>6998397</v>
       </c>
       <c r="S20" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2887,24 +2872,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gammal tallstubbe</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2915,26 +2890,51 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122818125</v>
+        <v>122817339</v>
       </c>
       <c r="B21" t="n">
-        <v>78503</v>
+        <v>79384</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2947,21 +2947,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2971,13 +2971,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528687</v>
+        <v>528649</v>
       </c>
       <c r="R21" t="n">
-        <v>6998489</v>
+        <v>6998383</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3016,12 +3016,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal tallstubbe i gammal barrblandskog</t>
+          <t>På gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3036,12 +3036,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -5083,10 +5083,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122818036</v>
+        <v>122818025</v>
       </c>
       <c r="B39" t="n">
-        <v>79751</v>
+        <v>79848</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5095,25 +5095,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5123,13 +5123,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528686</v>
+        <v>528631</v>
       </c>
       <c r="R39" t="n">
-        <v>6998471</v>
+        <v>6998469</v>
       </c>
       <c r="S39" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5156,24 +5156,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5188,22 +5173,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122817219</v>
+        <v>122818122</v>
       </c>
       <c r="B40" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5216,21 +5201,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5240,13 +5225,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528684</v>
+        <v>528631</v>
       </c>
       <c r="R40" t="n">
-        <v>6998437</v>
+        <v>6998473</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5278,11 +5263,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5291,31 +5271,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5332,10 +5287,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122817112</v>
+        <v>122818036</v>
       </c>
       <c r="B41" t="n">
-        <v>78766</v>
+        <v>79751</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5344,50 +5299,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528711</v>
+        <v>528686</v>
       </c>
       <c r="R41" t="n">
-        <v>6998411</v>
+        <v>6998471</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5416,7 +5362,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5426,12 +5372,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5446,22 +5392,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122818025</v>
+        <v>122817219</v>
       </c>
       <c r="B42" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5474,21 +5420,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5498,13 +5444,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528631</v>
+        <v>528684</v>
       </c>
       <c r="R42" t="n">
-        <v>6998469</v>
+        <v>6998437</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5536,6 +5482,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5544,6 +5495,31 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5560,10 +5536,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122818122</v>
+        <v>122817112</v>
       </c>
       <c r="B43" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5576,37 +5552,46 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528631</v>
+        <v>528711</v>
       </c>
       <c r="R43" t="n">
-        <v>6998473</v>
+        <v>6998411</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5633,9 +5618,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5650,22 +5650,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122818713</v>
+        <v>122818654</v>
       </c>
       <c r="B44" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5678,34 +5678,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528718</v>
+        <v>528711</v>
       </c>
       <c r="R44" t="n">
-        <v>6998641</v>
+        <v>6998632</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5738,6 +5743,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5764,10 +5774,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122819397</v>
+        <v>122818713</v>
       </c>
       <c r="B45" t="n">
-        <v>57494</v>
+        <v>90944</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5780,43 +5790,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528826</v>
+        <v>528718</v>
       </c>
       <c r="R45" t="n">
-        <v>6998595</v>
+        <v>6998641</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5875,10 +5876,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122818654</v>
+        <v>122819397</v>
       </c>
       <c r="B46" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5891,16 +5892,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5908,10 +5909,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5920,10 +5925,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528711</v>
+        <v>528826</v>
       </c>
       <c r="R46" t="n">
-        <v>6998632</v>
+        <v>6998595</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5956,11 +5961,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5987,10 +5987,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122818503</v>
+        <v>122818681</v>
       </c>
       <c r="B47" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6003,42 +6003,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528652</v>
+        <v>528686</v>
       </c>
       <c r="R47" t="n">
-        <v>6998555</v>
+        <v>6998618</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6070,11 +6065,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6083,6 +6073,31 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6099,7 +6114,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122818681</v>
+        <v>122817273</v>
       </c>
       <c r="B48" t="n">
         <v>78766</v>
@@ -6132,20 +6147,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528686</v>
+        <v>528623</v>
       </c>
       <c r="R48" t="n">
-        <v>6998618</v>
+        <v>6998311</v>
       </c>
       <c r="S48" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6172,11 +6196,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6185,51 +6224,26 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122817273</v>
+        <v>122818514</v>
       </c>
       <c r="B49" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6242,46 +6256,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528623</v>
+        <v>528635</v>
       </c>
       <c r="R49" t="n">
-        <v>6998311</v>
+        <v>6998546</v>
       </c>
       <c r="S49" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6308,24 +6313,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6340,22 +6330,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122818514</v>
+        <v>122818126</v>
       </c>
       <c r="B50" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6368,34 +6358,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528635</v>
+        <v>528624</v>
       </c>
       <c r="R50" t="n">
-        <v>6998546</v>
+        <v>6998489</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6454,10 +6444,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122818126</v>
+        <v>122819448</v>
       </c>
       <c r="B51" t="n">
-        <v>79847</v>
+        <v>79876</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6466,38 +6456,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528624</v>
+        <v>528696</v>
       </c>
       <c r="R51" t="n">
-        <v>6998489</v>
+        <v>6998688</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6532,6 +6527,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Frodiga bålar.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6540,6 +6540,21 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Stone/rock on land</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6556,10 +6571,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122819448</v>
+        <v>122818503</v>
       </c>
       <c r="B52" t="n">
-        <v>79876</v>
+        <v>57478</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6568,31 +6583,31 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6601,10 +6616,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>528696</v>
+        <v>528652</v>
       </c>
       <c r="R52" t="n">
-        <v>6998688</v>
+        <v>6998555</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6641,7 +6656,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Frodiga bålar.</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6652,21 +6667,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">

--- a/artfynd/A 55431-2024 artfynd.xlsx
+++ b/artfynd/A 55431-2024 artfynd.xlsx
@@ -1254,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122818536</v>
+        <v>122818613</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>98357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,46 +1266,55 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528665</v>
+        <v>528723</v>
       </c>
       <c r="R7" t="n">
-        <v>6998574</v>
+        <v>6998554</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1332,14 +1341,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,22 +1373,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122818613</v>
+        <v>122818536</v>
       </c>
       <c r="B8" t="n">
-        <v>98357</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,55 +1397,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528723</v>
+        <v>528665</v>
       </c>
       <c r="R8" t="n">
-        <v>6998554</v>
+        <v>6998574</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1453,24 +1463,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1485,12 +1485,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -2565,10 +2565,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122818125</v>
+        <v>122818323</v>
       </c>
       <c r="B18" t="n">
-        <v>78503</v>
+        <v>79847</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2581,21 +2581,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2605,13 +2605,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528687</v>
+        <v>528667</v>
       </c>
       <c r="R18" t="n">
-        <v>6998489</v>
+        <v>6998534</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2650,12 +2650,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal tallstubbe i gammal barrblandskog</t>
+          <t>Rikligt på bark på stam av levande gammal sälg i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2682,10 +2682,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122818323</v>
+        <v>122817657</v>
       </c>
       <c r="B19" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2698,21 +2698,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2722,13 +2722,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528667</v>
+        <v>528650</v>
       </c>
       <c r="R19" t="n">
-        <v>6998534</v>
+        <v>6998397</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2755,24 +2755,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rikligt på bark på stam av levande gammal sälg i gammal barrblandskog</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2783,26 +2773,51 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122817657</v>
+        <v>122817339</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2815,21 +2830,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2839,13 +2854,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528650</v>
+        <v>528649</v>
       </c>
       <c r="R20" t="n">
-        <v>6998397</v>
+        <v>6998383</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2872,14 +2887,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2890,51 +2915,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122817339</v>
+        <v>122818125</v>
       </c>
       <c r="B21" t="n">
-        <v>79384</v>
+        <v>78503</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2947,21 +2947,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2971,13 +2971,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528649</v>
+        <v>528687</v>
       </c>
       <c r="R21" t="n">
-        <v>6998383</v>
+        <v>6998489</v>
       </c>
       <c r="S21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3016,12 +3016,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gammal tallstubbe</t>
+          <t>På kolad ved på gammal tallstubbe i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3036,22 +3036,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122817601</v>
+        <v>122816979</v>
       </c>
       <c r="B22" t="n">
-        <v>90964</v>
+        <v>78503</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3064,21 +3064,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3088,13 +3088,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528645</v>
+        <v>528730</v>
       </c>
       <c r="R22" t="n">
-        <v>6998384</v>
+        <v>6998447</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3121,9 +3121,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På kolad ved</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3138,22 +3153,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122817869</v>
+        <v>122816987</v>
       </c>
       <c r="B23" t="n">
-        <v>57499</v>
+        <v>79384</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3162,50 +3177,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100110</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528645</v>
+        <v>528755</v>
       </c>
       <c r="R23" t="n">
-        <v>6998384</v>
+        <v>6998446</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3232,9 +3238,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På bränd jöttetallstubbe</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3249,22 +3270,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122816979</v>
+        <v>122817869</v>
       </c>
       <c r="B24" t="n">
-        <v>78503</v>
+        <v>57499</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3273,41 +3294,50 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>100110</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528730</v>
+        <v>528645</v>
       </c>
       <c r="R24" t="n">
-        <v>6998447</v>
+        <v>6998384</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3334,24 +3364,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>09:03</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>09:03</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På kolad ved</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3366,22 +3381,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122816987</v>
+        <v>122817601</v>
       </c>
       <c r="B25" t="n">
-        <v>79384</v>
+        <v>90964</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3394,21 +3409,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3418,13 +3433,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528755</v>
+        <v>528645</v>
       </c>
       <c r="R25" t="n">
-        <v>6998446</v>
+        <v>6998384</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3451,24 +3466,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>09:04</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>09:04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På bränd jöttetallstubbe</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3483,12 +3483,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -5987,10 +5987,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122818681</v>
+        <v>122818503</v>
       </c>
       <c r="B47" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6003,37 +6003,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528686</v>
+        <v>528652</v>
       </c>
       <c r="R47" t="n">
-        <v>6998618</v>
+        <v>6998555</v>
       </c>
       <c r="S47" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6065,6 +6070,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6073,31 +6083,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6114,7 +6099,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122817273</v>
+        <v>122818681</v>
       </c>
       <c r="B48" t="n">
         <v>78766</v>
@@ -6147,29 +6132,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528623</v>
+        <v>528686</v>
       </c>
       <c r="R48" t="n">
-        <v>6998311</v>
+        <v>6998618</v>
       </c>
       <c r="S48" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6196,26 +6172,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6224,26 +6185,51 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122818514</v>
+        <v>122817273</v>
       </c>
       <c r="B49" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6256,37 +6242,46 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528635</v>
+        <v>528623</v>
       </c>
       <c r="R49" t="n">
-        <v>6998546</v>
+        <v>6998311</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6313,9 +6308,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6330,22 +6340,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122818126</v>
+        <v>122818514</v>
       </c>
       <c r="B50" t="n">
-        <v>79847</v>
+        <v>74863</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6358,34 +6368,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528624</v>
+        <v>528635</v>
       </c>
       <c r="R50" t="n">
-        <v>6998489</v>
+        <v>6998546</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6444,10 +6454,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122819448</v>
+        <v>122818126</v>
       </c>
       <c r="B51" t="n">
-        <v>79876</v>
+        <v>79847</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6456,43 +6466,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528696</v>
+        <v>528624</v>
       </c>
       <c r="R51" t="n">
-        <v>6998688</v>
+        <v>6998489</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6527,11 +6532,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Frodiga bålar.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6540,21 +6540,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6571,10 +6556,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122818503</v>
+        <v>122819448</v>
       </c>
       <c r="B52" t="n">
-        <v>57478</v>
+        <v>79876</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6583,31 +6568,31 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6616,10 +6601,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>528652</v>
+        <v>528696</v>
       </c>
       <c r="R52" t="n">
-        <v>6998555</v>
+        <v>6998688</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6656,7 +6641,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>Frodiga bålar.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6667,6 +6652,21 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Stone/rock on land</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6683,10 +6683,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122818770</v>
+        <v>122819058</v>
       </c>
       <c r="B53" t="n">
-        <v>91235</v>
+        <v>78766</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6699,21 +6699,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6723,13 +6723,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>528718</v>
+        <v>528654</v>
       </c>
       <c r="R53" t="n">
-        <v>6998641</v>
+        <v>6998628</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6769,6 +6769,31 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6785,7 +6810,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122819058</v>
+        <v>122818040</v>
       </c>
       <c r="B54" t="n">
         <v>78766</v>
@@ -6821,17 +6846,17 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>528654</v>
+        <v>528621</v>
       </c>
       <c r="R54" t="n">
-        <v>6998628</v>
+        <v>6998383</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6874,27 +6899,27 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6912,10 +6937,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122818040</v>
+        <v>122818770</v>
       </c>
       <c r="B55" t="n">
-        <v>78766</v>
+        <v>91235</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6928,37 +6953,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>528621</v>
+        <v>528718</v>
       </c>
       <c r="R55" t="n">
-        <v>6998383</v>
+        <v>6998641</v>
       </c>
       <c r="S55" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6998,31 +7023,6 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -8315,10 +8315,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122818168</v>
+        <v>122818165</v>
       </c>
       <c r="B67" t="n">
-        <v>79807</v>
+        <v>78766</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8327,25 +8327,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8355,13 +8355,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>528669</v>
+        <v>528594</v>
       </c>
       <c r="R67" t="n">
-        <v>6998500</v>
+        <v>6998419</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8388,26 +8388,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På bark på stam av död gammal asp (40 cm dbh) i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8417,37 +8402,47 @@
       <c r="AG67" t="b">
         <v>0</v>
       </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122818165</v>
+        <v>122818675</v>
       </c>
       <c r="B68" t="n">
         <v>78766</v>
@@ -8480,20 +8475,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>528594</v>
+        <v>528722</v>
       </c>
       <c r="R68" t="n">
-        <v>6998419</v>
+        <v>6998660</v>
       </c>
       <c r="S68" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8520,11 +8524,21 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8533,51 +8547,26 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122818675</v>
+        <v>122818168</v>
       </c>
       <c r="B69" t="n">
-        <v>78766</v>
+        <v>79807</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8586,50 +8575,41 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>528722</v>
+        <v>528669</v>
       </c>
       <c r="R69" t="n">
-        <v>6998660</v>
+        <v>6998500</v>
       </c>
       <c r="S69" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8658,7 +8638,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8668,7 +8648,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På bark på stam av död gammal asp (40 cm dbh) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8679,16 +8664,31 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>

--- a/artfynd/A 55431-2024 artfynd.xlsx
+++ b/artfynd/A 55431-2024 artfynd.xlsx
@@ -1254,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122818613</v>
+        <v>122818536</v>
       </c>
       <c r="B7" t="n">
-        <v>98357</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,55 +1266,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528723</v>
+        <v>528665</v>
       </c>
       <c r="R7" t="n">
-        <v>6998554</v>
+        <v>6998574</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1341,24 +1332,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1373,22 +1354,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122818536</v>
+        <v>122818613</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>98357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,46 +1378,55 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528665</v>
+        <v>528723</v>
       </c>
       <c r="R8" t="n">
-        <v>6998574</v>
+        <v>6998554</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1463,14 +1453,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1485,12 +1485,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -2565,10 +2565,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122818323</v>
+        <v>122818125</v>
       </c>
       <c r="B18" t="n">
-        <v>79847</v>
+        <v>78503</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2581,21 +2581,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2605,13 +2605,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528667</v>
+        <v>528687</v>
       </c>
       <c r="R18" t="n">
-        <v>6998534</v>
+        <v>6998489</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2650,12 +2650,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt på bark på stam av levande gammal sälg i gammal barrblandskog</t>
+          <t>På kolad ved på gammal tallstubbe i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2682,10 +2682,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122817657</v>
+        <v>122818323</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2698,21 +2698,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2722,13 +2722,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528650</v>
+        <v>528667</v>
       </c>
       <c r="R19" t="n">
-        <v>6998397</v>
+        <v>6998534</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2755,14 +2755,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Rikligt på bark på stam av levande gammal sälg i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2773,51 +2783,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122817339</v>
+        <v>122817657</v>
       </c>
       <c r="B20" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2830,21 +2815,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2854,13 +2839,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528649</v>
+        <v>528650</v>
       </c>
       <c r="R20" t="n">
-        <v>6998383</v>
+        <v>6998397</v>
       </c>
       <c r="S20" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2887,24 +2872,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gammal tallstubbe</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2915,26 +2890,51 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122818125</v>
+        <v>122817339</v>
       </c>
       <c r="B21" t="n">
-        <v>78503</v>
+        <v>79384</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2947,21 +2947,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2971,13 +2971,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528687</v>
+        <v>528649</v>
       </c>
       <c r="R21" t="n">
-        <v>6998489</v>
+        <v>6998383</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3016,12 +3016,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal tallstubbe i gammal barrblandskog</t>
+          <t>På gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3036,22 +3036,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122816979</v>
+        <v>122817601</v>
       </c>
       <c r="B22" t="n">
-        <v>78503</v>
+        <v>90964</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3064,21 +3064,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3088,13 +3088,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528730</v>
+        <v>528645</v>
       </c>
       <c r="R22" t="n">
-        <v>6998447</v>
+        <v>6998384</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3121,24 +3121,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>09:03</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>09:03</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På kolad ved</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3153,22 +3138,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122816987</v>
+        <v>122817869</v>
       </c>
       <c r="B23" t="n">
-        <v>79384</v>
+        <v>57499</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3177,41 +3162,50 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>100110</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528755</v>
+        <v>528645</v>
       </c>
       <c r="R23" t="n">
-        <v>6998446</v>
+        <v>6998384</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3238,24 +3232,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>09:04</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>09:04</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På bränd jöttetallstubbe</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3270,22 +3249,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122817869</v>
+        <v>122816979</v>
       </c>
       <c r="B24" t="n">
-        <v>57499</v>
+        <v>78503</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3294,50 +3273,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100110</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528645</v>
+        <v>528730</v>
       </c>
       <c r="R24" t="n">
-        <v>6998384</v>
+        <v>6998447</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3364,9 +3334,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På kolad ved</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3381,22 +3366,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122817601</v>
+        <v>122816987</v>
       </c>
       <c r="B25" t="n">
-        <v>90964</v>
+        <v>79384</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3409,21 +3394,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3433,13 +3418,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528645</v>
+        <v>528755</v>
       </c>
       <c r="R25" t="n">
-        <v>6998384</v>
+        <v>6998446</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3466,9 +3451,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På bränd jöttetallstubbe</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3483,12 +3483,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -6683,10 +6683,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122819058</v>
+        <v>122818770</v>
       </c>
       <c r="B53" t="n">
-        <v>78766</v>
+        <v>91235</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6699,21 +6699,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6723,13 +6723,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>528654</v>
+        <v>528718</v>
       </c>
       <c r="R53" t="n">
-        <v>6998628</v>
+        <v>6998641</v>
       </c>
       <c r="S53" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6769,31 +6769,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6810,7 +6785,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122818040</v>
+        <v>122819058</v>
       </c>
       <c r="B54" t="n">
         <v>78766</v>
@@ -6846,17 +6821,17 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>528621</v>
+        <v>528654</v>
       </c>
       <c r="R54" t="n">
-        <v>6998383</v>
+        <v>6998628</v>
       </c>
       <c r="S54" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6899,27 +6874,27 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6937,10 +6912,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122818770</v>
+        <v>122818040</v>
       </c>
       <c r="B55" t="n">
-        <v>91235</v>
+        <v>78766</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6953,37 +6928,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>528718</v>
+        <v>528621</v>
       </c>
       <c r="R55" t="n">
-        <v>6998641</v>
+        <v>6998383</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7023,6 +6998,31 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">

--- a/artfynd/A 55431-2024 artfynd.xlsx
+++ b/artfynd/A 55431-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122818759</v>
+        <v>122818122</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528778</v>
+        <v>528631</v>
       </c>
       <c r="R3" t="n">
-        <v>6998602</v>
+        <v>6998473</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -859,24 +859,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,22 +876,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122818035</v>
+        <v>122818174</v>
       </c>
       <c r="B4" t="n">
-        <v>79807</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,38 +900,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528677</v>
+        <v>528625</v>
       </c>
       <c r="R4" t="n">
-        <v>6998487</v>
+        <v>6998500</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,24 +966,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,22 +988,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122817289</v>
+        <v>122817339</v>
       </c>
       <c r="B5" t="n">
-        <v>79145</v>
+        <v>79384</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>257107</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blek lundlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bacidia rosellizans</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>S.Ekman</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,13 +1040,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528632</v>
+        <v>528649</v>
       </c>
       <c r="R5" t="n">
-        <v>6998403</v>
+        <v>6998383</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,7 +1075,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,12 +1085,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>På gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,22 +1105,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122818321</v>
+        <v>122819024</v>
       </c>
       <c r="B6" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,37 +1133,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528805</v>
+        <v>528636</v>
       </c>
       <c r="R6" t="n">
-        <v>6998631</v>
+        <v>6998609</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1210,26 +1190,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1238,26 +1203,51 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Dead branch  # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122818536</v>
+        <v>122819118</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,42 +1260,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528665</v>
+        <v>528690</v>
       </c>
       <c r="R7" t="n">
-        <v>6998574</v>
+        <v>6998652</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1339,7 +1324,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,6 +1335,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1366,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122818613</v>
+        <v>122818035</v>
       </c>
       <c r="B8" t="n">
-        <v>98357</v>
+        <v>79807</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,55 +1388,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528723</v>
+        <v>528677</v>
       </c>
       <c r="R8" t="n">
-        <v>6998554</v>
+        <v>6998487</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1455,7 +1451,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1465,12 +1461,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1485,22 +1481,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122818204</v>
+        <v>122817657</v>
       </c>
       <c r="B9" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1513,21 +1509,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1537,13 +1533,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528649</v>
+        <v>528650</v>
       </c>
       <c r="R9" t="n">
-        <v>6998490</v>
+        <v>6998397</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1570,24 +1566,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:09</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:09</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På innerbark på gammal björkhögstubbe i gammal barrblandskog</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,26 +1584,51 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122818966</v>
+        <v>122819033</v>
       </c>
       <c r="B10" t="n">
-        <v>79847</v>
+        <v>74675</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1626,46 +1637,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6428</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528791</v>
+        <v>528798</v>
       </c>
       <c r="R10" t="n">
-        <v>6998599</v>
+        <v>6998603</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1694,7 +1700,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1704,12 +1710,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg (25 cm dbh) i gammal barrblandskog</t>
+          <t>På bark på stam av levande gammal sälg i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1720,21 +1726,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1751,10 +1742,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122817758</v>
+        <v>122818040</v>
       </c>
       <c r="B11" t="n">
-        <v>77699</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1767,21 +1758,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1791,13 +1782,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528610</v>
+        <v>528621</v>
       </c>
       <c r="R11" t="n">
-        <v>6998403</v>
+        <v>6998383</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1824,26 +1815,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1852,26 +1828,51 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122818955</v>
+        <v>122818536</v>
       </c>
       <c r="B12" t="n">
-        <v>74786</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1884,39 +1885,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1460</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528791</v>
+        <v>528665</v>
       </c>
       <c r="R12" t="n">
-        <v>6998633</v>
+        <v>6998574</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1946,24 +1947,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1978,22 +1969,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122817413</v>
+        <v>122817186</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>57428</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2002,20 +1993,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2023,10 +2014,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2035,10 +2035,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528612</v>
+        <v>528689</v>
       </c>
       <c r="R13" t="n">
-        <v>6998323</v>
+        <v>6998416</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2071,11 +2071,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2102,10 +2097,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122818387</v>
+        <v>122818514</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2118,34 +2113,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528619</v>
+        <v>528635</v>
       </c>
       <c r="R14" t="n">
-        <v>6998495</v>
+        <v>6998546</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2188,31 +2183,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2229,7 +2199,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122818653</v>
+        <v>122818026</v>
       </c>
       <c r="B15" t="n">
         <v>79847</v>
@@ -2269,13 +2239,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528732</v>
+        <v>528631</v>
       </c>
       <c r="R15" t="n">
-        <v>6998541</v>
+        <v>6998469</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2302,24 +2272,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På asplåga i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2334,22 +2289,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122817110</v>
+        <v>122818966</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2362,37 +2317,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528711</v>
+        <v>528791</v>
       </c>
       <c r="R16" t="n">
-        <v>6998430</v>
+        <v>6998599</v>
       </c>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2421,7 +2381,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2431,12 +2391,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På bark på stam av levande gammal sälg (25 cm dbh) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2447,6 +2407,21 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2463,10 +2438,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122818026</v>
+        <v>122817942</v>
       </c>
       <c r="B17" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2479,34 +2454,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528631</v>
+        <v>528655</v>
       </c>
       <c r="R17" t="n">
-        <v>6998469</v>
+        <v>6998433</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2539,6 +2519,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2565,10 +2550,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122818125</v>
+        <v>122817937</v>
       </c>
       <c r="B18" t="n">
-        <v>78503</v>
+        <v>90955</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2577,25 +2562,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>1205</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2605,13 +2590,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528687</v>
+        <v>528686</v>
       </c>
       <c r="R18" t="n">
-        <v>6998489</v>
+        <v>6998446</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2640,7 +2625,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2650,12 +2635,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal tallstubbe i gammal barrblandskog</t>
+          <t>På död asp</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2670,22 +2655,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122818323</v>
+        <v>122817144</v>
       </c>
       <c r="B19" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2698,37 +2683,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528667</v>
+        <v>528705</v>
       </c>
       <c r="R19" t="n">
-        <v>6998534</v>
+        <v>6998384</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2757,7 +2751,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2767,12 +2761,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:13</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt på bark på stam av levande gammal sälg i gammal barrblandskog</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2787,19 +2776,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122817657</v>
+        <v>122817112</v>
       </c>
       <c r="B20" t="n">
         <v>78766</v>
@@ -2832,17 +2821,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528650</v>
+        <v>528711</v>
       </c>
       <c r="R20" t="n">
-        <v>6998397</v>
+        <v>6998411</v>
       </c>
       <c r="S20" t="n">
         <v>9</v>
@@ -2872,14 +2870,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2890,51 +2898,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122817339</v>
+        <v>122817413</v>
       </c>
       <c r="B21" t="n">
-        <v>79384</v>
+        <v>57478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2947,37 +2930,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528649</v>
+        <v>528612</v>
       </c>
       <c r="R21" t="n">
-        <v>6998383</v>
+        <v>6998323</v>
       </c>
       <c r="S21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3004,24 +2992,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gammal tallstubbe</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3036,22 +3014,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122817601</v>
+        <v>122816988</v>
       </c>
       <c r="B22" t="n">
-        <v>90964</v>
+        <v>57478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3064,37 +3042,47 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528645</v>
+        <v>528756</v>
       </c>
       <c r="R22" t="n">
-        <v>6998384</v>
+        <v>6998450</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3126,6 +3114,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en tall.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3134,6 +3127,31 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3150,10 +3168,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122817869</v>
+        <v>122818125</v>
       </c>
       <c r="B23" t="n">
-        <v>57499</v>
+        <v>78503</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3162,47 +3180,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100110</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528645</v>
+        <v>528687</v>
       </c>
       <c r="R23" t="n">
-        <v>6998384</v>
+        <v>6998489</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3232,9 +3241,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal tallstubbe i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3249,22 +3273,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122816979</v>
+        <v>122817289</v>
       </c>
       <c r="B24" t="n">
-        <v>78503</v>
+        <v>79145</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3277,21 +3301,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>257107</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blek lundlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bacidia rosellizans</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>S.Ekman</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3301,10 +3325,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528730</v>
+        <v>528632</v>
       </c>
       <c r="R24" t="n">
-        <v>6998447</v>
+        <v>6998403</v>
       </c>
       <c r="S24" t="n">
         <v>8</v>
@@ -3336,7 +3360,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3346,12 +3370,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På kolad ved</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3366,22 +3390,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122816987</v>
+        <v>122818387</v>
       </c>
       <c r="B25" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3394,21 +3418,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3418,13 +3442,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528755</v>
+        <v>528619</v>
       </c>
       <c r="R25" t="n">
-        <v>6998446</v>
+        <v>6998495</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3451,26 +3475,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>09:04</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>09:04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På bränd jöttetallstubbe</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3479,26 +3488,51 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122817937</v>
+        <v>122818713</v>
       </c>
       <c r="B26" t="n">
-        <v>90955</v>
+        <v>90944</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3507,41 +3541,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528686</v>
+        <v>528718</v>
       </c>
       <c r="R26" t="n">
-        <v>6998446</v>
+        <v>6998641</v>
       </c>
       <c r="S26" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3568,24 +3602,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På död asp</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3600,22 +3619,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122817645</v>
+        <v>122818864</v>
       </c>
       <c r="B27" t="n">
-        <v>57499</v>
+        <v>74863</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3624,50 +3643,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100110</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528643</v>
+        <v>528732</v>
       </c>
       <c r="R27" t="n">
-        <v>6998354</v>
+        <v>6998659</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3696,7 +3706,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3706,7 +3716,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3721,22 +3736,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122817186</v>
+        <v>122818653</v>
       </c>
       <c r="B28" t="n">
-        <v>57428</v>
+        <v>79847</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3745,55 +3760,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102621</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528689</v>
+        <v>528732</v>
       </c>
       <c r="R28" t="n">
-        <v>6998416</v>
+        <v>6998541</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3820,9 +3821,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På asplåga i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3837,19 +3853,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122817144</v>
+        <v>122819058</v>
       </c>
       <c r="B29" t="n">
         <v>78766</v>
@@ -3882,29 +3898,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528705</v>
+        <v>528654</v>
       </c>
       <c r="R29" t="n">
-        <v>6998384</v>
+        <v>6998628</v>
       </c>
       <c r="S29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3931,21 +3938,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3954,26 +3951,51 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122817546</v>
+        <v>122817550</v>
       </c>
       <c r="B30" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3986,37 +4008,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528628</v>
+        <v>528648</v>
       </c>
       <c r="R30" t="n">
-        <v>6998367</v>
+        <v>6998358</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4043,24 +4070,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4075,22 +4092,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122819033</v>
+        <v>122817758</v>
       </c>
       <c r="B31" t="n">
-        <v>74675</v>
+        <v>77699</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4099,25 +4116,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6428</v>
+        <v>228579</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4127,13 +4144,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528798</v>
+        <v>528610</v>
       </c>
       <c r="R31" t="n">
-        <v>6998603</v>
+        <v>6998403</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4162,7 +4179,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4172,12 +4189,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal barrblandskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4192,22 +4209,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122819024</v>
+        <v>122818534</v>
       </c>
       <c r="B32" t="n">
-        <v>78766</v>
+        <v>79813</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4216,41 +4233,46 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528636</v>
+        <v>528727</v>
       </c>
       <c r="R32" t="n">
-        <v>6998609</v>
+        <v>6998595</v>
       </c>
       <c r="S32" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4277,11 +4299,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På gammal asp</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4290,51 +4327,26 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Dead branch  # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122817142</v>
+        <v>122817714</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4347,42 +4359,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528699</v>
+        <v>528625</v>
       </c>
       <c r="R33" t="n">
-        <v>6998430</v>
+        <v>6998424</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4409,14 +4416,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4431,22 +4448,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122816988</v>
+        <v>122818573</v>
       </c>
       <c r="B34" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4459,47 +4476,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528756</v>
+        <v>528630</v>
       </c>
       <c r="R34" t="n">
-        <v>6998450</v>
+        <v>6998539</v>
       </c>
       <c r="S34" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4531,11 +4538,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på en tall.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4552,22 +4554,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4585,10 +4587,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122819118</v>
+        <v>122818759</v>
       </c>
       <c r="B35" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4601,37 +4603,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528690</v>
+        <v>528778</v>
       </c>
       <c r="R35" t="n">
-        <v>6998652</v>
+        <v>6998602</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4658,14 +4660,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4676,51 +4688,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122818328</v>
+        <v>122817054</v>
       </c>
       <c r="B36" t="n">
-        <v>77699</v>
+        <v>79751</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4729,25 +4716,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228579</v>
+        <v>6456</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4757,13 +4744,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528800</v>
+        <v>528755</v>
       </c>
       <c r="R36" t="n">
-        <v>6998633</v>
+        <v>6998448</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4792,7 +4779,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4802,12 +4789,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4822,22 +4809,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122818247</v>
+        <v>122817325</v>
       </c>
       <c r="B37" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4850,34 +4837,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528605</v>
+        <v>528640</v>
       </c>
       <c r="R37" t="n">
-        <v>6998454</v>
+        <v>6998336</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4912,6 +4904,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4920,31 +4917,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4961,10 +4933,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122818534</v>
+        <v>122818323</v>
       </c>
       <c r="B38" t="n">
-        <v>79813</v>
+        <v>79847</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4973,46 +4945,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229748</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528727</v>
+        <v>528667</v>
       </c>
       <c r="R38" t="n">
-        <v>6998595</v>
+        <v>6998534</v>
       </c>
       <c r="S38" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5041,7 +5008,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5051,12 +5018,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>Rikligt på bark på stam av levande gammal sälg i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5071,22 +5038,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122818025</v>
+        <v>122817273</v>
       </c>
       <c r="B39" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5099,37 +5066,46 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528631</v>
+        <v>528623</v>
       </c>
       <c r="R39" t="n">
-        <v>6998469</v>
+        <v>6998311</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5156,9 +5132,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5173,22 +5164,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122818122</v>
+        <v>122817869</v>
       </c>
       <c r="B40" t="n">
-        <v>79848</v>
+        <v>57499</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5197,38 +5188,47 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>100110</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528631</v>
+        <v>528645</v>
       </c>
       <c r="R40" t="n">
-        <v>6998473</v>
+        <v>6998384</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5287,10 +5287,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122818036</v>
+        <v>122817142</v>
       </c>
       <c r="B41" t="n">
-        <v>79751</v>
+        <v>57478</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5299,41 +5299,46 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528686</v>
+        <v>528699</v>
       </c>
       <c r="R41" t="n">
-        <v>6998471</v>
+        <v>6998430</v>
       </c>
       <c r="S41" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5360,24 +5365,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5392,22 +5387,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122817219</v>
+        <v>122816979</v>
       </c>
       <c r="B42" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5420,21 +5415,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5444,10 +5439,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528684</v>
+        <v>528730</v>
       </c>
       <c r="R42" t="n">
-        <v>6998437</v>
+        <v>6998447</v>
       </c>
       <c r="S42" t="n">
         <v>8</v>
@@ -5477,14 +5472,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På kolad ved</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5495,51 +5500,26 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122817112</v>
+        <v>122818770</v>
       </c>
       <c r="B43" t="n">
-        <v>78766</v>
+        <v>91235</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5552,46 +5532,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528711</v>
+        <v>528718</v>
       </c>
       <c r="R43" t="n">
-        <v>6998411</v>
+        <v>6998641</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5618,24 +5589,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5650,22 +5606,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122818654</v>
+        <v>122818204</v>
       </c>
       <c r="B44" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5678,42 +5634,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528711</v>
+        <v>528649</v>
       </c>
       <c r="R44" t="n">
-        <v>6998632</v>
+        <v>6998490</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5740,14 +5691,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På innerbark på gammal björkhögstubbe i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5762,22 +5723,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122818713</v>
+        <v>122816987</v>
       </c>
       <c r="B45" t="n">
-        <v>90944</v>
+        <v>79384</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5790,37 +5751,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528718</v>
+        <v>528755</v>
       </c>
       <c r="R45" t="n">
-        <v>6998641</v>
+        <v>6998446</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5847,9 +5808,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På bränd jöttetallstubbe</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5864,22 +5840,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122819397</v>
+        <v>122818654</v>
       </c>
       <c r="B46" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5892,16 +5868,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5909,14 +5885,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5925,10 +5897,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528826</v>
+        <v>528711</v>
       </c>
       <c r="R46" t="n">
-        <v>6998595</v>
+        <v>6998632</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5961,6 +5933,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5987,10 +5964,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122818503</v>
+        <v>122817645</v>
       </c>
       <c r="B47" t="n">
-        <v>57478</v>
+        <v>57499</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5999,46 +5976,50 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>100110</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528652</v>
+        <v>528643</v>
       </c>
       <c r="R47" t="n">
-        <v>6998555</v>
+        <v>6998354</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6065,14 +6046,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6087,22 +6073,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122818681</v>
+        <v>122819448</v>
       </c>
       <c r="B48" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6111,41 +6097,46 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528686</v>
+        <v>528696</v>
       </c>
       <c r="R48" t="n">
-        <v>6998618</v>
+        <v>6998688</v>
       </c>
       <c r="S48" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6177,6 +6168,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Frodiga bålar.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6188,27 +6184,17 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Sten/berg på land</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stone/rock on land</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6226,10 +6212,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122817273</v>
+        <v>122818321</v>
       </c>
       <c r="B49" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6242,46 +6228,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528623</v>
+        <v>528805</v>
       </c>
       <c r="R49" t="n">
-        <v>6998311</v>
+        <v>6998631</v>
       </c>
       <c r="S49" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6310,7 +6287,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6320,12 +6297,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6352,10 +6329,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122818514</v>
+        <v>122818036</v>
       </c>
       <c r="B50" t="n">
-        <v>74863</v>
+        <v>79751</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6364,41 +6341,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528635</v>
+        <v>528686</v>
       </c>
       <c r="R50" t="n">
-        <v>6998546</v>
+        <v>6998471</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6425,9 +6402,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6442,22 +6434,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122818126</v>
+        <v>122819379</v>
       </c>
       <c r="B51" t="n">
-        <v>79847</v>
+        <v>98357</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6466,41 +6458,50 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528624</v>
+        <v>528802</v>
       </c>
       <c r="R51" t="n">
-        <v>6998489</v>
+        <v>6998594</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6527,9 +6528,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6544,22 +6560,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122819448</v>
+        <v>122817278</v>
       </c>
       <c r="B52" t="n">
-        <v>79876</v>
+        <v>57478</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6568,43 +6584,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>528696</v>
+        <v>528671</v>
       </c>
       <c r="R52" t="n">
-        <v>6998688</v>
+        <v>6998337</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6641,7 +6657,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Frodiga bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6652,21 +6668,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6683,10 +6684,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122818770</v>
+        <v>122818126</v>
       </c>
       <c r="B53" t="n">
-        <v>91235</v>
+        <v>79847</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6699,34 +6700,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>528718</v>
+        <v>528624</v>
       </c>
       <c r="R53" t="n">
-        <v>6998641</v>
+        <v>6998489</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6785,10 +6786,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122819058</v>
+        <v>122817601</v>
       </c>
       <c r="B54" t="n">
-        <v>78766</v>
+        <v>90964</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6801,37 +6802,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>528654</v>
+        <v>528645</v>
       </c>
       <c r="R54" t="n">
-        <v>6998628</v>
+        <v>6998384</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6871,31 +6872,6 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6912,10 +6888,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122818040</v>
+        <v>122818613</v>
       </c>
       <c r="B55" t="n">
-        <v>78766</v>
+        <v>98357</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6924,41 +6900,55 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>528621</v>
+        <v>528723</v>
       </c>
       <c r="R55" t="n">
-        <v>6998383</v>
+        <v>6998554</v>
       </c>
       <c r="S55" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6985,11 +6975,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På marken i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6998,51 +7003,26 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122817278</v>
+        <v>122819397</v>
       </c>
       <c r="B56" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7055,16 +7035,16 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -7072,22 +7052,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>528671</v>
+        <v>528826</v>
       </c>
       <c r="R56" t="n">
-        <v>6998337</v>
+        <v>6998595</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7120,11 +7104,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7151,10 +7130,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122817942</v>
+        <v>122818247</v>
       </c>
       <c r="B57" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7167,39 +7146,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>528655</v>
+        <v>528605</v>
       </c>
       <c r="R57" t="n">
-        <v>6998433</v>
+        <v>6998454</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7234,11 +7208,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7247,6 +7216,31 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7263,10 +7257,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122817325</v>
+        <v>122818165</v>
       </c>
       <c r="B58" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7279,42 +7273,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>528640</v>
+        <v>528594</v>
       </c>
       <c r="R58" t="n">
-        <v>6998336</v>
+        <v>6998419</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7346,11 +7335,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7359,6 +7343,31 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7375,10 +7384,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122817037</v>
+        <v>122817110</v>
       </c>
       <c r="B59" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7391,47 +7400,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>528752</v>
+        <v>528711</v>
       </c>
       <c r="R59" t="n">
-        <v>6998456</v>
+        <v>6998430</v>
       </c>
       <c r="S59" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7458,14 +7457,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall.</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7476,51 +7485,26 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122818174</v>
+        <v>122818675</v>
       </c>
       <c r="B60" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7533,27 +7517,31 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7562,13 +7550,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>528625</v>
+        <v>528722</v>
       </c>
       <c r="R60" t="n">
-        <v>6998500</v>
+        <v>6998660</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7595,14 +7583,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7617,22 +7610,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122817517</v>
+        <v>122817554</v>
       </c>
       <c r="B61" t="n">
-        <v>78411</v>
+        <v>57478</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7645,34 +7638,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>528643</v>
+        <v>528648</v>
       </c>
       <c r="R61" t="n">
-        <v>6998354</v>
+        <v>6998359</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7702,24 +7700,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På ved på gammal tallstubbe</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7734,19 +7722,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122817714</v>
+        <v>122817546</v>
       </c>
       <c r="B62" t="n">
         <v>74863</v>
@@ -7786,13 +7774,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>528625</v>
+        <v>528628</v>
       </c>
       <c r="R62" t="n">
-        <v>6998424</v>
+        <v>6998367</v>
       </c>
       <c r="S62" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7821,7 +7809,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7831,7 +7819,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -7863,10 +7851,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122818032</v>
+        <v>122818955</v>
       </c>
       <c r="B63" t="n">
-        <v>79876</v>
+        <v>74786</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7875,38 +7863,43 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6462</v>
+        <v>1460</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>528631</v>
+        <v>528791</v>
       </c>
       <c r="R63" t="n">
-        <v>6998469</v>
+        <v>6998633</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7936,9 +7929,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7953,22 +7961,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122817554</v>
+        <v>122818681</v>
       </c>
       <c r="B64" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7981,42 +7989,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>528648</v>
+        <v>528686</v>
       </c>
       <c r="R64" t="n">
-        <v>6998359</v>
+        <v>6998618</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8048,11 +8051,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8061,6 +8059,31 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -8077,10 +8100,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122817550</v>
+        <v>122818032</v>
       </c>
       <c r="B65" t="n">
-        <v>57478</v>
+        <v>79876</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8089,43 +8112,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>528648</v>
+        <v>528631</v>
       </c>
       <c r="R65" t="n">
-        <v>6998358</v>
+        <v>6998469</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8158,11 +8176,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8189,10 +8202,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122819379</v>
+        <v>122817037</v>
       </c>
       <c r="B66" t="n">
-        <v>98357</v>
+        <v>57478</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8201,35 +8214,36 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8238,13 +8252,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>528802</v>
+        <v>528752</v>
       </c>
       <c r="R66" t="n">
-        <v>6998594</v>
+        <v>6998456</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8271,24 +8285,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8299,26 +8303,51 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122818165</v>
+        <v>122818168</v>
       </c>
       <c r="B67" t="n">
-        <v>78766</v>
+        <v>79807</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8327,25 +8356,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8355,13 +8384,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>528594</v>
+        <v>528669</v>
       </c>
       <c r="R67" t="n">
-        <v>6998419</v>
+        <v>6998500</v>
       </c>
       <c r="S67" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8388,11 +8417,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På bark på stam av död gammal asp (40 cm dbh) i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8402,50 +8446,40 @@
       <c r="AG67" t="b">
         <v>0</v>
       </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122818675</v>
+        <v>122818328</v>
       </c>
       <c r="B68" t="n">
-        <v>78766</v>
+        <v>77699</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8458,46 +8492,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>528722</v>
+        <v>528800</v>
       </c>
       <c r="R68" t="n">
-        <v>6998660</v>
+        <v>6998633</v>
       </c>
       <c r="S68" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8526,7 +8551,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8536,7 +8561,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8563,10 +8593,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122818168</v>
+        <v>122818025</v>
       </c>
       <c r="B69" t="n">
-        <v>79807</v>
+        <v>79848</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8575,25 +8605,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>229497</v>
+        <v>2081</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8603,10 +8633,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>528669</v>
+        <v>528631</v>
       </c>
       <c r="R69" t="n">
-        <v>6998500</v>
+        <v>6998469</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8636,26 +8666,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På bark på stam av död gammal asp (40 cm dbh) i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -8664,41 +8679,26 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122818864</v>
+        <v>122817517</v>
       </c>
       <c r="B70" t="n">
-        <v>74863</v>
+        <v>78411</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8711,21 +8711,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6440</v>
+        <v>353</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8735,13 +8735,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>528732</v>
+        <v>528643</v>
       </c>
       <c r="R70" t="n">
-        <v>6998659</v>
+        <v>6998354</v>
       </c>
       <c r="S70" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8770,7 +8770,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8780,12 +8780,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På ved på gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8800,22 +8800,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122817054</v>
+        <v>122817219</v>
       </c>
       <c r="B71" t="n">
-        <v>79751</v>
+        <v>78766</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8824,25 +8824,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8852,13 +8852,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>528755</v>
+        <v>528684</v>
       </c>
       <c r="R71" t="n">
-        <v>6998448</v>
+        <v>6998437</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8885,24 +8885,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>09:08</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>09:08</t>
-        </is>
-      </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8913,26 +8903,51 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122818573</v>
+        <v>122818503</v>
       </c>
       <c r="B72" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8945,37 +8960,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>528630</v>
+        <v>528652</v>
       </c>
       <c r="R72" t="n">
-        <v>6998539</v>
+        <v>6998555</v>
       </c>
       <c r="S72" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9007,6 +9027,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -9015,31 +9040,6 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">

--- a/artfynd/A 55431-2024 artfynd.xlsx
+++ b/artfynd/A 55431-2024 artfynd.xlsx
@@ -2097,10 +2097,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122818514</v>
+        <v>122818966</v>
       </c>
       <c r="B14" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2113,37 +2113,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528635</v>
+        <v>528791</v>
       </c>
       <c r="R14" t="n">
-        <v>6998546</v>
+        <v>6998599</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2170,11 +2175,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal sälg (25 cm dbh) i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2183,26 +2203,41 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122818026</v>
+        <v>122818514</v>
       </c>
       <c r="B15" t="n">
-        <v>79847</v>
+        <v>74863</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2215,34 +2250,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528631</v>
+        <v>528635</v>
       </c>
       <c r="R15" t="n">
-        <v>6998469</v>
+        <v>6998546</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2301,7 +2336,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122818966</v>
+        <v>122818026</v>
       </c>
       <c r="B16" t="n">
         <v>79847</v>
@@ -2335,24 +2370,19 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528791</v>
+        <v>528631</v>
       </c>
       <c r="R16" t="n">
-        <v>6998599</v>
+        <v>6998469</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2379,26 +2409,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal sälg (25 cm dbh) i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2407,31 +2422,16 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -4343,10 +4343,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122817714</v>
+        <v>122817325</v>
       </c>
       <c r="B33" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4359,37 +4359,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528625</v>
+        <v>528640</v>
       </c>
       <c r="R33" t="n">
-        <v>6998424</v>
+        <v>6998336</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4416,24 +4421,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4448,22 +4443,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122818573</v>
+        <v>122817714</v>
       </c>
       <c r="B34" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4476,37 +4471,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528630</v>
+        <v>528625</v>
       </c>
       <c r="R34" t="n">
-        <v>6998539</v>
+        <v>6998424</v>
       </c>
       <c r="S34" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4533,11 +4528,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4546,51 +4556,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122818759</v>
+        <v>122818573</v>
       </c>
       <c r="B35" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4603,37 +4588,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528778</v>
+        <v>528630</v>
       </c>
       <c r="R35" t="n">
-        <v>6998602</v>
+        <v>6998539</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4660,26 +4645,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På gammal asp i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4688,26 +4658,51 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122817054</v>
+        <v>122818759</v>
       </c>
       <c r="B36" t="n">
-        <v>79751</v>
+        <v>79847</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4716,25 +4711,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4744,10 +4739,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528755</v>
+        <v>528778</v>
       </c>
       <c r="R36" t="n">
-        <v>6998448</v>
+        <v>6998602</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4779,7 +4774,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4789,12 +4784,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>På gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4821,10 +4816,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122817325</v>
+        <v>122817054</v>
       </c>
       <c r="B37" t="n">
-        <v>57478</v>
+        <v>79751</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4833,43 +4828,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528640</v>
+        <v>528755</v>
       </c>
       <c r="R37" t="n">
-        <v>6998336</v>
+        <v>6998448</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4899,14 +4889,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4921,22 +4921,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122818323</v>
+        <v>122816979</v>
       </c>
       <c r="B38" t="n">
-        <v>79847</v>
+        <v>78503</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4949,21 +4949,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4973,13 +4973,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528667</v>
+        <v>528730</v>
       </c>
       <c r="R38" t="n">
-        <v>6998534</v>
+        <v>6998447</v>
       </c>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Rikligt på bark på stam av levande gammal sälg i gammal barrblandskog</t>
+          <t>På kolad ved</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5038,22 +5038,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122817273</v>
+        <v>122818323</v>
       </c>
       <c r="B39" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5066,46 +5066,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528623</v>
+        <v>528667</v>
       </c>
       <c r="R39" t="n">
-        <v>6998311</v>
+        <v>6998534</v>
       </c>
       <c r="S39" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5134,7 +5125,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5144,12 +5135,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Rikligt på bark på stam av levande gammal sälg i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5164,22 +5155,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122817869</v>
+        <v>122817273</v>
       </c>
       <c r="B40" t="n">
-        <v>57499</v>
+        <v>78766</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5188,35 +5179,35 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100110</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5225,13 +5216,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528645</v>
+        <v>528623</v>
       </c>
       <c r="R40" t="n">
-        <v>6998384</v>
+        <v>6998311</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5258,9 +5249,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5275,22 +5281,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122817142</v>
+        <v>122817869</v>
       </c>
       <c r="B41" t="n">
-        <v>57478</v>
+        <v>57499</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5299,31 +5305,35 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>100110</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5332,10 +5342,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528699</v>
+        <v>528645</v>
       </c>
       <c r="R41" t="n">
-        <v>6998430</v>
+        <v>6998384</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5368,11 +5378,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5399,10 +5404,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122816979</v>
+        <v>122817142</v>
       </c>
       <c r="B42" t="n">
-        <v>78503</v>
+        <v>57478</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5415,37 +5420,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528730</v>
+        <v>528699</v>
       </c>
       <c r="R42" t="n">
-        <v>6998447</v>
+        <v>6998430</v>
       </c>
       <c r="S42" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5472,24 +5482,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>09:03</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>09:03</t>
-        </is>
-      </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På kolad ved</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5504,12 +5504,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -6446,10 +6446,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122819379</v>
+        <v>122817278</v>
       </c>
       <c r="B51" t="n">
-        <v>98357</v>
+        <v>57478</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6458,35 +6458,31 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6495,13 +6491,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528802</v>
+        <v>528671</v>
       </c>
       <c r="R51" t="n">
-        <v>6998594</v>
+        <v>6998337</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6528,24 +6524,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6560,22 +6546,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122817278</v>
+        <v>122819379</v>
       </c>
       <c r="B52" t="n">
-        <v>57478</v>
+        <v>98357</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6584,31 +6570,35 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6617,13 +6607,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>528671</v>
+        <v>528802</v>
       </c>
       <c r="R52" t="n">
-        <v>6998337</v>
+        <v>6998594</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6650,14 +6640,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6672,22 +6672,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122818126</v>
+        <v>122817601</v>
       </c>
       <c r="B53" t="n">
-        <v>79847</v>
+        <v>90964</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6700,21 +6700,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6724,10 +6724,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>528624</v>
+        <v>528645</v>
       </c>
       <c r="R53" t="n">
-        <v>6998489</v>
+        <v>6998384</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6786,10 +6786,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122817601</v>
+        <v>122818126</v>
       </c>
       <c r="B54" t="n">
-        <v>90964</v>
+        <v>79847</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6802,21 +6802,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6826,10 +6826,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>528645</v>
+        <v>528624</v>
       </c>
       <c r="R54" t="n">
-        <v>6998384</v>
+        <v>6998489</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -8476,10 +8476,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122818328</v>
+        <v>122818503</v>
       </c>
       <c r="B68" t="n">
-        <v>77699</v>
+        <v>57478</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8492,37 +8492,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>528800</v>
+        <v>528652</v>
       </c>
       <c r="R68" t="n">
-        <v>6998633</v>
+        <v>6998555</v>
       </c>
       <c r="S68" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8549,24 +8554,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8581,22 +8576,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122818025</v>
+        <v>122817219</v>
       </c>
       <c r="B69" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8609,21 +8604,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8633,13 +8628,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>528631</v>
+        <v>528684</v>
       </c>
       <c r="R69" t="n">
-        <v>6998469</v>
+        <v>6998437</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8671,6 +8666,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -8679,6 +8679,31 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8695,10 +8720,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122817517</v>
+        <v>122818025</v>
       </c>
       <c r="B70" t="n">
-        <v>78411</v>
+        <v>79848</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8711,21 +8736,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8735,10 +8760,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>528643</v>
+        <v>528631</v>
       </c>
       <c r="R70" t="n">
-        <v>6998354</v>
+        <v>6998469</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8768,24 +8793,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>På ved på gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8800,22 +8810,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122817219</v>
+        <v>122817517</v>
       </c>
       <c r="B71" t="n">
-        <v>78766</v>
+        <v>78411</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8828,21 +8838,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8852,13 +8862,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>528684</v>
+        <v>528643</v>
       </c>
       <c r="R71" t="n">
-        <v>6998437</v>
+        <v>6998354</v>
       </c>
       <c r="S71" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8885,14 +8895,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På ved på gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8903,51 +8923,26 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122818503</v>
+        <v>122818328</v>
       </c>
       <c r="B72" t="n">
-        <v>57478</v>
+        <v>77699</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8960,42 +8955,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>528652</v>
+        <v>528800</v>
       </c>
       <c r="R72" t="n">
-        <v>6998555</v>
+        <v>6998633</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9022,14 +9012,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9044,12 +9044,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>

--- a/artfynd/A 55431-2024 artfynd.xlsx
+++ b/artfynd/A 55431-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122818122</v>
+        <v>122818174</v>
       </c>
       <c r="B3" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,34 +802,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528631</v>
+        <v>528625</v>
       </c>
       <c r="R3" t="n">
-        <v>6998473</v>
+        <v>6998500</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,6 +867,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122818174</v>
+        <v>122818122</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,39 +914,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528625</v>
+        <v>528631</v>
       </c>
       <c r="R4" t="n">
-        <v>6998500</v>
+        <v>6998473</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,11 +974,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -2097,10 +2097,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122818966</v>
+        <v>122818514</v>
       </c>
       <c r="B14" t="n">
-        <v>79847</v>
+        <v>74863</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2113,42 +2113,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528791</v>
+        <v>528635</v>
       </c>
       <c r="R14" t="n">
-        <v>6998599</v>
+        <v>6998546</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2175,26 +2170,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal sälg (25 cm dbh) i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2203,41 +2183,26 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122818514</v>
+        <v>122818026</v>
       </c>
       <c r="B15" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2250,34 +2215,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528635</v>
+        <v>528631</v>
       </c>
       <c r="R15" t="n">
-        <v>6998546</v>
+        <v>6998469</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2336,7 +2301,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122818026</v>
+        <v>122818966</v>
       </c>
       <c r="B16" t="n">
         <v>79847</v>
@@ -2370,19 +2335,24 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528631</v>
+        <v>528791</v>
       </c>
       <c r="R16" t="n">
-        <v>6998469</v>
+        <v>6998599</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2409,11 +2379,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal sälg (25 cm dbh) i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2422,16 +2407,31 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2550,10 +2550,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122817937</v>
+        <v>122818125</v>
       </c>
       <c r="B18" t="n">
-        <v>90955</v>
+        <v>78503</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2562,25 +2562,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1205</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528686</v>
+        <v>528687</v>
       </c>
       <c r="R18" t="n">
-        <v>6998446</v>
+        <v>6998489</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På död asp</t>
+          <t>På kolad ved på gammal tallstubbe i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2655,22 +2655,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122817144</v>
+        <v>122817413</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2683,31 +2683,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2716,13 +2712,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528705</v>
+        <v>528612</v>
       </c>
       <c r="R19" t="n">
-        <v>6998384</v>
+        <v>6998323</v>
       </c>
       <c r="S19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2749,19 +2745,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>09:13</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2776,22 +2767,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122817112</v>
+        <v>122816988</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2804,31 +2795,32 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2837,13 +2829,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528711</v>
+        <v>528756</v>
       </c>
       <c r="R20" t="n">
-        <v>6998411</v>
+        <v>6998450</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2870,24 +2862,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Äldre ringhack på en tall.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2898,26 +2880,51 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122817413</v>
+        <v>122817937</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>90955</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2926,46 +2933,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528612</v>
+        <v>528686</v>
       </c>
       <c r="R21" t="n">
-        <v>6998323</v>
+        <v>6998446</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2992,14 +2994,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På död asp</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3014,22 +3026,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122816988</v>
+        <v>122817144</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3042,32 +3054,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3076,13 +3087,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528756</v>
+        <v>528705</v>
       </c>
       <c r="R22" t="n">
-        <v>6998450</v>
+        <v>6998384</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3109,14 +3120,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på en tall.</t>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3127,51 +3143,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122818125</v>
+        <v>122817112</v>
       </c>
       <c r="B23" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3184,37 +3175,46 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528687</v>
+        <v>528711</v>
       </c>
       <c r="R23" t="n">
-        <v>6998489</v>
+        <v>6998411</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal tallstubbe i gammal barrblandskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3273,12 +3273,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -4343,10 +4343,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122817325</v>
+        <v>122817714</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4359,42 +4359,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528640</v>
+        <v>528625</v>
       </c>
       <c r="R33" t="n">
-        <v>6998336</v>
+        <v>6998424</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4421,14 +4416,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4443,22 +4448,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122817714</v>
+        <v>122818573</v>
       </c>
       <c r="B34" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4471,37 +4476,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528625</v>
+        <v>528630</v>
       </c>
       <c r="R34" t="n">
-        <v>6998424</v>
+        <v>6998539</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4528,26 +4533,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4556,26 +4546,51 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122818573</v>
+        <v>122818759</v>
       </c>
       <c r="B35" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4588,37 +4603,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528630</v>
+        <v>528778</v>
       </c>
       <c r="R35" t="n">
-        <v>6998539</v>
+        <v>6998602</v>
       </c>
       <c r="S35" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4645,11 +4660,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På gammal asp i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4658,51 +4688,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122818759</v>
+        <v>122817054</v>
       </c>
       <c r="B36" t="n">
-        <v>79847</v>
+        <v>79751</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4711,25 +4716,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4739,10 +4744,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528778</v>
+        <v>528755</v>
       </c>
       <c r="R36" t="n">
-        <v>6998602</v>
+        <v>6998448</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4774,7 +4779,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4784,12 +4789,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På gammal asp i gammal barrblandskog</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4816,10 +4821,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122817054</v>
+        <v>122817325</v>
       </c>
       <c r="B37" t="n">
-        <v>79751</v>
+        <v>57478</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4828,38 +4833,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528755</v>
+        <v>528640</v>
       </c>
       <c r="R37" t="n">
-        <v>6998448</v>
+        <v>6998336</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4889,24 +4899,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>09:08</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>09:08</t>
-        </is>
-      </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4921,22 +4921,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122816979</v>
+        <v>122818323</v>
       </c>
       <c r="B38" t="n">
-        <v>78503</v>
+        <v>79847</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4949,21 +4949,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4973,13 +4973,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528730</v>
+        <v>528667</v>
       </c>
       <c r="R38" t="n">
-        <v>6998447</v>
+        <v>6998534</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På kolad ved</t>
+          <t>Rikligt på bark på stam av levande gammal sälg i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5038,22 +5038,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122818323</v>
+        <v>122817273</v>
       </c>
       <c r="B39" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5066,37 +5066,46 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528667</v>
+        <v>528623</v>
       </c>
       <c r="R39" t="n">
-        <v>6998534</v>
+        <v>6998311</v>
       </c>
       <c r="S39" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5125,7 +5134,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5135,12 +5144,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Rikligt på bark på stam av levande gammal sälg i gammal barrblandskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5155,22 +5164,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122817273</v>
+        <v>122817869</v>
       </c>
       <c r="B40" t="n">
-        <v>78766</v>
+        <v>57499</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5179,35 +5188,35 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100110</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5216,13 +5225,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528623</v>
+        <v>528645</v>
       </c>
       <c r="R40" t="n">
-        <v>6998311</v>
+        <v>6998384</v>
       </c>
       <c r="S40" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5249,24 +5258,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5281,22 +5275,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122817869</v>
+        <v>122817142</v>
       </c>
       <c r="B41" t="n">
-        <v>57499</v>
+        <v>57478</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5305,35 +5299,31 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100110</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5342,10 +5332,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528645</v>
+        <v>528699</v>
       </c>
       <c r="R41" t="n">
-        <v>6998384</v>
+        <v>6998430</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5378,6 +5368,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5404,10 +5399,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122817142</v>
+        <v>122816979</v>
       </c>
       <c r="B42" t="n">
-        <v>57478</v>
+        <v>78503</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5420,42 +5415,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528699</v>
+        <v>528730</v>
       </c>
       <c r="R42" t="n">
-        <v>6998430</v>
+        <v>6998447</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5482,14 +5472,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På kolad ved</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5504,12 +5504,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -6446,10 +6446,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122817278</v>
+        <v>122819379</v>
       </c>
       <c r="B51" t="n">
-        <v>57478</v>
+        <v>98357</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6458,31 +6458,35 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6491,13 +6495,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528671</v>
+        <v>528802</v>
       </c>
       <c r="R51" t="n">
-        <v>6998337</v>
+        <v>6998594</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6524,14 +6528,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6546,22 +6560,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122819379</v>
+        <v>122817278</v>
       </c>
       <c r="B52" t="n">
-        <v>98357</v>
+        <v>57478</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6570,35 +6584,31 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6607,13 +6617,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>528802</v>
+        <v>528671</v>
       </c>
       <c r="R52" t="n">
-        <v>6998594</v>
+        <v>6998337</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6640,24 +6650,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6672,22 +6672,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122817601</v>
+        <v>122818126</v>
       </c>
       <c r="B53" t="n">
-        <v>90964</v>
+        <v>79847</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6700,21 +6700,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6724,10 +6724,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>528645</v>
+        <v>528624</v>
       </c>
       <c r="R53" t="n">
-        <v>6998384</v>
+        <v>6998489</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6786,10 +6786,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122818126</v>
+        <v>122817601</v>
       </c>
       <c r="B54" t="n">
-        <v>79847</v>
+        <v>90964</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6802,21 +6802,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6826,10 +6826,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>528624</v>
+        <v>528645</v>
       </c>
       <c r="R54" t="n">
-        <v>6998489</v>
+        <v>6998384</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -8476,10 +8476,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122818503</v>
+        <v>122818328</v>
       </c>
       <c r="B68" t="n">
-        <v>57478</v>
+        <v>77699</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8492,42 +8492,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>528652</v>
+        <v>528800</v>
       </c>
       <c r="R68" t="n">
-        <v>6998555</v>
+        <v>6998633</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8554,14 +8549,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8576,22 +8581,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122817219</v>
+        <v>122818025</v>
       </c>
       <c r="B69" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8604,21 +8609,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8628,13 +8633,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>528684</v>
+        <v>528631</v>
       </c>
       <c r="R69" t="n">
-        <v>6998437</v>
+        <v>6998469</v>
       </c>
       <c r="S69" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8666,11 +8671,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -8679,31 +8679,6 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8720,10 +8695,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122818025</v>
+        <v>122817517</v>
       </c>
       <c r="B70" t="n">
-        <v>79848</v>
+        <v>78411</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8736,21 +8711,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8760,10 +8735,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>528631</v>
+        <v>528643</v>
       </c>
       <c r="R70" t="n">
-        <v>6998469</v>
+        <v>6998354</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8793,9 +8768,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>På ved på gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8810,22 +8800,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122817517</v>
+        <v>122817219</v>
       </c>
       <c r="B71" t="n">
-        <v>78411</v>
+        <v>78766</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8838,21 +8828,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8862,13 +8852,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>528643</v>
+        <v>528684</v>
       </c>
       <c r="R71" t="n">
-        <v>6998354</v>
+        <v>6998437</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8895,24 +8885,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På ved på gammal tallstubbe</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8923,26 +8903,51 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122818328</v>
+        <v>122818503</v>
       </c>
       <c r="B72" t="n">
-        <v>77699</v>
+        <v>57478</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8955,37 +8960,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>528800</v>
+        <v>528652</v>
       </c>
       <c r="R72" t="n">
-        <v>6998633</v>
+        <v>6998555</v>
       </c>
       <c r="S72" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9012,24 +9022,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9044,12 +9044,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>

--- a/artfynd/A 55431-2024 artfynd.xlsx
+++ b/artfynd/A 55431-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122818174</v>
+        <v>122818026</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,39 +802,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528625</v>
+        <v>528631</v>
       </c>
       <c r="R3" t="n">
-        <v>6998500</v>
+        <v>6998469</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,11 +862,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122818122</v>
+        <v>122818032</v>
       </c>
       <c r="B4" t="n">
-        <v>79848</v>
+        <v>79876</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,25 +900,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -941,7 +931,7 @@
         <v>528631</v>
       </c>
       <c r="R4" t="n">
-        <v>6998473</v>
+        <v>6998469</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122817339</v>
+        <v>122819448</v>
       </c>
       <c r="B5" t="n">
-        <v>79384</v>
+        <v>79876</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,41 +1002,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528649</v>
+        <v>528696</v>
       </c>
       <c r="R5" t="n">
-        <v>6998383</v>
+        <v>6998688</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1073,24 +1068,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gammal tallstubbe</t>
+          <t>Frodiga bålar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,26 +1086,41 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stone/rock on land</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122819024</v>
+        <v>122817278</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,37 +1133,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528636</v>
+        <v>528671</v>
       </c>
       <c r="R6" t="n">
-        <v>6998609</v>
+        <v>6998337</v>
       </c>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1195,6 +1200,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1203,31 +1213,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Dead branch  # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1244,7 +1229,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122819118</v>
+        <v>122818681</v>
       </c>
       <c r="B7" t="n">
         <v>78766</v>
@@ -1284,13 +1269,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528690</v>
+        <v>528686</v>
       </c>
       <c r="R7" t="n">
-        <v>6998652</v>
+        <v>6998618</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1320,11 +1305,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122818035</v>
+        <v>122818654</v>
       </c>
       <c r="B8" t="n">
-        <v>79807</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,38 +1368,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528677</v>
+        <v>528711</v>
       </c>
       <c r="R8" t="n">
-        <v>6998487</v>
+        <v>6998632</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1449,24 +1434,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,22 +1456,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122817657</v>
+        <v>122818613</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1505,38 +1480,52 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528650</v>
+        <v>528723</v>
       </c>
       <c r="R9" t="n">
-        <v>6998397</v>
+        <v>6998554</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1566,14 +1555,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,51 +1583,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122819033</v>
+        <v>122817289</v>
       </c>
       <c r="B10" t="n">
-        <v>74675</v>
+        <v>79145</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1637,25 +1611,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6428</v>
+        <v>257107</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Blek lundlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Bacidia rosellizans</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>S.Ekman</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1665,13 +1639,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528798</v>
+        <v>528632</v>
       </c>
       <c r="R10" t="n">
-        <v>6998603</v>
+        <v>6998403</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1700,7 +1674,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1710,12 +1684,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal barrblandskog</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1742,10 +1716,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122818040</v>
+        <v>122818955</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>74786</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1758,37 +1732,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1460</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528621</v>
+        <v>528791</v>
       </c>
       <c r="R11" t="n">
-        <v>6998383</v>
+        <v>6998633</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1815,11 +1794,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1828,51 +1822,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122818536</v>
+        <v>122817273</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1885,42 +1854,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528665</v>
+        <v>528623</v>
       </c>
       <c r="R12" t="n">
-        <v>6998574</v>
+        <v>6998311</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1947,14 +1920,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1969,22 +1952,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122817186</v>
+        <v>122817054</v>
       </c>
       <c r="B13" t="n">
-        <v>57428</v>
+        <v>79751</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1997,48 +1980,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102621</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528689</v>
+        <v>528755</v>
       </c>
       <c r="R13" t="n">
-        <v>6998416</v>
+        <v>6998448</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2068,9 +2037,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2085,22 +2069,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122818514</v>
+        <v>122816987</v>
       </c>
       <c r="B14" t="n">
-        <v>74863</v>
+        <v>79384</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2113,37 +2097,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528635</v>
+        <v>528755</v>
       </c>
       <c r="R14" t="n">
-        <v>6998546</v>
+        <v>6998446</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2170,9 +2154,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På bränd jöttetallstubbe</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2187,22 +2186,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122818026</v>
+        <v>122817339</v>
       </c>
       <c r="B15" t="n">
-        <v>79847</v>
+        <v>79384</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2215,21 +2214,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2239,13 +2238,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528631</v>
+        <v>528649</v>
       </c>
       <c r="R15" t="n">
-        <v>6998469</v>
+        <v>6998383</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2272,9 +2271,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2289,22 +2303,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122818966</v>
+        <v>122817112</v>
       </c>
       <c r="B16" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2317,27 +2331,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2346,13 +2364,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528791</v>
+        <v>528711</v>
       </c>
       <c r="R16" t="n">
-        <v>6998599</v>
+        <v>6998411</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2381,7 +2399,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2391,12 +2409,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg (25 cm dbh) i gammal barrblandskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2407,38 +2425,23 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122817942</v>
+        <v>122817413</v>
       </c>
       <c r="B17" t="n">
         <v>57478</v>
@@ -2483,10 +2486,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528655</v>
+        <v>528612</v>
       </c>
       <c r="R17" t="n">
-        <v>6998433</v>
+        <v>6998323</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2523,7 +2526,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2550,10 +2553,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122818125</v>
+        <v>122817714</v>
       </c>
       <c r="B18" t="n">
-        <v>78503</v>
+        <v>74863</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2566,21 +2569,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2590,13 +2593,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528687</v>
+        <v>528625</v>
       </c>
       <c r="R18" t="n">
-        <v>6998489</v>
+        <v>6998424</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2625,7 +2628,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2635,12 +2638,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal tallstubbe i gammal barrblandskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2655,22 +2658,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122817413</v>
+        <v>122817186</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>57428</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2679,20 +2682,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2700,10 +2703,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2712,10 +2724,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528612</v>
+        <v>528689</v>
       </c>
       <c r="R19" t="n">
-        <v>6998323</v>
+        <v>6998416</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2748,11 +2760,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2779,10 +2786,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122816988</v>
+        <v>122817144</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2795,32 +2802,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2829,13 +2835,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528756</v>
+        <v>528705</v>
       </c>
       <c r="R20" t="n">
-        <v>6998450</v>
+        <v>6998384</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2862,14 +2868,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på en tall.</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2880,51 +2891,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122817937</v>
+        <v>122818514</v>
       </c>
       <c r="B21" t="n">
-        <v>90955</v>
+        <v>74863</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2933,41 +2919,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1205</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528686</v>
+        <v>528635</v>
       </c>
       <c r="R21" t="n">
-        <v>6998446</v>
+        <v>6998546</v>
       </c>
       <c r="S21" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2994,24 +2980,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På död asp</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3026,22 +2997,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122817144</v>
+        <v>122818125</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3054,46 +3025,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528705</v>
+        <v>528687</v>
       </c>
       <c r="R22" t="n">
-        <v>6998384</v>
+        <v>6998489</v>
       </c>
       <c r="S22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3122,7 +3084,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3132,7 +3094,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal tallstubbe i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3147,22 +3114,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122817112</v>
+        <v>122818126</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3175,46 +3142,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528711</v>
+        <v>528624</v>
       </c>
       <c r="R23" t="n">
-        <v>6998411</v>
+        <v>6998489</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3241,24 +3199,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3273,22 +3216,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122817289</v>
+        <v>122817869</v>
       </c>
       <c r="B24" t="n">
-        <v>79145</v>
+        <v>57499</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3297,41 +3240,50 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>257107</v>
+        <v>100110</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blek lundlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bacidia rosellizans</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>S.Ekman</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528632</v>
+        <v>528645</v>
       </c>
       <c r="R24" t="n">
-        <v>6998403</v>
+        <v>6998384</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3358,24 +3310,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>09:23</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>09:23</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3390,22 +3327,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122818387</v>
+        <v>122818534</v>
       </c>
       <c r="B25" t="n">
-        <v>78766</v>
+        <v>79813</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3414,41 +3351,46 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528619</v>
+        <v>528727</v>
       </c>
       <c r="R25" t="n">
-        <v>6998495</v>
+        <v>6998595</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3475,11 +3417,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På gammal asp</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3488,51 +3445,26 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122818713</v>
+        <v>122818503</v>
       </c>
       <c r="B26" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3545,34 +3477,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528718</v>
+        <v>528652</v>
       </c>
       <c r="R26" t="n">
-        <v>6998641</v>
+        <v>6998555</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3605,6 +3542,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3631,10 +3573,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122818864</v>
+        <v>122817325</v>
       </c>
       <c r="B27" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3647,37 +3589,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528732</v>
+        <v>528640</v>
       </c>
       <c r="R27" t="n">
-        <v>6998659</v>
+        <v>6998336</v>
       </c>
       <c r="S27" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3704,24 +3651,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3736,22 +3673,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122818653</v>
+        <v>122819379</v>
       </c>
       <c r="B28" t="n">
-        <v>79847</v>
+        <v>98365</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3760,41 +3697,50 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528732</v>
+        <v>528802</v>
       </c>
       <c r="R28" t="n">
-        <v>6998541</v>
+        <v>6998594</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3823,7 +3769,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3833,12 +3779,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På asplåga i gammal barrblandskog</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3865,10 +3811,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122819058</v>
+        <v>122818025</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3881,37 +3827,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528654</v>
+        <v>528631</v>
       </c>
       <c r="R29" t="n">
-        <v>6998628</v>
+        <v>6998469</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3951,31 +3897,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3992,10 +3913,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122817550</v>
+        <v>122818204</v>
       </c>
       <c r="B30" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4008,42 +3929,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528648</v>
+        <v>528649</v>
       </c>
       <c r="R30" t="n">
-        <v>6998358</v>
+        <v>6998490</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4070,14 +3986,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På innerbark på gammal björkhögstubbe i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4092,22 +4018,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122817758</v>
+        <v>122818653</v>
       </c>
       <c r="B31" t="n">
-        <v>77699</v>
+        <v>79847</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4120,21 +4046,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4144,13 +4070,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528610</v>
+        <v>528732</v>
       </c>
       <c r="R31" t="n">
-        <v>6998403</v>
+        <v>6998541</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4179,7 +4105,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4189,12 +4115,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På asplåga i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4209,22 +4135,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122818534</v>
+        <v>122817219</v>
       </c>
       <c r="B32" t="n">
-        <v>79813</v>
+        <v>78766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4233,46 +4159,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528727</v>
+        <v>528684</v>
       </c>
       <c r="R32" t="n">
-        <v>6998595</v>
+        <v>6998437</v>
       </c>
       <c r="S32" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4299,24 +4220,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4327,26 +4238,51 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122817714</v>
+        <v>122817942</v>
       </c>
       <c r="B33" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4359,37 +4295,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528625</v>
+        <v>528655</v>
       </c>
       <c r="R33" t="n">
-        <v>6998424</v>
+        <v>6998433</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4416,24 +4357,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4448,22 +4379,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122818573</v>
+        <v>122817550</v>
       </c>
       <c r="B34" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4476,37 +4407,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528630</v>
+        <v>528648</v>
       </c>
       <c r="R34" t="n">
-        <v>6998539</v>
+        <v>6998358</v>
       </c>
       <c r="S34" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4538,6 +4474,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4546,31 +4487,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4587,10 +4503,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122818759</v>
+        <v>122818864</v>
       </c>
       <c r="B35" t="n">
-        <v>79847</v>
+        <v>74863</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4603,21 +4519,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4627,13 +4543,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528778</v>
+        <v>528732</v>
       </c>
       <c r="R35" t="n">
-        <v>6998602</v>
+        <v>6998659</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4662,7 +4578,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4672,12 +4588,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På gammal asp i gammal barrblandskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4692,22 +4608,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122817054</v>
+        <v>122817546</v>
       </c>
       <c r="B36" t="n">
-        <v>79751</v>
+        <v>74863</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4716,25 +4632,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4744,13 +4660,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528755</v>
+        <v>528628</v>
       </c>
       <c r="R36" t="n">
-        <v>6998448</v>
+        <v>6998367</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4779,7 +4695,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4789,12 +4705,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4809,22 +4725,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122817325</v>
+        <v>122819058</v>
       </c>
       <c r="B37" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4837,42 +4753,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528640</v>
+        <v>528654</v>
       </c>
       <c r="R37" t="n">
-        <v>6998336</v>
+        <v>6998628</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4904,11 +4815,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4917,6 +4823,31 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4933,7 +4864,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122818323</v>
+        <v>122818759</v>
       </c>
       <c r="B38" t="n">
         <v>79847</v>
@@ -4973,13 +4904,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528667</v>
+        <v>528778</v>
       </c>
       <c r="R38" t="n">
-        <v>6998534</v>
+        <v>6998602</v>
       </c>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5008,7 +4939,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5018,12 +4949,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Rikligt på bark på stam av levande gammal sälg i gammal barrblandskog</t>
+          <t>På gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5050,7 +4981,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122817273</v>
+        <v>122819118</v>
       </c>
       <c r="B39" t="n">
         <v>78766</v>
@@ -5083,29 +5014,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528623</v>
+        <v>528690</v>
       </c>
       <c r="R39" t="n">
-        <v>6998311</v>
+        <v>6998652</v>
       </c>
       <c r="S39" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5132,24 +5054,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5160,26 +5072,51 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122817869</v>
+        <v>122818168</v>
       </c>
       <c r="B40" t="n">
-        <v>57499</v>
+        <v>79807</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5192,43 +5129,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100110</v>
+        <v>229497</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528645</v>
+        <v>528669</v>
       </c>
       <c r="R40" t="n">
-        <v>6998384</v>
+        <v>6998500</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5258,11 +5186,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På bark på stam av död gammal asp (40 cm dbh) i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5271,26 +5214,41 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122817142</v>
+        <v>122817937</v>
       </c>
       <c r="B41" t="n">
-        <v>57478</v>
+        <v>90963</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5299,46 +5257,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528699</v>
+        <v>528686</v>
       </c>
       <c r="R41" t="n">
-        <v>6998430</v>
+        <v>6998446</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5365,14 +5318,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På död asp</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5387,22 +5350,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122816979</v>
+        <v>122818122</v>
       </c>
       <c r="B42" t="n">
-        <v>78503</v>
+        <v>79848</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5415,21 +5378,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5439,13 +5402,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528730</v>
+        <v>528631</v>
       </c>
       <c r="R42" t="n">
-        <v>6998447</v>
+        <v>6998473</v>
       </c>
       <c r="S42" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5472,24 +5435,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>09:03</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>09:03</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På kolad ved</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5504,22 +5452,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122818770</v>
+        <v>122818247</v>
       </c>
       <c r="B43" t="n">
-        <v>91235</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5532,34 +5480,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528718</v>
+        <v>528605</v>
       </c>
       <c r="R43" t="n">
-        <v>6998641</v>
+        <v>6998454</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5602,6 +5550,31 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5618,10 +5591,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122818204</v>
+        <v>122819397</v>
       </c>
       <c r="B44" t="n">
-        <v>79847</v>
+        <v>57494</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5634,37 +5607,46 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528649</v>
+        <v>528826</v>
       </c>
       <c r="R44" t="n">
-        <v>6998490</v>
+        <v>6998595</v>
       </c>
       <c r="S44" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5691,24 +5673,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>10:09</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>10:09</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På innerbark på gammal björkhögstubbe i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5723,22 +5690,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122816987</v>
+        <v>122818174</v>
       </c>
       <c r="B45" t="n">
-        <v>79384</v>
+        <v>57478</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5751,37 +5718,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528755</v>
+        <v>528625</v>
       </c>
       <c r="R45" t="n">
-        <v>6998446</v>
+        <v>6998500</v>
       </c>
       <c r="S45" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5808,24 +5780,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>09:04</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>09:04</t>
-        </is>
-      </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På bränd jöttetallstubbe</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5840,19 +5802,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122818654</v>
+        <v>122817554</v>
       </c>
       <c r="B46" t="n">
         <v>57478</v>
@@ -5893,14 +5855,14 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528711</v>
+        <v>528648</v>
       </c>
       <c r="R46" t="n">
-        <v>6998632</v>
+        <v>6998359</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5964,10 +5926,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122817645</v>
+        <v>122816988</v>
       </c>
       <c r="B47" t="n">
-        <v>57499</v>
+        <v>57478</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5976,35 +5938,36 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100110</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6013,13 +5976,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528643</v>
+        <v>528756</v>
       </c>
       <c r="R47" t="n">
-        <v>6998354</v>
+        <v>6998450</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6046,19 +6009,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>09:45</t>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en tall.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6069,26 +6027,51 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122819448</v>
+        <v>122818036</v>
       </c>
       <c r="B48" t="n">
-        <v>79876</v>
+        <v>79751</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6101,42 +6084,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528696</v>
+        <v>528686</v>
       </c>
       <c r="R48" t="n">
-        <v>6998688</v>
+        <v>6998471</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6163,14 +6141,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Frodiga bålar.</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6181,41 +6169,26 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122818321</v>
+        <v>122817037</v>
       </c>
       <c r="B49" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6228,37 +6201,47 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528805</v>
+        <v>528752</v>
       </c>
       <c r="R49" t="n">
-        <v>6998631</v>
+        <v>6998456</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6285,24 +6268,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6313,26 +6286,51 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122818036</v>
+        <v>122817142</v>
       </c>
       <c r="B50" t="n">
-        <v>79751</v>
+        <v>57478</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6341,41 +6339,46 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528686</v>
+        <v>528699</v>
       </c>
       <c r="R50" t="n">
-        <v>6998471</v>
+        <v>6998430</v>
       </c>
       <c r="S50" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6402,24 +6405,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6434,22 +6427,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122819379</v>
+        <v>122817758</v>
       </c>
       <c r="B51" t="n">
-        <v>98357</v>
+        <v>77699</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6458,50 +6451,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528802</v>
+        <v>528610</v>
       </c>
       <c r="R51" t="n">
-        <v>6998594</v>
+        <v>6998403</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6530,7 +6514,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6540,12 +6524,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6560,22 +6544,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122817278</v>
+        <v>122816979</v>
       </c>
       <c r="B52" t="n">
-        <v>57478</v>
+        <v>78503</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6588,42 +6572,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>528671</v>
+        <v>528730</v>
       </c>
       <c r="R52" t="n">
-        <v>6998337</v>
+        <v>6998447</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6650,14 +6629,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På kolad ved</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6672,22 +6661,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122818126</v>
+        <v>122817601</v>
       </c>
       <c r="B53" t="n">
-        <v>79847</v>
+        <v>90972</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6700,21 +6689,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6724,10 +6713,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>528624</v>
+        <v>528645</v>
       </c>
       <c r="R53" t="n">
-        <v>6998489</v>
+        <v>6998384</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6786,10 +6775,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122817601</v>
+        <v>122818387</v>
       </c>
       <c r="B54" t="n">
-        <v>90964</v>
+        <v>78766</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6802,21 +6791,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6826,10 +6815,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>528645</v>
+        <v>528619</v>
       </c>
       <c r="R54" t="n">
-        <v>6998384</v>
+        <v>6998495</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6872,6 +6861,31 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6888,10 +6902,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122818613</v>
+        <v>122818675</v>
       </c>
       <c r="B55" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6900,40 +6914,35 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6942,13 +6951,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>528723</v>
+        <v>528722</v>
       </c>
       <c r="R55" t="n">
-        <v>6998554</v>
+        <v>6998660</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6977,7 +6986,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6987,12 +6996,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:28</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7007,22 +7011,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122819397</v>
+        <v>122818713</v>
       </c>
       <c r="B56" t="n">
-        <v>57494</v>
+        <v>90952</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7035,43 +7039,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>528826</v>
+        <v>528718</v>
       </c>
       <c r="R56" t="n">
-        <v>6998595</v>
+        <v>6998641</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7130,7 +7125,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122818247</v>
+        <v>122819024</v>
       </c>
       <c r="B57" t="n">
         <v>78766</v>
@@ -7166,17 +7161,17 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>528605</v>
+        <v>528636</v>
       </c>
       <c r="R57" t="n">
-        <v>6998454</v>
+        <v>6998609</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7224,22 +7219,22 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7257,7 +7252,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122818165</v>
+        <v>122817657</v>
       </c>
       <c r="B58" t="n">
         <v>78766</v>
@@ -7297,13 +7292,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>528594</v>
+        <v>528650</v>
       </c>
       <c r="R58" t="n">
-        <v>6998419</v>
+        <v>6998397</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7335,6 +7330,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7346,27 +7346,27 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7501,10 +7501,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122818675</v>
+        <v>122818035</v>
       </c>
       <c r="B60" t="n">
-        <v>78766</v>
+        <v>79807</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7513,50 +7513,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>528722</v>
+        <v>528677</v>
       </c>
       <c r="R60" t="n">
-        <v>6998660</v>
+        <v>6998487</v>
       </c>
       <c r="S60" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7585,7 +7576,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7595,7 +7586,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7622,10 +7618,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122817554</v>
+        <v>122817517</v>
       </c>
       <c r="B61" t="n">
-        <v>57478</v>
+        <v>78411</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7638,39 +7634,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>528648</v>
+        <v>528643</v>
       </c>
       <c r="R61" t="n">
-        <v>6998359</v>
+        <v>6998354</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7700,14 +7691,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På ved på gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7722,22 +7723,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122817546</v>
+        <v>122819033</v>
       </c>
       <c r="B62" t="n">
-        <v>74863</v>
+        <v>74675</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7746,25 +7747,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6440</v>
+        <v>6428</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7774,13 +7775,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>528628</v>
+        <v>528798</v>
       </c>
       <c r="R62" t="n">
-        <v>6998367</v>
+        <v>6998603</v>
       </c>
       <c r="S62" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7809,7 +7810,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7819,12 +7820,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal sälg i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7839,22 +7840,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122818955</v>
+        <v>122818966</v>
       </c>
       <c r="B63" t="n">
-        <v>74786</v>
+        <v>79847</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7867,21 +7868,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1460</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7899,10 +7900,10 @@
         <v>528791</v>
       </c>
       <c r="R63" t="n">
-        <v>6998633</v>
+        <v>6998599</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7946,7 +7947,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På bark på stam av levande gammal sälg (25 cm dbh) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7957,23 +7958,38 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122818681</v>
+        <v>122818165</v>
       </c>
       <c r="B64" t="n">
         <v>78766</v>
@@ -8009,17 +8025,17 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>528686</v>
+        <v>528594</v>
       </c>
       <c r="R64" t="n">
-        <v>6998618</v>
+        <v>6998419</v>
       </c>
       <c r="S64" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8062,27 +8078,27 @@
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8100,10 +8116,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122818032</v>
+        <v>122818321</v>
       </c>
       <c r="B65" t="n">
-        <v>79876</v>
+        <v>74863</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8112,25 +8128,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8140,10 +8156,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>528631</v>
+        <v>528805</v>
       </c>
       <c r="R65" t="n">
-        <v>6998469</v>
+        <v>6998631</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8173,9 +8189,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8190,22 +8221,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122817037</v>
+        <v>122818040</v>
       </c>
       <c r="B66" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8218,47 +8249,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>528752</v>
+        <v>528621</v>
       </c>
       <c r="R66" t="n">
-        <v>6998456</v>
+        <v>6998383</v>
       </c>
       <c r="S66" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8290,11 +8311,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -8311,22 +8327,22 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8344,10 +8360,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122818168</v>
+        <v>122818770</v>
       </c>
       <c r="B67" t="n">
-        <v>79807</v>
+        <v>91243</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8356,38 +8372,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229497</v>
+        <v>658</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>528669</v>
+        <v>528718</v>
       </c>
       <c r="R67" t="n">
-        <v>6998500</v>
+        <v>6998641</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8417,26 +8433,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På bark på stam av död gammal asp (40 cm dbh) i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8445,41 +8446,26 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122818328</v>
+        <v>122818536</v>
       </c>
       <c r="B68" t="n">
-        <v>77699</v>
+        <v>57478</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8492,37 +8478,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>528800</v>
+        <v>528665</v>
       </c>
       <c r="R68" t="n">
-        <v>6998633</v>
+        <v>6998574</v>
       </c>
       <c r="S68" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8549,24 +8540,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8581,22 +8562,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122818025</v>
+        <v>122818328</v>
       </c>
       <c r="B69" t="n">
-        <v>79848</v>
+        <v>77699</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8609,21 +8590,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8633,13 +8614,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>528631</v>
+        <v>528800</v>
       </c>
       <c r="R69" t="n">
-        <v>6998469</v>
+        <v>6998633</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8666,9 +8647,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8683,22 +8679,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122817517</v>
+        <v>122818323</v>
       </c>
       <c r="B70" t="n">
-        <v>78411</v>
+        <v>79847</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8711,21 +8707,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8735,13 +8731,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>528643</v>
+        <v>528667</v>
       </c>
       <c r="R70" t="n">
-        <v>6998354</v>
+        <v>6998534</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8770,7 +8766,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8780,12 +8776,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På ved på gammal tallstubbe</t>
+          <t>Rikligt på bark på stam av levande gammal sälg i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8812,7 +8808,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122817219</v>
+        <v>122818573</v>
       </c>
       <c r="B71" t="n">
         <v>78766</v>
@@ -8848,17 +8844,17 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>528684</v>
+        <v>528630</v>
       </c>
       <c r="R71" t="n">
-        <v>6998437</v>
+        <v>6998539</v>
       </c>
       <c r="S71" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8888,11 +8884,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8944,10 +8935,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122818503</v>
+        <v>122817645</v>
       </c>
       <c r="B72" t="n">
-        <v>57478</v>
+        <v>57499</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8956,46 +8947,50 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>100110</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>528652</v>
+        <v>528643</v>
       </c>
       <c r="R72" t="n">
-        <v>6998555</v>
+        <v>6998354</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9022,14 +9017,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9044,12 +9044,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -9192,7 +9192,7 @@
         <v>122818930</v>
       </c>
       <c r="B74" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>

--- a/artfynd/A 55431-2024 artfynd.xlsx
+++ b/artfynd/A 55431-2024 artfynd.xlsx
@@ -7501,10 +7501,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122818035</v>
+        <v>122817517</v>
       </c>
       <c r="B60" t="n">
-        <v>79807</v>
+        <v>78411</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7513,25 +7513,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229497</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7541,10 +7541,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>528677</v>
+        <v>528643</v>
       </c>
       <c r="R60" t="n">
-        <v>6998487</v>
+        <v>6998354</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7576,7 +7576,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7586,12 +7586,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>På ved på gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7606,22 +7606,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122817517</v>
+        <v>122819033</v>
       </c>
       <c r="B61" t="n">
-        <v>78411</v>
+        <v>74675</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7630,25 +7630,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>353</v>
+        <v>6428</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7658,13 +7658,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>528643</v>
+        <v>528798</v>
       </c>
       <c r="R61" t="n">
-        <v>6998354</v>
+        <v>6998603</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7703,12 +7703,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På ved på gammal tallstubbe</t>
+          <t>På bark på stam av levande gammal sälg i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7735,10 +7735,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122819033</v>
+        <v>122818966</v>
       </c>
       <c r="B62" t="n">
-        <v>74675</v>
+        <v>79847</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7747,41 +7747,46 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6428</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>528798</v>
+        <v>528791</v>
       </c>
       <c r="R62" t="n">
-        <v>6998603</v>
+        <v>6998599</v>
       </c>
       <c r="S62" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7810,7 +7815,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7820,12 +7825,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal barrblandskog</t>
+          <t>På bark på stam av levande gammal sälg (25 cm dbh) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7836,6 +7841,21 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7852,10 +7872,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122818966</v>
+        <v>122818035</v>
       </c>
       <c r="B63" t="n">
-        <v>79847</v>
+        <v>79807</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7864,46 +7884,41 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>528791</v>
+        <v>528677</v>
       </c>
       <c r="R63" t="n">
-        <v>6998599</v>
+        <v>6998487</v>
       </c>
       <c r="S63" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7932,7 +7947,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7942,12 +7957,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg (25 cm dbh) i gammal barrblandskog</t>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7958,41 +7973,26 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122818165</v>
+        <v>122818321</v>
       </c>
       <c r="B64" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8005,21 +8005,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8029,13 +8029,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>528594</v>
+        <v>528805</v>
       </c>
       <c r="R64" t="n">
-        <v>6998419</v>
+        <v>6998631</v>
       </c>
       <c r="S64" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8062,11 +8062,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8075,51 +8090,26 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122818321</v>
+        <v>122818165</v>
       </c>
       <c r="B65" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8132,21 +8122,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8156,13 +8146,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>528805</v>
+        <v>528594</v>
       </c>
       <c r="R65" t="n">
-        <v>6998631</v>
+        <v>6998419</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8189,26 +8179,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -8217,16 +8192,41 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>

--- a/artfynd/A 55431-2024 artfynd.xlsx
+++ b/artfynd/A 55431-2024 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122818026</v>
+        <v>122818966</v>
       </c>
       <c r="B3" t="n">
         <v>79847</v>
@@ -820,19 +820,24 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528631</v>
+        <v>528791</v>
       </c>
       <c r="R3" t="n">
-        <v>6998469</v>
+        <v>6998599</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,11 +864,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal sälg (25 cm dbh) i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -872,26 +892,41 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122818032</v>
+        <v>122819118</v>
       </c>
       <c r="B4" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,41 +935,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528631</v>
+        <v>528690</v>
       </c>
       <c r="R4" t="n">
-        <v>6998469</v>
+        <v>6998652</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -966,6 +1001,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -974,6 +1014,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -990,10 +1055,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122819448</v>
+        <v>122818036</v>
       </c>
       <c r="B5" t="n">
-        <v>79876</v>
+        <v>79751</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,42 +1071,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528696</v>
+        <v>528686</v>
       </c>
       <c r="R5" t="n">
-        <v>6998688</v>
+        <v>6998471</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1068,14 +1128,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Frodiga bålar.</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,38 +1156,23 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122817278</v>
+        <v>122818503</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1158,14 +1213,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528671</v>
+        <v>528652</v>
       </c>
       <c r="R6" t="n">
-        <v>6998337</v>
+        <v>6998555</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,7 +1257,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,10 +1284,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122818681</v>
+        <v>122818125</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,37 +1300,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528686</v>
+        <v>528687</v>
       </c>
       <c r="R7" t="n">
-        <v>6998618</v>
+        <v>6998489</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1302,11 +1357,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal tallstubbe i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1315,51 +1385,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122818654</v>
+        <v>122817186</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>57428</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,20 +1413,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1389,22 +1434,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528711</v>
+        <v>528689</v>
       </c>
       <c r="R8" t="n">
-        <v>6998632</v>
+        <v>6998416</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,11 +1491,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,10 +1517,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122818613</v>
+        <v>122819058</v>
       </c>
       <c r="B9" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,52 +1529,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528723</v>
+        <v>528654</v>
       </c>
       <c r="R9" t="n">
-        <v>6998554</v>
+        <v>6998628</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1555,26 +1590,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På marken i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1583,26 +1603,51 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122817289</v>
+        <v>122817937</v>
       </c>
       <c r="B10" t="n">
-        <v>79145</v>
+        <v>90963</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,25 +1656,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>257107</v>
+        <v>1205</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blek lundlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bacidia rosellizans</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>S.Ekman</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1639,13 +1684,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528632</v>
+        <v>528686</v>
       </c>
       <c r="R10" t="n">
-        <v>6998403</v>
+        <v>6998446</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1674,7 +1719,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1684,12 +1729,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>På död asp</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1704,22 +1749,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122818955</v>
+        <v>122817037</v>
       </c>
       <c r="B11" t="n">
-        <v>74786</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1732,27 +1777,32 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1460</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1761,13 +1811,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528791</v>
+        <v>528752</v>
       </c>
       <c r="R11" t="n">
-        <v>6998633</v>
+        <v>6998456</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1794,24 +1844,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,26 +1862,51 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122817273</v>
+        <v>122817339</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1854,43 +1919,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528623</v>
+        <v>528649</v>
       </c>
       <c r="R12" t="n">
-        <v>6998311</v>
+        <v>6998383</v>
       </c>
       <c r="S12" t="n">
         <v>11</v>
@@ -1922,7 +1978,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1932,12 +1988,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1964,10 +2020,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122817054</v>
+        <v>122818247</v>
       </c>
       <c r="B13" t="n">
-        <v>79751</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1976,25 +2032,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2004,10 +2060,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528755</v>
+        <v>528605</v>
       </c>
       <c r="R13" t="n">
-        <v>6998448</v>
+        <v>6998454</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2037,26 +2093,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>09:08</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>09:08</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2065,26 +2106,51 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122816987</v>
+        <v>122817110</v>
       </c>
       <c r="B14" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2097,21 +2163,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2121,13 +2187,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528755</v>
+        <v>528711</v>
       </c>
       <c r="R14" t="n">
-        <v>6998446</v>
+        <v>6998430</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2156,7 +2222,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2166,12 +2232,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På bränd jöttetallstubbe</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2198,10 +2264,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122817339</v>
+        <v>122818759</v>
       </c>
       <c r="B15" t="n">
-        <v>79384</v>
+        <v>79847</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2214,21 +2280,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2238,13 +2304,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528649</v>
+        <v>528778</v>
       </c>
       <c r="R15" t="n">
-        <v>6998383</v>
+        <v>6998602</v>
       </c>
       <c r="S15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2273,7 +2339,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2283,12 +2349,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gammal tallstubbe</t>
+          <t>På gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2303,22 +2369,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122817112</v>
+        <v>122819397</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2331,46 +2397,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528711</v>
+        <v>528826</v>
       </c>
       <c r="R16" t="n">
-        <v>6998411</v>
+        <v>6998595</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2397,24 +2463,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2429,19 +2480,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122817413</v>
+        <v>122817325</v>
       </c>
       <c r="B17" t="n">
         <v>57478</v>
@@ -2486,10 +2537,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528612</v>
+        <v>528640</v>
       </c>
       <c r="R17" t="n">
-        <v>6998323</v>
+        <v>6998336</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2526,7 +2577,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2553,10 +2604,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122817714</v>
+        <v>122818536</v>
       </c>
       <c r="B18" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2569,37 +2620,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528625</v>
+        <v>528665</v>
       </c>
       <c r="R18" t="n">
-        <v>6998424</v>
+        <v>6998574</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2626,24 +2682,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2658,22 +2704,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122817186</v>
+        <v>122818025</v>
       </c>
       <c r="B19" t="n">
-        <v>57428</v>
+        <v>79848</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2682,52 +2728,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102621</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528689</v>
+        <v>528631</v>
       </c>
       <c r="R19" t="n">
-        <v>6998416</v>
+        <v>6998469</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2907,10 +2939,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122818514</v>
+        <v>122818126</v>
       </c>
       <c r="B21" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2923,34 +2955,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528635</v>
+        <v>528624</v>
       </c>
       <c r="R21" t="n">
-        <v>6998546</v>
+        <v>6998489</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3009,10 +3041,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122818125</v>
+        <v>122818534</v>
       </c>
       <c r="B22" t="n">
-        <v>78503</v>
+        <v>79813</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3021,41 +3053,46 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>229748</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528687</v>
+        <v>528727</v>
       </c>
       <c r="R22" t="n">
-        <v>6998489</v>
+        <v>6998595</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3084,7 +3121,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3094,12 +3131,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal tallstubbe i gammal barrblandskog</t>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3114,22 +3151,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122818126</v>
+        <v>122818387</v>
       </c>
       <c r="B23" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3142,21 +3179,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3166,10 +3203,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528624</v>
+        <v>528619</v>
       </c>
       <c r="R23" t="n">
-        <v>6998489</v>
+        <v>6998495</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3212,6 +3249,31 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3228,10 +3290,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122817869</v>
+        <v>122817546</v>
       </c>
       <c r="B24" t="n">
-        <v>57499</v>
+        <v>74863</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3240,50 +3302,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100110</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528645</v>
+        <v>528628</v>
       </c>
       <c r="R24" t="n">
-        <v>6998384</v>
+        <v>6998367</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3310,9 +3363,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3327,22 +3395,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122818534</v>
+        <v>122818321</v>
       </c>
       <c r="B25" t="n">
-        <v>79813</v>
+        <v>74863</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3351,46 +3419,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229748</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528727</v>
+        <v>528805</v>
       </c>
       <c r="R25" t="n">
-        <v>6998595</v>
+        <v>6998631</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3419,7 +3482,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3429,12 +3492,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3461,10 +3524,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122818503</v>
+        <v>122818864</v>
       </c>
       <c r="B26" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3477,42 +3540,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528652</v>
+        <v>528732</v>
       </c>
       <c r="R26" t="n">
-        <v>6998555</v>
+        <v>6998659</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3539,14 +3597,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3561,22 +3629,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122817325</v>
+        <v>122819033</v>
       </c>
       <c r="B27" t="n">
-        <v>57478</v>
+        <v>74675</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3585,46 +3653,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6428</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528640</v>
+        <v>528798</v>
       </c>
       <c r="R27" t="n">
-        <v>6998336</v>
+        <v>6998603</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3651,14 +3714,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På bark på stam av levande gammal sälg i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3673,22 +3746,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122819379</v>
+        <v>122818040</v>
       </c>
       <c r="B28" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3697,50 +3770,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528802</v>
+        <v>528621</v>
       </c>
       <c r="R28" t="n">
-        <v>6998594</v>
+        <v>6998383</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3767,26 +3831,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På marken i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3795,26 +3844,51 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122818025</v>
+        <v>122817142</v>
       </c>
       <c r="B29" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3827,34 +3901,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528631</v>
+        <v>528699</v>
       </c>
       <c r="R29" t="n">
-        <v>6998469</v>
+        <v>6998430</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3887,6 +3966,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3913,10 +3997,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122818204</v>
+        <v>122817554</v>
       </c>
       <c r="B30" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3929,37 +4013,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528649</v>
+        <v>528648</v>
       </c>
       <c r="R30" t="n">
-        <v>6998490</v>
+        <v>6998359</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3986,24 +4075,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>10:09</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>10:09</t>
-        </is>
-      </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På innerbark på gammal björkhögstubbe i gammal barrblandskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4018,19 +4097,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122818653</v>
+        <v>122818204</v>
       </c>
       <c r="B31" t="n">
         <v>79847</v>
@@ -4070,10 +4149,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528732</v>
+        <v>528649</v>
       </c>
       <c r="R31" t="n">
-        <v>6998541</v>
+        <v>6998490</v>
       </c>
       <c r="S31" t="n">
         <v>8</v>
@@ -4105,7 +4184,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4115,12 +4194,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På asplåga i gammal barrblandskog</t>
+          <t>På innerbark på gammal björkhögstubbe i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4147,10 +4226,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122817219</v>
+        <v>122816988</v>
       </c>
       <c r="B32" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4163,34 +4242,44 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528684</v>
+        <v>528756</v>
       </c>
       <c r="R32" t="n">
-        <v>6998437</v>
+        <v>6998450</v>
       </c>
       <c r="S32" t="n">
         <v>8</v>
@@ -4227,7 +4316,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack på en tall.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4246,22 +4335,22 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4279,10 +4368,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122817942</v>
+        <v>122817273</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4295,27 +4384,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4324,13 +4417,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528655</v>
+        <v>528623</v>
       </c>
       <c r="R33" t="n">
-        <v>6998433</v>
+        <v>6998311</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4357,14 +4450,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4379,22 +4482,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122817550</v>
+        <v>122818675</v>
       </c>
       <c r="B34" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4407,27 +4510,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4436,13 +4543,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528648</v>
+        <v>528722</v>
       </c>
       <c r="R34" t="n">
-        <v>6998358</v>
+        <v>6998660</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4469,14 +4576,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4491,22 +4603,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122818864</v>
+        <v>122817112</v>
       </c>
       <c r="B35" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4519,37 +4631,46 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528732</v>
+        <v>528711</v>
       </c>
       <c r="R35" t="n">
-        <v>6998659</v>
+        <v>6998411</v>
       </c>
       <c r="S35" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4578,7 +4699,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4588,12 +4709,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4620,10 +4741,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122817546</v>
+        <v>122818653</v>
       </c>
       <c r="B36" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4636,21 +4757,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4660,10 +4781,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528628</v>
+        <v>528732</v>
       </c>
       <c r="R36" t="n">
-        <v>6998367</v>
+        <v>6998541</v>
       </c>
       <c r="S36" t="n">
         <v>8</v>
@@ -4695,7 +4816,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4705,12 +4826,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På asplåga i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4725,22 +4846,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122819058</v>
+        <v>122818613</v>
       </c>
       <c r="B37" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4749,38 +4870,52 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528654</v>
+        <v>528723</v>
       </c>
       <c r="R37" t="n">
-        <v>6998628</v>
+        <v>6998554</v>
       </c>
       <c r="S37" t="n">
         <v>9</v>
@@ -4810,11 +4945,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På marken i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4823,51 +4973,26 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122818759</v>
+        <v>122816987</v>
       </c>
       <c r="B38" t="n">
-        <v>79847</v>
+        <v>79384</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4880,21 +5005,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4904,13 +5029,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528778</v>
+        <v>528755</v>
       </c>
       <c r="R38" t="n">
-        <v>6998602</v>
+        <v>6998446</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4939,7 +5064,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4949,12 +5074,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På gammal asp i gammal barrblandskog</t>
+          <t>På bränd jöttetallstubbe</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4981,10 +5106,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122819118</v>
+        <v>122818035</v>
       </c>
       <c r="B39" t="n">
-        <v>78766</v>
+        <v>79807</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4993,41 +5118,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528690</v>
+        <v>528677</v>
       </c>
       <c r="R39" t="n">
-        <v>6998652</v>
+        <v>6998487</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5054,14 +5179,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5072,51 +5207,26 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122818168</v>
+        <v>122818770</v>
       </c>
       <c r="B40" t="n">
-        <v>79807</v>
+        <v>91243</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5125,38 +5235,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229497</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528669</v>
+        <v>528718</v>
       </c>
       <c r="R40" t="n">
-        <v>6998500</v>
+        <v>6998641</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5186,26 +5296,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På bark på stam av död gammal asp (40 cm dbh) i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5214,41 +5309,26 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122817937</v>
+        <v>122818026</v>
       </c>
       <c r="B41" t="n">
-        <v>90963</v>
+        <v>79847</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5257,25 +5337,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5285,13 +5365,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528686</v>
+        <v>528631</v>
       </c>
       <c r="R41" t="n">
-        <v>6998446</v>
+        <v>6998469</v>
       </c>
       <c r="S41" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5318,24 +5398,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På död asp</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5350,22 +5415,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122818122</v>
+        <v>122819448</v>
       </c>
       <c r="B42" t="n">
-        <v>79848</v>
+        <v>79876</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5374,38 +5439,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528631</v>
+        <v>528696</v>
       </c>
       <c r="R42" t="n">
-        <v>6998473</v>
+        <v>6998688</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5440,6 +5510,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Frodiga bålar.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5448,6 +5523,21 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Stone/rock on land</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5464,10 +5554,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122818247</v>
+        <v>122818122</v>
       </c>
       <c r="B43" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5480,21 +5570,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5504,10 +5594,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528605</v>
+        <v>528631</v>
       </c>
       <c r="R43" t="n">
-        <v>6998454</v>
+        <v>6998473</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5550,31 +5640,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5591,10 +5656,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122819397</v>
+        <v>122817413</v>
       </c>
       <c r="B44" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5607,16 +5672,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5624,26 +5689,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528826</v>
+        <v>528612</v>
       </c>
       <c r="R44" t="n">
-        <v>6998595</v>
+        <v>6998323</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5676,6 +5737,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5702,10 +5768,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122818174</v>
+        <v>122819379</v>
       </c>
       <c r="B45" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5714,31 +5780,35 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5747,13 +5817,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528625</v>
+        <v>528802</v>
       </c>
       <c r="R45" t="n">
-        <v>6998500</v>
+        <v>6998594</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5780,14 +5850,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5802,22 +5882,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122817554</v>
+        <v>122818328</v>
       </c>
       <c r="B46" t="n">
-        <v>57478</v>
+        <v>77699</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5830,42 +5910,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528648</v>
+        <v>528800</v>
       </c>
       <c r="R46" t="n">
-        <v>6998359</v>
+        <v>6998633</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5892,14 +5967,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5914,22 +5999,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122816988</v>
+        <v>122817289</v>
       </c>
       <c r="B47" t="n">
-        <v>57478</v>
+        <v>79145</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5942,44 +6027,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>257107</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blek lundlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bacidia rosellizans</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>S.Ekman</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528756</v>
+        <v>528632</v>
       </c>
       <c r="R47" t="n">
-        <v>6998450</v>
+        <v>6998403</v>
       </c>
       <c r="S47" t="n">
         <v>8</v>
@@ -6009,14 +6084,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en tall.</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6027,51 +6112,26 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122818036</v>
+        <v>122818514</v>
       </c>
       <c r="B48" t="n">
-        <v>79751</v>
+        <v>74863</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6080,41 +6140,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528686</v>
+        <v>528635</v>
       </c>
       <c r="R48" t="n">
-        <v>6998471</v>
+        <v>6998546</v>
       </c>
       <c r="S48" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6141,24 +6201,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6173,22 +6218,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122817037</v>
+        <v>122817714</v>
       </c>
       <c r="B49" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6201,44 +6246,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528752</v>
+        <v>528625</v>
       </c>
       <c r="R49" t="n">
-        <v>6998456</v>
+        <v>6998424</v>
       </c>
       <c r="S49" t="n">
         <v>9</v>
@@ -6268,14 +6303,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall.</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6286,51 +6331,26 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122817142</v>
+        <v>122818573</v>
       </c>
       <c r="B50" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6343,42 +6363,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528699</v>
+        <v>528630</v>
       </c>
       <c r="R50" t="n">
-        <v>6998430</v>
+        <v>6998539</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6410,11 +6425,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6423,6 +6433,31 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6439,10 +6474,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122817758</v>
+        <v>122818165</v>
       </c>
       <c r="B51" t="n">
-        <v>77699</v>
+        <v>78766</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6455,21 +6490,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6479,13 +6514,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528610</v>
+        <v>528594</v>
       </c>
       <c r="R51" t="n">
-        <v>6998403</v>
+        <v>6998419</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6512,26 +6547,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6540,26 +6560,51 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122816979</v>
+        <v>122818323</v>
       </c>
       <c r="B52" t="n">
-        <v>78503</v>
+        <v>79847</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6572,21 +6617,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6596,13 +6641,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>528730</v>
+        <v>528667</v>
       </c>
       <c r="R52" t="n">
-        <v>6998447</v>
+        <v>6998534</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6631,7 +6676,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6641,12 +6686,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På kolad ved</t>
+          <t>Rikligt på bark på stam av levande gammal sälg i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6661,22 +6706,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122817601</v>
+        <v>122818032</v>
       </c>
       <c r="B53" t="n">
-        <v>90972</v>
+        <v>79876</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6685,25 +6730,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5442</v>
+        <v>6462</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6713,10 +6758,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>528645</v>
+        <v>528631</v>
       </c>
       <c r="R53" t="n">
-        <v>6998384</v>
+        <v>6998469</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6775,10 +6820,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122818387</v>
+        <v>122817645</v>
       </c>
       <c r="B54" t="n">
-        <v>78766</v>
+        <v>57499</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6787,41 +6832,50 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100110</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>528619</v>
+        <v>528643</v>
       </c>
       <c r="R54" t="n">
-        <v>6998495</v>
+        <v>6998354</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6848,11 +6902,21 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6861,48 +6925,23 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122818675</v>
+        <v>122818681</v>
       </c>
       <c r="B55" t="n">
         <v>78766</v>
@@ -6935,26 +6974,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>528722</v>
+        <v>528686</v>
       </c>
       <c r="R55" t="n">
-        <v>6998660</v>
+        <v>6998618</v>
       </c>
       <c r="S55" t="n">
         <v>12</v>
@@ -6984,21 +7014,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>10:31</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>10:31</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -7007,26 +7027,51 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122818713</v>
+        <v>122817657</v>
       </c>
       <c r="B56" t="n">
-        <v>90952</v>
+        <v>78766</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7039,37 +7084,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>528718</v>
+        <v>528650</v>
       </c>
       <c r="R56" t="n">
-        <v>6998641</v>
+        <v>6998397</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7101,6 +7146,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7109,6 +7159,31 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7125,10 +7200,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122819024</v>
+        <v>122818168</v>
       </c>
       <c r="B57" t="n">
-        <v>78766</v>
+        <v>79807</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7137,41 +7212,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>528636</v>
+        <v>528669</v>
       </c>
       <c r="R57" t="n">
-        <v>6998609</v>
+        <v>6998500</v>
       </c>
       <c r="S57" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7198,11 +7273,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På bark på stam av död gammal asp (40 cm dbh) i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7212,50 +7302,40 @@
       <c r="AG57" t="b">
         <v>0</v>
       </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Död gren</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Dead branch  # Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122817657</v>
+        <v>122817517</v>
       </c>
       <c r="B58" t="n">
-        <v>78766</v>
+        <v>78411</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7268,21 +7348,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7292,13 +7372,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>528650</v>
+        <v>528643</v>
       </c>
       <c r="R58" t="n">
-        <v>6998397</v>
+        <v>6998354</v>
       </c>
       <c r="S58" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7325,14 +7405,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På ved på gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7343,51 +7433,26 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122817110</v>
+        <v>122817942</v>
       </c>
       <c r="B59" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7400,37 +7465,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>528711</v>
+        <v>528655</v>
       </c>
       <c r="R59" t="n">
-        <v>6998430</v>
+        <v>6998433</v>
       </c>
       <c r="S59" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7457,24 +7527,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>09:11</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>09:11</t>
-        </is>
-      </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7489,22 +7549,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122817517</v>
+        <v>122816979</v>
       </c>
       <c r="B60" t="n">
-        <v>78411</v>
+        <v>78503</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7517,21 +7577,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7541,13 +7601,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>528643</v>
+        <v>528730</v>
       </c>
       <c r="R60" t="n">
-        <v>6998354</v>
+        <v>6998447</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7576,7 +7636,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7586,12 +7646,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På ved på gammal tallstubbe</t>
+          <t>På kolad ved</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7606,22 +7666,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122819033</v>
+        <v>122818713</v>
       </c>
       <c r="B61" t="n">
-        <v>74675</v>
+        <v>90952</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7630,41 +7690,41 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6428</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>528798</v>
+        <v>528718</v>
       </c>
       <c r="R61" t="n">
-        <v>6998603</v>
+        <v>6998641</v>
       </c>
       <c r="S61" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7691,24 +7751,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal sälg i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7723,22 +7768,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122818966</v>
+        <v>122817758</v>
       </c>
       <c r="B62" t="n">
-        <v>79847</v>
+        <v>77699</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7751,42 +7796,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>528791</v>
+        <v>528610</v>
       </c>
       <c r="R62" t="n">
-        <v>6998599</v>
+        <v>6998403</v>
       </c>
       <c r="S62" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7815,7 +7855,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7825,12 +7865,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg (25 cm dbh) i gammal barrblandskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7841,41 +7881,26 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122818035</v>
+        <v>122817278</v>
       </c>
       <c r="B63" t="n">
-        <v>79807</v>
+        <v>57478</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7884,38 +7909,43 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>528677</v>
+        <v>528671</v>
       </c>
       <c r="R63" t="n">
-        <v>6998487</v>
+        <v>6998337</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7945,24 +7975,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7977,22 +7997,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122818321</v>
+        <v>122818174</v>
       </c>
       <c r="B64" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8005,34 +8025,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>528805</v>
+        <v>528625</v>
       </c>
       <c r="R64" t="n">
-        <v>6998631</v>
+        <v>6998500</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8062,24 +8087,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8094,19 +8109,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122818165</v>
+        <v>122817219</v>
       </c>
       <c r="B65" t="n">
         <v>78766</v>
@@ -8146,10 +8161,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>528594</v>
+        <v>528684</v>
       </c>
       <c r="R65" t="n">
-        <v>6998419</v>
+        <v>6998437</v>
       </c>
       <c r="S65" t="n">
         <v>8</v>
@@ -8184,6 +8199,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -8195,27 +8215,27 @@
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8233,10 +8253,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122818040</v>
+        <v>122817054</v>
       </c>
       <c r="B66" t="n">
-        <v>78766</v>
+        <v>79751</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8245,25 +8265,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8273,13 +8293,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>528621</v>
+        <v>528755</v>
       </c>
       <c r="R66" t="n">
-        <v>6998383</v>
+        <v>6998448</v>
       </c>
       <c r="S66" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8306,11 +8326,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -8319,51 +8354,26 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122818770</v>
+        <v>122819024</v>
       </c>
       <c r="B67" t="n">
-        <v>91243</v>
+        <v>78766</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8376,21 +8386,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8400,13 +8410,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>528718</v>
+        <v>528636</v>
       </c>
       <c r="R67" t="n">
-        <v>6998641</v>
+        <v>6998609</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8446,6 +8456,31 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Dead branch  # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -8462,10 +8497,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122818536</v>
+        <v>122818955</v>
       </c>
       <c r="B68" t="n">
-        <v>57478</v>
+        <v>74786</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8478,39 +8513,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>1460</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>528665</v>
+        <v>528791</v>
       </c>
       <c r="R68" t="n">
-        <v>6998574</v>
+        <v>6998633</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8540,14 +8575,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8562,22 +8607,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122818328</v>
+        <v>122818654</v>
       </c>
       <c r="B69" t="n">
-        <v>77699</v>
+        <v>57478</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8590,37 +8635,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>528800</v>
+        <v>528711</v>
       </c>
       <c r="R69" t="n">
-        <v>6998633</v>
+        <v>6998632</v>
       </c>
       <c r="S69" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8647,24 +8697,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8679,22 +8719,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122818323</v>
+        <v>122817869</v>
       </c>
       <c r="B70" t="n">
-        <v>79847</v>
+        <v>57499</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8703,41 +8743,50 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>100110</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>528667</v>
+        <v>528645</v>
       </c>
       <c r="R70" t="n">
-        <v>6998534</v>
+        <v>6998384</v>
       </c>
       <c r="S70" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8764,24 +8813,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Rikligt på bark på stam av levande gammal sälg i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8796,22 +8830,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122818573</v>
+        <v>122817550</v>
       </c>
       <c r="B71" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8824,37 +8858,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>528630</v>
+        <v>528648</v>
       </c>
       <c r="R71" t="n">
-        <v>6998539</v>
+        <v>6998358</v>
       </c>
       <c r="S71" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8886,6 +8925,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -8894,31 +8938,6 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -8935,10 +8954,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122817645</v>
+        <v>122817601</v>
       </c>
       <c r="B72" t="n">
-        <v>57499</v>
+        <v>90972</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8947,50 +8966,41 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100110</v>
+        <v>5442</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>528643</v>
+        <v>528645</v>
       </c>
       <c r="R72" t="n">
-        <v>6998354</v>
+        <v>6998384</v>
       </c>
       <c r="S72" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9017,19 +9027,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9044,12 +9044,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>

--- a/artfynd/A 55431-2024 artfynd.xlsx
+++ b/artfynd/A 55431-2024 artfynd.xlsx
@@ -1055,10 +1055,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122818036</v>
+        <v>122818503</v>
       </c>
       <c r="B5" t="n">
-        <v>79751</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1067,41 +1067,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528686</v>
+        <v>528652</v>
       </c>
       <c r="R5" t="n">
-        <v>6998471</v>
+        <v>6998555</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1128,24 +1133,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1160,22 +1155,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122818503</v>
+        <v>122818036</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>79751</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1184,46 +1179,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528652</v>
+        <v>528686</v>
       </c>
       <c r="R6" t="n">
-        <v>6998555</v>
+        <v>6998471</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1250,14 +1240,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,12 +1272,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1517,10 +1517,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122819058</v>
+        <v>122817037</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1533,34 +1533,44 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528654</v>
+        <v>528752</v>
       </c>
       <c r="R9" t="n">
-        <v>6998628</v>
+        <v>6998456</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1595,6 +1605,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1606,7 +1621,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1621,12 +1636,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1644,10 +1659,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122817937</v>
+        <v>122819058</v>
       </c>
       <c r="B10" t="n">
-        <v>90963</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1656,41 +1671,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528686</v>
+        <v>528654</v>
       </c>
       <c r="R10" t="n">
-        <v>6998446</v>
+        <v>6998628</v>
       </c>
       <c r="S10" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1717,26 +1732,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På död asp</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1745,26 +1745,51 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122817037</v>
+        <v>122817937</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>90963</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1773,51 +1798,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528752</v>
+        <v>528686</v>
       </c>
       <c r="R11" t="n">
-        <v>6998456</v>
+        <v>6998446</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1844,14 +1859,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall.</t>
+          <t>På död asp</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1862,41 +1887,16 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2716,10 +2716,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122818025</v>
+        <v>122818534</v>
       </c>
       <c r="B19" t="n">
-        <v>79848</v>
+        <v>79813</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2728,41 +2728,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>229748</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528631</v>
+        <v>528727</v>
       </c>
       <c r="R19" t="n">
-        <v>6998469</v>
+        <v>6998595</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2789,9 +2794,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2806,12 +2826,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -3041,10 +3061,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122818534</v>
+        <v>122818025</v>
       </c>
       <c r="B22" t="n">
-        <v>79813</v>
+        <v>79848</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3053,46 +3073,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229748</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528727</v>
+        <v>528631</v>
       </c>
       <c r="R22" t="n">
-        <v>6998595</v>
+        <v>6998469</v>
       </c>
       <c r="S22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3119,24 +3134,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3151,12 +3151,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -4989,10 +4989,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122816987</v>
+        <v>122818328</v>
       </c>
       <c r="B38" t="n">
-        <v>79384</v>
+        <v>77699</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5005,21 +5005,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>228579</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5029,13 +5029,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528755</v>
+        <v>528800</v>
       </c>
       <c r="R38" t="n">
-        <v>6998446</v>
+        <v>6998633</v>
       </c>
       <c r="S38" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5074,12 +5074,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På bränd jöttetallstubbe</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5094,12 +5094,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5223,10 +5223,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122818770</v>
+        <v>122819448</v>
       </c>
       <c r="B40" t="n">
-        <v>91243</v>
+        <v>79876</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5235,38 +5235,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528718</v>
+        <v>528696</v>
       </c>
       <c r="R40" t="n">
-        <v>6998641</v>
+        <v>6998688</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5301,6 +5306,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Frodiga bålar.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5309,6 +5319,21 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Stone/rock on land</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5325,10 +5350,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122818026</v>
+        <v>122816987</v>
       </c>
       <c r="B41" t="n">
-        <v>79847</v>
+        <v>79384</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5341,21 +5366,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5365,13 +5390,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528631</v>
+        <v>528755</v>
       </c>
       <c r="R41" t="n">
-        <v>6998469</v>
+        <v>6998446</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5398,9 +5423,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På bränd jöttetallstubbe</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5415,22 +5455,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122819448</v>
+        <v>122818770</v>
       </c>
       <c r="B42" t="n">
-        <v>79876</v>
+        <v>91243</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5439,43 +5479,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528696</v>
+        <v>528718</v>
       </c>
       <c r="R42" t="n">
-        <v>6998688</v>
+        <v>6998641</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5510,11 +5545,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Frodiga bålar.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5523,21 +5553,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5554,10 +5569,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122818122</v>
+        <v>122818026</v>
       </c>
       <c r="B43" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5570,21 +5585,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5597,7 +5612,7 @@
         <v>528631</v>
       </c>
       <c r="R43" t="n">
-        <v>6998473</v>
+        <v>6998469</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5656,10 +5671,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122817413</v>
+        <v>122818122</v>
       </c>
       <c r="B44" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5672,39 +5687,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528612</v>
+        <v>528631</v>
       </c>
       <c r="R44" t="n">
-        <v>6998323</v>
+        <v>6998473</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5737,11 +5747,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5768,10 +5773,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122819379</v>
+        <v>122817413</v>
       </c>
       <c r="B45" t="n">
-        <v>98365</v>
+        <v>57478</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5780,35 +5785,31 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5817,13 +5818,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528802</v>
+        <v>528612</v>
       </c>
       <c r="R45" t="n">
-        <v>6998594</v>
+        <v>6998323</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5850,24 +5851,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5882,22 +5873,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122818328</v>
+        <v>122819379</v>
       </c>
       <c r="B46" t="n">
-        <v>77699</v>
+        <v>98365</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5906,41 +5897,50 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528800</v>
+        <v>528802</v>
       </c>
       <c r="R46" t="n">
-        <v>6998633</v>
+        <v>6998594</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5999,22 +5999,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122817289</v>
+        <v>122818514</v>
       </c>
       <c r="B47" t="n">
-        <v>79145</v>
+        <v>74863</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6027,37 +6027,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>257107</v>
+        <v>6440</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blek lundlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bacidia rosellizans</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>S.Ekman</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528632</v>
+        <v>528635</v>
       </c>
       <c r="R47" t="n">
-        <v>6998403</v>
+        <v>6998546</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6084,24 +6084,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>09:23</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>09:23</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6116,19 +6101,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122818514</v>
+        <v>122817714</v>
       </c>
       <c r="B48" t="n">
         <v>74863</v>
@@ -6164,17 +6149,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528635</v>
+        <v>528625</v>
       </c>
       <c r="R48" t="n">
-        <v>6998546</v>
+        <v>6998424</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6201,9 +6186,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6218,22 +6218,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122817714</v>
+        <v>122817289</v>
       </c>
       <c r="B49" t="n">
-        <v>74863</v>
+        <v>79145</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6246,21 +6246,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6440</v>
+        <v>257107</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blek lundlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bacidia rosellizans</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>S.Ekman</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6270,13 +6270,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528625</v>
+        <v>528632</v>
       </c>
       <c r="R49" t="n">
-        <v>6998424</v>
+        <v>6998403</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6315,12 +6315,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6335,12 +6335,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -7200,10 +7200,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122818168</v>
+        <v>122817517</v>
       </c>
       <c r="B57" t="n">
-        <v>79807</v>
+        <v>78411</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7212,25 +7212,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>229497</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7240,10 +7240,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>528669</v>
+        <v>528643</v>
       </c>
       <c r="R57" t="n">
-        <v>6998500</v>
+        <v>6998354</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7275,7 +7275,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På bark på stam av död gammal asp (40 cm dbh) i gammal barrblandskog</t>
+          <t>På ved på gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7301,21 +7301,6 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7332,10 +7317,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122817517</v>
+        <v>122816979</v>
       </c>
       <c r="B58" t="n">
-        <v>78411</v>
+        <v>78503</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7348,21 +7333,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7372,13 +7357,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>528643</v>
+        <v>528730</v>
       </c>
       <c r="R58" t="n">
-        <v>6998354</v>
+        <v>6998447</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7407,7 +7392,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7417,12 +7402,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På ved på gammal tallstubbe</t>
+          <t>På kolad ved</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7437,12 +7422,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7561,10 +7546,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122816979</v>
+        <v>122818168</v>
       </c>
       <c r="B60" t="n">
-        <v>78503</v>
+        <v>79807</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7573,25 +7558,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>229497</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7601,13 +7586,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>528730</v>
+        <v>528669</v>
       </c>
       <c r="R60" t="n">
-        <v>6998447</v>
+        <v>6998500</v>
       </c>
       <c r="S60" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7636,7 +7621,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7646,12 +7631,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På kolad ved</t>
+          <t>På bark på stam av död gammal asp (40 cm dbh) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7662,16 +7647,31 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>

--- a/artfynd/A 55431-2024 artfynd.xlsx
+++ b/artfynd/A 55431-2024 artfynd.xlsx
@@ -1055,10 +1055,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122818503</v>
+        <v>122818036</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>79751</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1067,46 +1067,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528652</v>
+        <v>528686</v>
       </c>
       <c r="R5" t="n">
-        <v>6998555</v>
+        <v>6998471</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1133,14 +1128,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,22 +1160,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122818036</v>
+        <v>122818503</v>
       </c>
       <c r="B6" t="n">
-        <v>79751</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1179,41 +1184,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528686</v>
+        <v>528652</v>
       </c>
       <c r="R6" t="n">
-        <v>6998471</v>
+        <v>6998555</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1240,24 +1250,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,12 +1272,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -2716,10 +2716,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122818534</v>
+        <v>122818025</v>
       </c>
       <c r="B19" t="n">
-        <v>79813</v>
+        <v>79848</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2728,46 +2728,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229748</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528727</v>
+        <v>528631</v>
       </c>
       <c r="R19" t="n">
-        <v>6998595</v>
+        <v>6998469</v>
       </c>
       <c r="S19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2794,24 +2789,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2826,12 +2806,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -3061,10 +3041,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122818025</v>
+        <v>122818534</v>
       </c>
       <c r="B22" t="n">
-        <v>79848</v>
+        <v>79813</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3073,41 +3053,46 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>229748</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528631</v>
+        <v>528727</v>
       </c>
       <c r="R22" t="n">
-        <v>6998469</v>
+        <v>6998595</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3134,9 +3119,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3151,12 +3151,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3885,10 +3885,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122817142</v>
+        <v>122818204</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3901,42 +3901,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528699</v>
+        <v>528649</v>
       </c>
       <c r="R29" t="n">
-        <v>6998430</v>
+        <v>6998490</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3963,14 +3958,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På innerbark på gammal björkhögstubbe i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3985,19 +3990,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122817554</v>
+        <v>122817142</v>
       </c>
       <c r="B30" t="n">
         <v>57478</v>
@@ -4042,10 +4047,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528648</v>
+        <v>528699</v>
       </c>
       <c r="R30" t="n">
-        <v>6998359</v>
+        <v>6998430</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4082,7 +4087,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4109,10 +4114,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122818204</v>
+        <v>122817554</v>
       </c>
       <c r="B31" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4125,37 +4130,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528649</v>
+        <v>528648</v>
       </c>
       <c r="R31" t="n">
-        <v>6998490</v>
+        <v>6998359</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4182,24 +4192,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>10:09</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>10:09</t>
-        </is>
-      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På innerbark på gammal björkhögstubbe i gammal barrblandskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4214,12 +4214,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4989,10 +4989,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122818328</v>
+        <v>122818770</v>
       </c>
       <c r="B38" t="n">
-        <v>77699</v>
+        <v>91243</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5005,37 +5005,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228579</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528800</v>
+        <v>528718</v>
       </c>
       <c r="R38" t="n">
-        <v>6998633</v>
+        <v>6998641</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5062,24 +5062,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5094,22 +5079,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122818035</v>
+        <v>122818026</v>
       </c>
       <c r="B39" t="n">
-        <v>79807</v>
+        <v>79847</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5118,25 +5103,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5146,10 +5131,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528677</v>
+        <v>528631</v>
       </c>
       <c r="R39" t="n">
-        <v>6998487</v>
+        <v>6998469</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5179,24 +5164,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5211,12 +5181,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5350,10 +5320,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122816987</v>
+        <v>122818122</v>
       </c>
       <c r="B41" t="n">
-        <v>79384</v>
+        <v>79848</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5366,21 +5336,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5390,13 +5360,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528755</v>
+        <v>528631</v>
       </c>
       <c r="R41" t="n">
-        <v>6998446</v>
+        <v>6998473</v>
       </c>
       <c r="S41" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5423,24 +5393,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>09:04</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>09:04</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På bränd jöttetallstubbe</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5455,22 +5410,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122818770</v>
+        <v>122817413</v>
       </c>
       <c r="B42" t="n">
-        <v>91243</v>
+        <v>57478</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5483,34 +5438,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528718</v>
+        <v>528612</v>
       </c>
       <c r="R42" t="n">
-        <v>6998641</v>
+        <v>6998323</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5543,6 +5503,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5569,10 +5534,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122818026</v>
+        <v>122819379</v>
       </c>
       <c r="B43" t="n">
-        <v>79847</v>
+        <v>98365</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5581,41 +5546,50 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528631</v>
+        <v>528802</v>
       </c>
       <c r="R43" t="n">
-        <v>6998469</v>
+        <v>6998594</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5642,9 +5616,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5659,22 +5648,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122818122</v>
+        <v>122818328</v>
       </c>
       <c r="B44" t="n">
-        <v>79848</v>
+        <v>77699</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5687,21 +5676,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5711,13 +5700,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528631</v>
+        <v>528800</v>
       </c>
       <c r="R44" t="n">
-        <v>6998473</v>
+        <v>6998633</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5744,9 +5733,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5761,22 +5765,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122817413</v>
+        <v>122816987</v>
       </c>
       <c r="B45" t="n">
-        <v>57478</v>
+        <v>79384</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5789,42 +5793,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528612</v>
+        <v>528755</v>
       </c>
       <c r="R45" t="n">
-        <v>6998323</v>
+        <v>6998446</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5851,14 +5850,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På bränd jöttetallstubbe</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5873,22 +5882,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122819379</v>
+        <v>122818035</v>
       </c>
       <c r="B46" t="n">
-        <v>98365</v>
+        <v>79807</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5897,50 +5906,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528802</v>
+        <v>528677</v>
       </c>
       <c r="R46" t="n">
-        <v>6998594</v>
+        <v>6998487</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5999,12 +5999,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -6347,10 +6347,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122818573</v>
+        <v>122818323</v>
       </c>
       <c r="B50" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6363,37 +6363,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528630</v>
+        <v>528667</v>
       </c>
       <c r="R50" t="n">
-        <v>6998539</v>
+        <v>6998534</v>
       </c>
       <c r="S50" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6420,11 +6420,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Rikligt på bark på stam av levande gammal sälg i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6433,51 +6448,26 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122818165</v>
+        <v>122818032</v>
       </c>
       <c r="B51" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6486,25 +6476,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6514,13 +6504,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528594</v>
+        <v>528631</v>
       </c>
       <c r="R51" t="n">
-        <v>6998419</v>
+        <v>6998469</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6560,31 +6550,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6601,10 +6566,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122818323</v>
+        <v>122818573</v>
       </c>
       <c r="B52" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6617,37 +6582,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>528667</v>
+        <v>528630</v>
       </c>
       <c r="R52" t="n">
-        <v>6998534</v>
+        <v>6998539</v>
       </c>
       <c r="S52" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6674,26 +6639,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Rikligt på bark på stam av levande gammal sälg i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6702,26 +6652,51 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122818032</v>
+        <v>122818165</v>
       </c>
       <c r="B53" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6730,25 +6705,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6758,13 +6733,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>528631</v>
+        <v>528594</v>
       </c>
       <c r="R53" t="n">
-        <v>6998469</v>
+        <v>6998419</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6804,6 +6779,31 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">

--- a/artfynd/A 55431-2024 artfynd.xlsx
+++ b/artfynd/A 55431-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122818966</v>
+        <v>122818387</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,42 +802,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528791</v>
+        <v>528619</v>
       </c>
       <c r="R3" t="n">
-        <v>6998599</v>
+        <v>6998495</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,26 +859,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal sälg (25 cm dbh) i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -893,37 +873,47 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122819118</v>
+        <v>122818165</v>
       </c>
       <c r="B4" t="n">
         <v>78766</v>
@@ -959,17 +949,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528690</v>
+        <v>528594</v>
       </c>
       <c r="R4" t="n">
-        <v>6998652</v>
+        <v>6998419</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,11 +991,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1017,27 +1002,27 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1055,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122818036</v>
+        <v>122819397</v>
       </c>
       <c r="B5" t="n">
-        <v>79751</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1067,41 +1052,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528686</v>
+        <v>528826</v>
       </c>
       <c r="R5" t="n">
-        <v>6998471</v>
+        <v>6998595</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1128,24 +1122,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1160,22 +1139,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122818503</v>
+        <v>122817517</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>78411</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1188,39 +1167,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528652</v>
+        <v>528643</v>
       </c>
       <c r="R6" t="n">
-        <v>6998555</v>
+        <v>6998354</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,14 +1224,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>På ved på gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,22 +1256,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122818125</v>
+        <v>122819448</v>
       </c>
       <c r="B7" t="n">
-        <v>78503</v>
+        <v>79876</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1296,38 +1280,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528687</v>
+        <v>528696</v>
       </c>
       <c r="R7" t="n">
-        <v>6998489</v>
+        <v>6998688</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1357,24 +1346,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal tallstubbe i gammal barrblandskog</t>
+          <t>Frodiga bålar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1385,26 +1364,41 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Stone/rock on land</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122817186</v>
+        <v>122817219</v>
       </c>
       <c r="B8" t="n">
-        <v>57428</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1413,55 +1407,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102621</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528689</v>
+        <v>528684</v>
       </c>
       <c r="R8" t="n">
-        <v>6998416</v>
+        <v>6998437</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1493,6 +1473,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1501,6 +1486,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1517,10 +1527,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122817037</v>
+        <v>122818770</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>91243</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1533,47 +1543,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528752</v>
+        <v>528718</v>
       </c>
       <c r="R9" t="n">
-        <v>6998456</v>
+        <v>6998641</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1605,11 +1605,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1618,31 +1613,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1659,10 +1629,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122819058</v>
+        <v>122818174</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1675,37 +1645,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528654</v>
+        <v>528625</v>
       </c>
       <c r="R10" t="n">
-        <v>6998628</v>
+        <v>6998500</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1737,6 +1712,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1745,31 +1725,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1786,10 +1741,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122817937</v>
+        <v>122816988</v>
       </c>
       <c r="B11" t="n">
-        <v>90963</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1798,41 +1753,51 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528686</v>
+        <v>528756</v>
       </c>
       <c r="R11" t="n">
-        <v>6998446</v>
+        <v>6998450</v>
       </c>
       <c r="S11" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1859,24 +1824,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På död asp</t>
+          <t>Äldre ringhack på en tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1887,26 +1842,51 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122817339</v>
+        <v>122818536</v>
       </c>
       <c r="B12" t="n">
-        <v>79384</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1919,37 +1899,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528649</v>
+        <v>528665</v>
       </c>
       <c r="R12" t="n">
-        <v>6998383</v>
+        <v>6998574</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1976,24 +1961,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gammal tallstubbe</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2008,22 +1983,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122818247</v>
+        <v>122818759</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2036,21 +2011,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2060,10 +2035,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528605</v>
+        <v>528778</v>
       </c>
       <c r="R13" t="n">
-        <v>6998454</v>
+        <v>6998602</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2093,11 +2068,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På gammal asp i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2106,51 +2096,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122817110</v>
+        <v>122818514</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2163,37 +2128,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528711</v>
+        <v>528635</v>
       </c>
       <c r="R14" t="n">
-        <v>6998430</v>
+        <v>6998546</v>
       </c>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2220,24 +2185,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>09:11</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>09:11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2252,22 +2202,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122818759</v>
+        <v>122819058</v>
       </c>
       <c r="B15" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2280,37 +2230,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528778</v>
+        <v>528654</v>
       </c>
       <c r="R15" t="n">
-        <v>6998602</v>
+        <v>6998628</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2337,26 +2287,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På gammal asp i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2365,26 +2300,51 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122819397</v>
+        <v>122818168</v>
       </c>
       <c r="B16" t="n">
-        <v>57494</v>
+        <v>79807</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2393,47 +2353,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>229497</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528826</v>
+        <v>528669</v>
       </c>
       <c r="R16" t="n">
-        <v>6998595</v>
+        <v>6998500</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2463,11 +2414,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På bark på stam av död gammal asp (40 cm dbh) i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2476,26 +2442,41 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122817325</v>
+        <v>122817289</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>79145</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2508,42 +2489,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>257107</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blek lundlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bacidia rosellizans</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>S.Ekman</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528640</v>
+        <v>528632</v>
       </c>
       <c r="R17" t="n">
-        <v>6998336</v>
+        <v>6998403</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2570,14 +2546,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2592,22 +2578,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122818536</v>
+        <v>122818204</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2620,42 +2606,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528665</v>
+        <v>528649</v>
       </c>
       <c r="R18" t="n">
-        <v>6998574</v>
+        <v>6998490</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2682,14 +2663,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>På innerbark på gammal björkhögstubbe i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2704,22 +2695,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122818025</v>
+        <v>122819024</v>
       </c>
       <c r="B19" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2732,37 +2723,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528631</v>
+        <v>528636</v>
       </c>
       <c r="R19" t="n">
-        <v>6998469</v>
+        <v>6998609</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2802,6 +2793,31 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Dead branch  # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2818,10 +2834,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122817144</v>
+        <v>122818966</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2834,31 +2850,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2867,13 +2879,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528705</v>
+        <v>528791</v>
       </c>
       <c r="R20" t="n">
-        <v>6998384</v>
+        <v>6998599</v>
       </c>
       <c r="S20" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2902,7 +2914,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2912,7 +2924,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal sälg (25 cm dbh) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2923,26 +2940,41 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122818126</v>
+        <v>122818125</v>
       </c>
       <c r="B21" t="n">
-        <v>79847</v>
+        <v>78503</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2955,21 +2987,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2979,7 +3011,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528624</v>
+        <v>528687</v>
       </c>
       <c r="R21" t="n">
         <v>6998489</v>
@@ -3012,9 +3044,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal tallstubbe i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3029,22 +3076,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122818534</v>
+        <v>122817942</v>
       </c>
       <c r="B22" t="n">
-        <v>79813</v>
+        <v>57478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3053,31 +3100,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229748</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3086,13 +3133,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528727</v>
+        <v>528655</v>
       </c>
       <c r="R22" t="n">
-        <v>6998595</v>
+        <v>6998433</v>
       </c>
       <c r="S22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3119,24 +3166,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3151,22 +3188,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122818387</v>
+        <v>122819033</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
+        <v>74675</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3175,25 +3212,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3203,13 +3240,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528619</v>
+        <v>528798</v>
       </c>
       <c r="R23" t="n">
-        <v>6998495</v>
+        <v>6998603</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3236,11 +3273,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal sälg i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3249,51 +3301,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122817546</v>
+        <v>122818955</v>
       </c>
       <c r="B24" t="n">
-        <v>74863</v>
+        <v>74786</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3306,37 +3333,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>1460</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528628</v>
+        <v>528791</v>
       </c>
       <c r="R24" t="n">
-        <v>6998367</v>
+        <v>6998633</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3365,7 +3397,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3375,12 +3407,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3407,10 +3439,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122818321</v>
+        <v>122817186</v>
       </c>
       <c r="B25" t="n">
-        <v>74863</v>
+        <v>57428</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3419,38 +3451,52 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>102621</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528805</v>
+        <v>528689</v>
       </c>
       <c r="R25" t="n">
-        <v>6998631</v>
+        <v>6998416</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3480,24 +3526,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3512,22 +3543,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122818864</v>
+        <v>122818503</v>
       </c>
       <c r="B26" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3540,37 +3571,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528732</v>
+        <v>528652</v>
       </c>
       <c r="R26" t="n">
-        <v>6998659</v>
+        <v>6998555</v>
       </c>
       <c r="S26" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3597,24 +3633,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3629,22 +3655,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122819033</v>
+        <v>122817554</v>
       </c>
       <c r="B27" t="n">
-        <v>74675</v>
+        <v>57478</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3653,41 +3679,46 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6428</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528798</v>
+        <v>528648</v>
       </c>
       <c r="R27" t="n">
-        <v>6998603</v>
+        <v>6998359</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3714,24 +3745,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal barrblandskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3746,22 +3767,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122818040</v>
+        <v>122817601</v>
       </c>
       <c r="B28" t="n">
-        <v>78766</v>
+        <v>90972</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3774,21 +3795,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3798,13 +3819,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528621</v>
+        <v>528645</v>
       </c>
       <c r="R28" t="n">
-        <v>6998383</v>
+        <v>6998384</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3844,31 +3865,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3885,10 +3881,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122818204</v>
+        <v>122816987</v>
       </c>
       <c r="B29" t="n">
-        <v>79847</v>
+        <v>79384</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3901,21 +3897,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3925,13 +3921,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528649</v>
+        <v>528755</v>
       </c>
       <c r="R29" t="n">
-        <v>6998490</v>
+        <v>6998446</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3960,7 +3956,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3970,12 +3966,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På innerbark på gammal björkhögstubbe i gammal barrblandskog</t>
+          <t>På bränd jöttetallstubbe</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4002,10 +3998,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122817142</v>
+        <v>122817273</v>
       </c>
       <c r="B30" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4018,27 +4014,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4047,13 +4047,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528699</v>
+        <v>528623</v>
       </c>
       <c r="R30" t="n">
-        <v>6998430</v>
+        <v>6998311</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4080,14 +4080,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4102,22 +4112,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122817554</v>
+        <v>122817339</v>
       </c>
       <c r="B31" t="n">
-        <v>57478</v>
+        <v>79384</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4130,42 +4140,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528648</v>
+        <v>528649</v>
       </c>
       <c r="R31" t="n">
-        <v>6998359</v>
+        <v>6998383</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4192,14 +4197,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4214,22 +4229,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122816988</v>
+        <v>122817937</v>
       </c>
       <c r="B32" t="n">
-        <v>57478</v>
+        <v>90963</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4238,51 +4253,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528756</v>
+        <v>528686</v>
       </c>
       <c r="R32" t="n">
-        <v>6998450</v>
+        <v>6998446</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4309,14 +4314,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en tall.</t>
+          <t>På död asp</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4327,51 +4342,26 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122817273</v>
+        <v>122819379</v>
       </c>
       <c r="B33" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4380,35 +4370,35 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4417,13 +4407,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528623</v>
+        <v>528802</v>
       </c>
       <c r="R33" t="n">
-        <v>6998311</v>
+        <v>6998594</v>
       </c>
       <c r="S33" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4452,7 +4442,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4462,12 +4452,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4482,22 +4472,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122818675</v>
+        <v>122817714</v>
       </c>
       <c r="B34" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4510,46 +4500,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528722</v>
+        <v>528625</v>
       </c>
       <c r="R34" t="n">
-        <v>6998660</v>
+        <v>6998424</v>
       </c>
       <c r="S34" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4578,7 +4559,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4588,7 +4569,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4615,7 +4601,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122817112</v>
+        <v>122817110</v>
       </c>
       <c r="B35" t="n">
         <v>78766</v>
@@ -4648,16 +4634,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
@@ -4667,10 +4644,10 @@
         <v>528711</v>
       </c>
       <c r="R35" t="n">
-        <v>6998411</v>
+        <v>6998430</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4699,7 +4676,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4709,12 +4686,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4729,19 +4706,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122818653</v>
+        <v>122818026</v>
       </c>
       <c r="B36" t="n">
         <v>79847</v>
@@ -4781,13 +4758,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528732</v>
+        <v>528631</v>
       </c>
       <c r="R36" t="n">
-        <v>6998541</v>
+        <v>6998469</v>
       </c>
       <c r="S36" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4814,24 +4791,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På asplåga i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4846,22 +4808,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122818613</v>
+        <v>122818025</v>
       </c>
       <c r="B37" t="n">
-        <v>98365</v>
+        <v>79848</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4870,55 +4832,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528723</v>
+        <v>528631</v>
       </c>
       <c r="R37" t="n">
-        <v>6998554</v>
+        <v>6998469</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4945,24 +4893,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4977,22 +4910,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122818770</v>
+        <v>122817645</v>
       </c>
       <c r="B38" t="n">
-        <v>91243</v>
+        <v>57499</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5001,41 +4934,50 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>100110</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528718</v>
+        <v>528643</v>
       </c>
       <c r="R38" t="n">
-        <v>6998641</v>
+        <v>6998354</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5062,9 +5004,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5079,22 +5031,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122818026</v>
+        <v>122817142</v>
       </c>
       <c r="B39" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5107,34 +5059,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528631</v>
+        <v>528699</v>
       </c>
       <c r="R39" t="n">
-        <v>6998469</v>
+        <v>6998430</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5167,6 +5124,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5193,10 +5155,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122819448</v>
+        <v>122818036</v>
       </c>
       <c r="B40" t="n">
-        <v>79876</v>
+        <v>79751</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5209,42 +5171,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528696</v>
+        <v>528686</v>
       </c>
       <c r="R40" t="n">
-        <v>6998688</v>
+        <v>6998471</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5271,14 +5228,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Frodiga bålar.</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5289,41 +5256,26 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122818122</v>
+        <v>122818321</v>
       </c>
       <c r="B41" t="n">
-        <v>79848</v>
+        <v>74863</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5336,21 +5288,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5360,10 +5312,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528631</v>
+        <v>528805</v>
       </c>
       <c r="R41" t="n">
-        <v>6998473</v>
+        <v>6998631</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5393,9 +5345,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5410,22 +5377,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122817413</v>
+        <v>122817112</v>
       </c>
       <c r="B42" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5438,27 +5405,31 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5467,13 +5438,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528612</v>
+        <v>528711</v>
       </c>
       <c r="R42" t="n">
-        <v>6998323</v>
+        <v>6998411</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5500,14 +5471,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5522,22 +5503,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122819379</v>
+        <v>122818573</v>
       </c>
       <c r="B43" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5546,50 +5527,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528802</v>
+        <v>528630</v>
       </c>
       <c r="R43" t="n">
-        <v>6998594</v>
+        <v>6998539</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5616,26 +5588,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På marken i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5644,26 +5601,51 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122818328</v>
+        <v>122817413</v>
       </c>
       <c r="B44" t="n">
-        <v>77699</v>
+        <v>57478</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5676,37 +5658,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528800</v>
+        <v>528612</v>
       </c>
       <c r="R44" t="n">
-        <v>6998633</v>
+        <v>6998323</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5733,24 +5720,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5765,22 +5742,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122816987</v>
+        <v>122818654</v>
       </c>
       <c r="B45" t="n">
-        <v>79384</v>
+        <v>57478</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5793,37 +5770,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528755</v>
+        <v>528711</v>
       </c>
       <c r="R45" t="n">
-        <v>6998446</v>
+        <v>6998632</v>
       </c>
       <c r="S45" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5850,24 +5832,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>09:04</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>09:04</t>
-        </is>
-      </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På bränd jöttetallstubbe</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5882,22 +5854,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122818035</v>
+        <v>122816979</v>
       </c>
       <c r="B46" t="n">
-        <v>79807</v>
+        <v>78503</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5906,25 +5878,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229497</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5934,13 +5906,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528677</v>
+        <v>528730</v>
       </c>
       <c r="R46" t="n">
-        <v>6998487</v>
+        <v>6998447</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5969,7 +5941,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5979,12 +5951,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>På kolad ved</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6011,7 +5983,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122818514</v>
+        <v>122817546</v>
       </c>
       <c r="B47" t="n">
         <v>74863</v>
@@ -6047,17 +6019,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528635</v>
+        <v>528628</v>
       </c>
       <c r="R47" t="n">
-        <v>6998546</v>
+        <v>6998367</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6084,9 +6056,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6101,22 +6088,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122817714</v>
+        <v>122817054</v>
       </c>
       <c r="B48" t="n">
-        <v>74863</v>
+        <v>79751</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6125,25 +6112,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6153,13 +6140,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528625</v>
+        <v>528755</v>
       </c>
       <c r="R48" t="n">
-        <v>6998424</v>
+        <v>6998448</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6188,7 +6175,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6198,12 +6185,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6218,22 +6205,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122817289</v>
+        <v>122818040</v>
       </c>
       <c r="B49" t="n">
-        <v>79145</v>
+        <v>78766</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6246,21 +6233,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>257107</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blek lundlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bacidia rosellizans</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>S.Ekman</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6270,13 +6257,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528632</v>
+        <v>528621</v>
       </c>
       <c r="R49" t="n">
-        <v>6998403</v>
+        <v>6998383</v>
       </c>
       <c r="S49" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6303,26 +6290,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>09:23</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>09:23</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6331,26 +6303,51 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122818323</v>
+        <v>122818675</v>
       </c>
       <c r="B50" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6363,37 +6360,46 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528667</v>
+        <v>528722</v>
       </c>
       <c r="R50" t="n">
-        <v>6998534</v>
+        <v>6998660</v>
       </c>
       <c r="S50" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6422,7 +6428,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6432,12 +6438,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:13</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Rikligt på bark på stam av levande gammal sälg i gammal barrblandskog</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6452,22 +6453,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122818032</v>
+        <v>122818122</v>
       </c>
       <c r="B51" t="n">
-        <v>79876</v>
+        <v>79848</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6476,25 +6477,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6507,7 +6508,7 @@
         <v>528631</v>
       </c>
       <c r="R51" t="n">
-        <v>6998469</v>
+        <v>6998473</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6566,10 +6567,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122818573</v>
+        <v>122818864</v>
       </c>
       <c r="B52" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6582,37 +6583,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>528630</v>
+        <v>528732</v>
       </c>
       <c r="R52" t="n">
-        <v>6998539</v>
+        <v>6998659</v>
       </c>
       <c r="S52" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6639,11 +6640,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6652,48 +6668,23 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122818165</v>
+        <v>122818247</v>
       </c>
       <c r="B53" t="n">
         <v>78766</v>
@@ -6733,13 +6724,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>528594</v>
+        <v>528605</v>
       </c>
       <c r="R53" t="n">
-        <v>6998419</v>
+        <v>6998454</v>
       </c>
       <c r="S53" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6787,22 +6778,22 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6820,10 +6811,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122817645</v>
+        <v>122817550</v>
       </c>
       <c r="B54" t="n">
-        <v>57499</v>
+        <v>57478</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6832,35 +6823,31 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100110</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6869,13 +6856,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>528643</v>
+        <v>528648</v>
       </c>
       <c r="R54" t="n">
-        <v>6998354</v>
+        <v>6998358</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6902,19 +6889,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>09:45</t>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6929,22 +6911,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122818681</v>
+        <v>122817278</v>
       </c>
       <c r="B55" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6957,37 +6939,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>528686</v>
+        <v>528671</v>
       </c>
       <c r="R55" t="n">
-        <v>6998618</v>
+        <v>6998337</v>
       </c>
       <c r="S55" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7019,6 +7006,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -7027,31 +7019,6 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7068,10 +7035,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122817657</v>
+        <v>122818713</v>
       </c>
       <c r="B56" t="n">
-        <v>78766</v>
+        <v>90952</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7084,37 +7051,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>528650</v>
+        <v>528718</v>
       </c>
       <c r="R56" t="n">
-        <v>6998397</v>
+        <v>6998641</v>
       </c>
       <c r="S56" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7146,11 +7113,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7159,31 +7121,6 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7200,10 +7137,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122817517</v>
+        <v>122818653</v>
       </c>
       <c r="B57" t="n">
-        <v>78411</v>
+        <v>79847</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7216,21 +7153,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7240,13 +7177,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>528643</v>
+        <v>528732</v>
       </c>
       <c r="R57" t="n">
-        <v>6998354</v>
+        <v>6998541</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7275,7 +7212,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7285,12 +7222,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På ved på gammal tallstubbe</t>
+          <t>På asplåga i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7317,10 +7254,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122816979</v>
+        <v>122817037</v>
       </c>
       <c r="B58" t="n">
-        <v>78503</v>
+        <v>57478</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7333,37 +7270,47 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>528730</v>
+        <v>528752</v>
       </c>
       <c r="R58" t="n">
-        <v>6998447</v>
+        <v>6998456</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7390,24 +7337,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>09:03</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>09:03</t>
-        </is>
-      </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På kolad ved</t>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7418,26 +7355,51 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122817942</v>
+        <v>122817144</v>
       </c>
       <c r="B59" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7450,27 +7412,31 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7479,13 +7445,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>528655</v>
+        <v>528705</v>
       </c>
       <c r="R59" t="n">
-        <v>6998433</v>
+        <v>6998384</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7512,14 +7478,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7534,22 +7505,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122818168</v>
+        <v>122818681</v>
       </c>
       <c r="B60" t="n">
-        <v>79807</v>
+        <v>78766</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7558,41 +7529,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>528669</v>
+        <v>528686</v>
       </c>
       <c r="R60" t="n">
-        <v>6998500</v>
+        <v>6998618</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7619,26 +7590,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>På bark på stam av död gammal asp (40 cm dbh) i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -7648,40 +7604,50 @@
       <c r="AG60" t="b">
         <v>0</v>
       </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122818713</v>
+        <v>122818032</v>
       </c>
       <c r="B61" t="n">
-        <v>90952</v>
+        <v>79876</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7690,38 +7656,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>528718</v>
+        <v>528631</v>
       </c>
       <c r="R61" t="n">
-        <v>6998641</v>
+        <v>6998469</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7780,10 +7746,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122817758</v>
+        <v>122819118</v>
       </c>
       <c r="B62" t="n">
-        <v>77699</v>
+        <v>78766</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7796,37 +7762,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>528610</v>
+        <v>528690</v>
       </c>
       <c r="R62" t="n">
-        <v>6998403</v>
+        <v>6998652</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7853,24 +7819,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7881,26 +7837,51 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122817278</v>
+        <v>122818613</v>
       </c>
       <c r="B63" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7909,31 +7890,40 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7942,13 +7932,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>528671</v>
+        <v>528723</v>
       </c>
       <c r="R63" t="n">
-        <v>6998337</v>
+        <v>6998554</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7975,14 +7965,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7997,22 +7997,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122818174</v>
+        <v>122818323</v>
       </c>
       <c r="B64" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8025,42 +8025,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>528625</v>
+        <v>528667</v>
       </c>
       <c r="R64" t="n">
-        <v>6998500</v>
+        <v>6998534</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8087,14 +8082,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Rikligt på bark på stam av levande gammal sälg i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8109,22 +8114,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122817219</v>
+        <v>122817758</v>
       </c>
       <c r="B65" t="n">
-        <v>78766</v>
+        <v>77699</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8137,21 +8142,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8161,13 +8166,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>528684</v>
+        <v>528610</v>
       </c>
       <c r="R65" t="n">
-        <v>6998437</v>
+        <v>6998403</v>
       </c>
       <c r="S65" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8194,14 +8199,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8212,51 +8227,26 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122817054</v>
+        <v>122817869</v>
       </c>
       <c r="B66" t="n">
-        <v>79751</v>
+        <v>57499</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8269,34 +8259,43 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6456</v>
+        <v>100110</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>528755</v>
+        <v>528645</v>
       </c>
       <c r="R66" t="n">
-        <v>6998448</v>
+        <v>6998384</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8326,24 +8325,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>09:08</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>09:08</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8358,22 +8342,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122819024</v>
+        <v>122818534</v>
       </c>
       <c r="B67" t="n">
-        <v>78766</v>
+        <v>79813</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8382,41 +8366,46 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>528636</v>
+        <v>528727</v>
       </c>
       <c r="R67" t="n">
-        <v>6998609</v>
+        <v>6998595</v>
       </c>
       <c r="S67" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8443,11 +8432,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På gammal asp</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8456,51 +8460,26 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Dead branch  # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122818955</v>
+        <v>122818035</v>
       </c>
       <c r="B68" t="n">
-        <v>74786</v>
+        <v>79807</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8509,43 +8488,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1460</v>
+        <v>229497</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>528791</v>
+        <v>528677</v>
       </c>
       <c r="R68" t="n">
-        <v>6998633</v>
+        <v>6998487</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8577,7 +8551,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8587,12 +8561,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8619,10 +8593,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122818654</v>
+        <v>122818126</v>
       </c>
       <c r="B69" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8635,39 +8609,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>528711</v>
+        <v>528624</v>
       </c>
       <c r="R69" t="n">
-        <v>6998632</v>
+        <v>6998489</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8700,11 +8669,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8731,10 +8695,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122817869</v>
+        <v>122817657</v>
       </c>
       <c r="B70" t="n">
-        <v>57499</v>
+        <v>78766</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8743,50 +8707,41 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100110</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>528645</v>
+        <v>528650</v>
       </c>
       <c r="R70" t="n">
-        <v>6998384</v>
+        <v>6998397</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8818,6 +8773,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -8826,6 +8786,31 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -8842,7 +8827,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122817550</v>
+        <v>122817325</v>
       </c>
       <c r="B71" t="n">
         <v>57478</v>
@@ -8887,10 +8872,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>528648</v>
+        <v>528640</v>
       </c>
       <c r="R71" t="n">
-        <v>6998358</v>
+        <v>6998336</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8954,10 +8939,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122817601</v>
+        <v>122818328</v>
       </c>
       <c r="B72" t="n">
-        <v>90972</v>
+        <v>77699</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8970,21 +8955,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5442</v>
+        <v>228579</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8994,13 +8979,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>528645</v>
+        <v>528800</v>
       </c>
       <c r="R72" t="n">
-        <v>6998384</v>
+        <v>6998633</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9027,9 +9012,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9044,12 +9044,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>

--- a/artfynd/A 55431-2024 artfynd.xlsx
+++ b/artfynd/A 55431-2024 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122818387</v>
+        <v>122818681</v>
       </c>
       <c r="B3" t="n">
         <v>78766</v>
@@ -822,17 +822,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528619</v>
+        <v>528686</v>
       </c>
       <c r="R3" t="n">
-        <v>6998495</v>
+        <v>6998618</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122818165</v>
+        <v>122818503</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,37 +929,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528594</v>
+        <v>528652</v>
       </c>
       <c r="R4" t="n">
-        <v>6998419</v>
+        <v>6998555</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,6 +996,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -999,31 +1009,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1040,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122819397</v>
+        <v>122818534</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>79813</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,50 +1037,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>229748</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528826</v>
+        <v>528727</v>
       </c>
       <c r="R5" t="n">
         <v>6998595</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,9 +1103,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,22 +1135,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122817517</v>
+        <v>122817144</v>
       </c>
       <c r="B6" t="n">
-        <v>78411</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,37 +1163,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528643</v>
+        <v>528705</v>
       </c>
       <c r="R6" t="n">
-        <v>6998354</v>
+        <v>6998384</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1226,7 +1231,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1236,12 +1241,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:34</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På ved på gammal tallstubbe</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,22 +1256,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122819448</v>
+        <v>122819024</v>
       </c>
       <c r="B7" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1280,46 +1280,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528696</v>
+        <v>528636</v>
       </c>
       <c r="R7" t="n">
-        <v>6998688</v>
+        <v>6998609</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1351,11 +1346,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Frodiga bålar.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1370,14 +1360,24 @@
           <t>Tallskog</t>
         </is>
       </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Sten/berg på land</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stone/rock on land</t>
+          <t>Dead branch  # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1395,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122817219</v>
+        <v>122818654</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1411,37 +1411,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528684</v>
+        <v>528711</v>
       </c>
       <c r="R8" t="n">
-        <v>6998437</v>
+        <v>6998632</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1475,7 +1480,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,31 +1491,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1527,10 +1507,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122818770</v>
+        <v>122818126</v>
       </c>
       <c r="B9" t="n">
-        <v>91243</v>
+        <v>79847</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1543,34 +1523,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528718</v>
+        <v>528624</v>
       </c>
       <c r="R9" t="n">
-        <v>6998641</v>
+        <v>6998489</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1629,10 +1609,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122818174</v>
+        <v>122818955</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>74786</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1645,27 +1625,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1460</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1674,10 +1654,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528625</v>
+        <v>528791</v>
       </c>
       <c r="R10" t="n">
-        <v>6998500</v>
+        <v>6998633</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1707,14 +1687,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1729,22 +1719,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122816988</v>
+        <v>122818323</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1757,47 +1747,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528756</v>
+        <v>528667</v>
       </c>
       <c r="R11" t="n">
-        <v>6998450</v>
+        <v>6998534</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1824,14 +1804,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en tall.</t>
+          <t>Rikligt på bark på stam av levande gammal sälg i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1842,51 +1832,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122818536</v>
+        <v>122818387</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1899,39 +1864,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528665</v>
+        <v>528619</v>
       </c>
       <c r="R12" t="n">
-        <v>6998574</v>
+        <v>6998495</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1966,11 +1926,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1979,6 +1934,31 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1995,10 +1975,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122818759</v>
+        <v>122817657</v>
       </c>
       <c r="B13" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2011,21 +1991,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2035,13 +2015,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528778</v>
+        <v>528650</v>
       </c>
       <c r="R13" t="n">
-        <v>6998602</v>
+        <v>6998397</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2068,24 +2048,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal asp i gammal barrblandskog</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2096,26 +2066,51 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122818514</v>
+        <v>122817942</v>
       </c>
       <c r="B14" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2128,34 +2123,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528635</v>
+        <v>528655</v>
       </c>
       <c r="R14" t="n">
-        <v>6998546</v>
+        <v>6998433</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2188,6 +2188,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2214,10 +2219,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122819058</v>
+        <v>122817550</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2230,37 +2235,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528654</v>
+        <v>528648</v>
       </c>
       <c r="R15" t="n">
-        <v>6998628</v>
+        <v>6998358</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2292,6 +2302,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2300,31 +2315,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2473,10 +2463,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122817289</v>
+        <v>122818713</v>
       </c>
       <c r="B17" t="n">
-        <v>79145</v>
+        <v>90952</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2489,37 +2479,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>257107</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blek lundlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bacidia rosellizans</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>S.Ekman</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528632</v>
+        <v>528718</v>
       </c>
       <c r="R17" t="n">
-        <v>6998403</v>
+        <v>6998641</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2546,24 +2536,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>09:23</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>09:23</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2578,22 +2553,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122818204</v>
+        <v>122818514</v>
       </c>
       <c r="B18" t="n">
-        <v>79847</v>
+        <v>74863</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2606,37 +2581,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528649</v>
+        <v>528635</v>
       </c>
       <c r="R18" t="n">
-        <v>6998490</v>
+        <v>6998546</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2663,24 +2638,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>10:09</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>10:09</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På innerbark på gammal björkhögstubbe i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2695,22 +2655,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122819024</v>
+        <v>122819448</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2719,41 +2679,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528636</v>
+        <v>528696</v>
       </c>
       <c r="R19" t="n">
-        <v>6998609</v>
+        <v>6998688</v>
       </c>
       <c r="S19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2785,6 +2750,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Frodiga bålar.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2799,24 +2769,14 @@
           <t>Tallskog</t>
         </is>
       </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Sten/berg på land</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Dead branch  # Pinus sylvestris</t>
+          <t>Stone/rock on land</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2834,10 +2794,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122818966</v>
+        <v>122818122</v>
       </c>
       <c r="B20" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2850,42 +2810,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528791</v>
+        <v>528631</v>
       </c>
       <c r="R20" t="n">
-        <v>6998599</v>
+        <v>6998473</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2912,26 +2867,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal sälg (25 cm dbh) i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2940,41 +2880,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122818125</v>
+        <v>122817413</v>
       </c>
       <c r="B21" t="n">
-        <v>78503</v>
+        <v>57478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2987,34 +2912,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528687</v>
+        <v>528612</v>
       </c>
       <c r="R21" t="n">
-        <v>6998489</v>
+        <v>6998323</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3044,24 +2974,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal tallstubbe i gammal barrblandskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3076,22 +2996,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122817942</v>
+        <v>122818040</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3104,42 +3024,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528655</v>
+        <v>528621</v>
       </c>
       <c r="R22" t="n">
-        <v>6998433</v>
+        <v>6998383</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3171,11 +3086,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3184,6 +3094,31 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3200,10 +3135,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122819033</v>
+        <v>122818966</v>
       </c>
       <c r="B23" t="n">
-        <v>74675</v>
+        <v>79847</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3212,41 +3147,46 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6428</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528798</v>
+        <v>528791</v>
       </c>
       <c r="R23" t="n">
-        <v>6998603</v>
+        <v>6998599</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3275,7 +3215,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3285,12 +3225,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal barrblandskog</t>
+          <t>På bark på stam av levande gammal sälg (25 cm dbh) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3301,6 +3241,21 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3317,10 +3272,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122818955</v>
+        <v>122817219</v>
       </c>
       <c r="B24" t="n">
-        <v>74786</v>
+        <v>78766</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3333,42 +3288,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1460</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528791</v>
+        <v>528684</v>
       </c>
       <c r="R24" t="n">
-        <v>6998633</v>
+        <v>6998437</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3395,24 +3345,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3423,26 +3363,51 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122817186</v>
+        <v>122817325</v>
       </c>
       <c r="B25" t="n">
-        <v>57428</v>
+        <v>57478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3451,20 +3416,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3472,19 +3437,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3493,10 +3449,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528689</v>
+        <v>528640</v>
       </c>
       <c r="R25" t="n">
-        <v>6998416</v>
+        <v>6998336</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3529,6 +3485,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3555,10 +3516,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122818503</v>
+        <v>122817645</v>
       </c>
       <c r="B26" t="n">
-        <v>57478</v>
+        <v>57499</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3567,46 +3528,50 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>100110</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528652</v>
+        <v>528643</v>
       </c>
       <c r="R26" t="n">
-        <v>6998555</v>
+        <v>6998354</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3633,14 +3598,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3655,19 +3625,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122817554</v>
+        <v>122818174</v>
       </c>
       <c r="B27" t="n">
         <v>57478</v>
@@ -3712,10 +3682,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528648</v>
+        <v>528625</v>
       </c>
       <c r="R27" t="n">
-        <v>6998359</v>
+        <v>6998500</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3752,7 +3722,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3779,10 +3749,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122817601</v>
+        <v>122818204</v>
       </c>
       <c r="B28" t="n">
-        <v>90972</v>
+        <v>79847</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3795,21 +3765,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3819,13 +3789,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528645</v>
+        <v>528649</v>
       </c>
       <c r="R28" t="n">
-        <v>6998384</v>
+        <v>6998490</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3852,9 +3822,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På innerbark på gammal björkhögstubbe i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3869,22 +3854,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122816987</v>
+        <v>122817546</v>
       </c>
       <c r="B29" t="n">
-        <v>79384</v>
+        <v>74863</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3897,21 +3882,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3921,13 +3906,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528755</v>
+        <v>528628</v>
       </c>
       <c r="R29" t="n">
-        <v>6998446</v>
+        <v>6998367</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3956,7 +3941,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3966,12 +3951,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På bränd jöttetallstubbe</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3986,12 +3971,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4124,10 +4109,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122817339</v>
+        <v>122817186</v>
       </c>
       <c r="B31" t="n">
-        <v>79384</v>
+        <v>57428</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4136,41 +4121,55 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>102621</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528649</v>
+        <v>528689</v>
       </c>
       <c r="R31" t="n">
-        <v>6998383</v>
+        <v>6998416</v>
       </c>
       <c r="S31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4197,24 +4196,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4229,22 +4213,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122817937</v>
+        <v>122818247</v>
       </c>
       <c r="B32" t="n">
-        <v>90963</v>
+        <v>78766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4253,25 +4237,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4281,13 +4265,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528686</v>
+        <v>528605</v>
       </c>
       <c r="R32" t="n">
-        <v>6998446</v>
+        <v>6998454</v>
       </c>
       <c r="S32" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4314,26 +4298,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På död asp</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4342,26 +4311,51 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122819379</v>
+        <v>122817142</v>
       </c>
       <c r="B33" t="n">
-        <v>98365</v>
+        <v>57478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4370,35 +4364,31 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4407,13 +4397,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528802</v>
+        <v>528699</v>
       </c>
       <c r="R33" t="n">
-        <v>6998594</v>
+        <v>6998430</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4440,24 +4430,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4472,22 +4452,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122817714</v>
+        <v>122817517</v>
       </c>
       <c r="B34" t="n">
-        <v>74863</v>
+        <v>78411</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4500,21 +4480,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4524,13 +4504,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528625</v>
+        <v>528643</v>
       </c>
       <c r="R34" t="n">
-        <v>6998424</v>
+        <v>6998354</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4559,7 +4539,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4569,12 +4549,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På ved på gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4589,19 +4569,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122817110</v>
+        <v>122818165</v>
       </c>
       <c r="B35" t="n">
         <v>78766</v>
@@ -4641,13 +4621,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528711</v>
+        <v>528594</v>
       </c>
       <c r="R35" t="n">
-        <v>6998430</v>
+        <v>6998419</v>
       </c>
       <c r="S35" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4674,26 +4654,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>09:11</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>09:11</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4702,26 +4667,51 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122818026</v>
+        <v>122817054</v>
       </c>
       <c r="B36" t="n">
-        <v>79847</v>
+        <v>79751</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4730,25 +4720,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4758,10 +4748,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528631</v>
+        <v>528755</v>
       </c>
       <c r="R36" t="n">
-        <v>6998469</v>
+        <v>6998448</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4791,9 +4781,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4808,22 +4813,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122818025</v>
+        <v>122817278</v>
       </c>
       <c r="B37" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4836,34 +4841,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528631</v>
+        <v>528671</v>
       </c>
       <c r="R37" t="n">
-        <v>6998469</v>
+        <v>6998337</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4896,6 +4906,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4922,10 +4937,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122817645</v>
+        <v>122817037</v>
       </c>
       <c r="B38" t="n">
-        <v>57499</v>
+        <v>57478</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4934,35 +4949,36 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100110</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4971,13 +4987,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528643</v>
+        <v>528752</v>
       </c>
       <c r="R38" t="n">
-        <v>6998354</v>
+        <v>6998456</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5004,19 +5020,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>09:45</t>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5027,26 +5038,51 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122817142</v>
+        <v>122818613</v>
       </c>
       <c r="B39" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5055,31 +5091,40 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5088,13 +5133,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528699</v>
+        <v>528723</v>
       </c>
       <c r="R39" t="n">
-        <v>6998430</v>
+        <v>6998554</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5121,14 +5166,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5143,22 +5198,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122818036</v>
+        <v>122818035</v>
       </c>
       <c r="B40" t="n">
-        <v>79751</v>
+        <v>79807</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5171,21 +5226,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5195,13 +5250,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528686</v>
+        <v>528677</v>
       </c>
       <c r="R40" t="n">
-        <v>6998471</v>
+        <v>6998487</v>
       </c>
       <c r="S40" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5230,7 +5285,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5240,12 +5295,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5260,22 +5315,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122818321</v>
+        <v>122818328</v>
       </c>
       <c r="B41" t="n">
-        <v>74863</v>
+        <v>77699</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5288,21 +5343,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5312,13 +5367,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528805</v>
+        <v>528800</v>
       </c>
       <c r="R41" t="n">
-        <v>6998631</v>
+        <v>6998633</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5389,10 +5444,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122817112</v>
+        <v>122817758</v>
       </c>
       <c r="B42" t="n">
-        <v>78766</v>
+        <v>77699</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5405,46 +5460,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528711</v>
+        <v>528610</v>
       </c>
       <c r="R42" t="n">
-        <v>6998411</v>
+        <v>6998403</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5473,7 +5519,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5483,12 +5529,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5515,10 +5561,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122818573</v>
+        <v>122817289</v>
       </c>
       <c r="B43" t="n">
-        <v>78766</v>
+        <v>79145</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5531,37 +5577,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>257107</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blek lundlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bacidia rosellizans</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>S.Ekman</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528630</v>
+        <v>528632</v>
       </c>
       <c r="R43" t="n">
-        <v>6998539</v>
+        <v>6998403</v>
       </c>
       <c r="S43" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5588,11 +5634,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5601,51 +5662,26 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122817413</v>
+        <v>122816987</v>
       </c>
       <c r="B44" t="n">
-        <v>57478</v>
+        <v>79384</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5658,42 +5694,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528612</v>
+        <v>528755</v>
       </c>
       <c r="R44" t="n">
-        <v>6998323</v>
+        <v>6998446</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5720,14 +5751,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På bränd jöttetallstubbe</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5742,22 +5783,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122818654</v>
+        <v>122818573</v>
       </c>
       <c r="B45" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5770,42 +5811,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528711</v>
+        <v>528630</v>
       </c>
       <c r="R45" t="n">
-        <v>6998632</v>
+        <v>6998539</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5837,11 +5873,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5850,6 +5881,31 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5866,10 +5922,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122816979</v>
+        <v>122816988</v>
       </c>
       <c r="B46" t="n">
-        <v>78503</v>
+        <v>57478</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5882,34 +5938,44 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528730</v>
+        <v>528756</v>
       </c>
       <c r="R46" t="n">
-        <v>6998447</v>
+        <v>6998450</v>
       </c>
       <c r="S46" t="n">
         <v>8</v>
@@ -5939,24 +6005,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>09:03</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>09:03</t>
-        </is>
-      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På kolad ved</t>
+          <t>Äldre ringhack på en tall.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5967,26 +6023,51 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122817546</v>
+        <v>122818653</v>
       </c>
       <c r="B47" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5999,21 +6080,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6023,10 +6104,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528628</v>
+        <v>528732</v>
       </c>
       <c r="R47" t="n">
-        <v>6998367</v>
+        <v>6998541</v>
       </c>
       <c r="S47" t="n">
         <v>8</v>
@@ -6058,7 +6139,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6068,12 +6149,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På asplåga i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6088,22 +6169,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122817054</v>
+        <v>122818025</v>
       </c>
       <c r="B48" t="n">
-        <v>79751</v>
+        <v>79848</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6112,25 +6193,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6140,10 +6221,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528755</v>
+        <v>528631</v>
       </c>
       <c r="R48" t="n">
-        <v>6998448</v>
+        <v>6998469</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6173,24 +6254,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>09:08</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>09:08</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6205,22 +6271,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122818040</v>
+        <v>122817869</v>
       </c>
       <c r="B49" t="n">
-        <v>78766</v>
+        <v>57499</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6229,41 +6295,50 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100110</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528621</v>
+        <v>528645</v>
       </c>
       <c r="R49" t="n">
-        <v>6998383</v>
+        <v>6998384</v>
       </c>
       <c r="S49" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6303,31 +6378,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6344,10 +6394,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122818675</v>
+        <v>122816979</v>
       </c>
       <c r="B50" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6360,46 +6410,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528722</v>
+        <v>528730</v>
       </c>
       <c r="R50" t="n">
-        <v>6998660</v>
+        <v>6998447</v>
       </c>
       <c r="S50" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6428,7 +6469,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6438,7 +6479,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På kolad ved</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6465,10 +6511,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122818122</v>
+        <v>122818864</v>
       </c>
       <c r="B51" t="n">
-        <v>79848</v>
+        <v>74863</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6481,21 +6527,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6505,13 +6551,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528631</v>
+        <v>528732</v>
       </c>
       <c r="R51" t="n">
-        <v>6998473</v>
+        <v>6998659</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6538,9 +6584,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6555,22 +6616,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122818864</v>
+        <v>122818026</v>
       </c>
       <c r="B52" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6583,21 +6644,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6607,13 +6668,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>528732</v>
+        <v>528631</v>
       </c>
       <c r="R52" t="n">
-        <v>6998659</v>
+        <v>6998469</v>
       </c>
       <c r="S52" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6640,24 +6701,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6672,22 +6718,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122818247</v>
+        <v>122819397</v>
       </c>
       <c r="B53" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6700,34 +6746,43 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>528605</v>
+        <v>528826</v>
       </c>
       <c r="R53" t="n">
-        <v>6998454</v>
+        <v>6998595</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6770,31 +6825,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6811,7 +6841,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122817550</v>
+        <v>122817554</v>
       </c>
       <c r="B54" t="n">
         <v>57478</v>
@@ -6859,7 +6889,7 @@
         <v>528648</v>
       </c>
       <c r="R54" t="n">
-        <v>6998358</v>
+        <v>6998359</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6896,7 +6926,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6923,10 +6953,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122817278</v>
+        <v>122819033</v>
       </c>
       <c r="B55" t="n">
-        <v>57478</v>
+        <v>74675</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6935,46 +6965,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6428</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>528671</v>
+        <v>528798</v>
       </c>
       <c r="R55" t="n">
-        <v>6998337</v>
+        <v>6998603</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7001,14 +7026,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På bark på stam av levande gammal sälg i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7023,22 +7058,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122818713</v>
+        <v>122819118</v>
       </c>
       <c r="B56" t="n">
-        <v>90952</v>
+        <v>78766</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7051,21 +7086,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7075,13 +7110,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>528718</v>
+        <v>528690</v>
       </c>
       <c r="R56" t="n">
-        <v>6998641</v>
+        <v>6998652</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7113,6 +7148,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7121,6 +7161,31 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7137,7 +7202,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122818653</v>
+        <v>122818759</v>
       </c>
       <c r="B57" t="n">
         <v>79847</v>
@@ -7177,13 +7242,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>528732</v>
+        <v>528778</v>
       </c>
       <c r="R57" t="n">
-        <v>6998541</v>
+        <v>6998602</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7212,7 +7277,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7222,12 +7287,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På asplåga i gammal barrblandskog</t>
+          <t>På gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7254,10 +7319,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122817037</v>
+        <v>122818032</v>
       </c>
       <c r="B58" t="n">
-        <v>57478</v>
+        <v>79876</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7266,51 +7331,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>528752</v>
+        <v>528631</v>
       </c>
       <c r="R58" t="n">
-        <v>6998456</v>
+        <v>6998469</v>
       </c>
       <c r="S58" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7342,11 +7397,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7355,31 +7405,6 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7396,7 +7421,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122817144</v>
+        <v>122819058</v>
       </c>
       <c r="B59" t="n">
         <v>78766</v>
@@ -7429,29 +7454,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>528705</v>
+        <v>528654</v>
       </c>
       <c r="R59" t="n">
-        <v>6998384</v>
+        <v>6998628</v>
       </c>
       <c r="S59" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7478,21 +7494,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -7501,26 +7507,51 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122818681</v>
+        <v>122818536</v>
       </c>
       <c r="B60" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7533,37 +7564,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>528686</v>
+        <v>528665</v>
       </c>
       <c r="R60" t="n">
-        <v>6998618</v>
+        <v>6998574</v>
       </c>
       <c r="S60" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7595,6 +7631,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -7603,31 +7644,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7644,10 +7660,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122818032</v>
+        <v>122817110</v>
       </c>
       <c r="B61" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7656,25 +7672,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7684,13 +7700,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>528631</v>
+        <v>528711</v>
       </c>
       <c r="R61" t="n">
-        <v>6998469</v>
+        <v>6998430</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7717,9 +7733,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7734,22 +7765,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122819118</v>
+        <v>122817339</v>
       </c>
       <c r="B62" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7762,37 +7793,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>528690</v>
+        <v>528649</v>
       </c>
       <c r="R62" t="n">
-        <v>6998652</v>
+        <v>6998383</v>
       </c>
       <c r="S62" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7819,14 +7850,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7837,51 +7878,26 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122818613</v>
+        <v>122818770</v>
       </c>
       <c r="B63" t="n">
-        <v>98365</v>
+        <v>91243</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7890,55 +7906,41 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>528723</v>
+        <v>528718</v>
       </c>
       <c r="R63" t="n">
-        <v>6998554</v>
+        <v>6998641</v>
       </c>
       <c r="S63" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7965,24 +7967,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7997,22 +7984,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122818323</v>
+        <v>122817112</v>
       </c>
       <c r="B64" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8025,37 +8012,46 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>528667</v>
+        <v>528711</v>
       </c>
       <c r="R64" t="n">
-        <v>6998534</v>
+        <v>6998411</v>
       </c>
       <c r="S64" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8084,7 +8080,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8094,12 +8090,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Rikligt på bark på stam av levande gammal sälg i gammal barrblandskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8114,22 +8110,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122817758</v>
+        <v>122819379</v>
       </c>
       <c r="B65" t="n">
-        <v>77699</v>
+        <v>98365</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8138,41 +8134,50 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>528610</v>
+        <v>528802</v>
       </c>
       <c r="R65" t="n">
-        <v>6998403</v>
+        <v>6998594</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8201,7 +8206,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8211,12 +8216,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8231,22 +8236,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122817869</v>
+        <v>122817714</v>
       </c>
       <c r="B66" t="n">
-        <v>57499</v>
+        <v>74863</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8255,50 +8260,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100110</v>
+        <v>6440</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>528645</v>
+        <v>528625</v>
       </c>
       <c r="R66" t="n">
-        <v>6998384</v>
+        <v>6998424</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8325,9 +8321,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8342,22 +8353,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122818534</v>
+        <v>122818675</v>
       </c>
       <c r="B67" t="n">
-        <v>79813</v>
+        <v>78766</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8366,31 +8377,35 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8399,13 +8414,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>528727</v>
+        <v>528722</v>
       </c>
       <c r="R67" t="n">
-        <v>6998595</v>
+        <v>6998660</v>
       </c>
       <c r="S67" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8434,7 +8449,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8444,12 +8459,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:23</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På gammal asp</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8476,10 +8486,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122818035</v>
+        <v>122817601</v>
       </c>
       <c r="B68" t="n">
-        <v>79807</v>
+        <v>90972</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8488,25 +8498,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>229497</v>
+        <v>5442</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8516,10 +8526,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>528677</v>
+        <v>528645</v>
       </c>
       <c r="R68" t="n">
-        <v>6998487</v>
+        <v>6998384</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8549,24 +8559,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8581,22 +8576,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122818126</v>
+        <v>122818125</v>
       </c>
       <c r="B69" t="n">
-        <v>79847</v>
+        <v>78503</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8609,21 +8604,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8633,7 +8628,7 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>528624</v>
+        <v>528687</v>
       </c>
       <c r="R69" t="n">
         <v>6998489</v>
@@ -8666,9 +8661,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal tallstubbe i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8683,22 +8693,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122817657</v>
+        <v>122818036</v>
       </c>
       <c r="B70" t="n">
-        <v>78766</v>
+        <v>79751</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8707,25 +8717,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8735,13 +8745,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>528650</v>
+        <v>528686</v>
       </c>
       <c r="R70" t="n">
-        <v>6998397</v>
+        <v>6998471</v>
       </c>
       <c r="S70" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8768,14 +8778,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8786,51 +8806,26 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122817325</v>
+        <v>122818321</v>
       </c>
       <c r="B71" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8843,39 +8838,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>528640</v>
+        <v>528805</v>
       </c>
       <c r="R71" t="n">
-        <v>6998336</v>
+        <v>6998631</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8905,14 +8895,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8927,22 +8927,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122818328</v>
+        <v>122817937</v>
       </c>
       <c r="B72" t="n">
-        <v>77699</v>
+        <v>90963</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8951,25 +8951,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228579</v>
+        <v>1205</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8979,13 +8979,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>528800</v>
+        <v>528686</v>
       </c>
       <c r="R72" t="n">
-        <v>6998633</v>
+        <v>6998446</v>
       </c>
       <c r="S72" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9024,12 +9024,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På död asp</t>
         </is>
       </c>
       <c r="AD72" t="b">

--- a/artfynd/A 55431-2024 artfynd.xlsx
+++ b/artfynd/A 55431-2024 artfynd.xlsx
@@ -1147,7 +1147,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122817144</v>
+        <v>122819024</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1180,29 +1180,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528705</v>
+        <v>528636</v>
       </c>
       <c r="R6" t="n">
-        <v>6998384</v>
+        <v>6998609</v>
       </c>
       <c r="S6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1229,21 +1220,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1252,26 +1233,51 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Dead branch  # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122819024</v>
+        <v>122818654</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1284,37 +1290,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528636</v>
+        <v>528711</v>
       </c>
       <c r="R7" t="n">
-        <v>6998609</v>
+        <v>6998632</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1346,6 +1357,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1354,31 +1370,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Dead branch  # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1395,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122818654</v>
+        <v>122817144</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1411,42 +1402,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528711</v>
+        <v>528705</v>
       </c>
       <c r="R8" t="n">
-        <v>6998632</v>
+        <v>6998384</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1473,14 +1468,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1495,12 +1495,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1609,10 +1609,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122818955</v>
+        <v>122818323</v>
       </c>
       <c r="B10" t="n">
-        <v>74786</v>
+        <v>79847</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1625,42 +1625,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1460</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528791</v>
+        <v>528667</v>
       </c>
       <c r="R10" t="n">
-        <v>6998633</v>
+        <v>6998534</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1689,7 +1684,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1699,12 +1694,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Rikligt på bark på stam av levande gammal sälg i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,22 +1714,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122818323</v>
+        <v>122818387</v>
       </c>
       <c r="B11" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1747,21 +1742,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1771,13 +1766,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528667</v>
+        <v>528619</v>
       </c>
       <c r="R11" t="n">
-        <v>6998534</v>
+        <v>6998495</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1804,26 +1799,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt på bark på stam av levande gammal sälg i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1832,23 +1812,48 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122818387</v>
+        <v>122817657</v>
       </c>
       <c r="B12" t="n">
         <v>78766</v>
@@ -1888,13 +1893,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528619</v>
+        <v>528650</v>
       </c>
       <c r="R12" t="n">
-        <v>6998495</v>
+        <v>6998397</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1924,6 +1929,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1975,10 +1985,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122817657</v>
+        <v>122818955</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>74786</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1991,37 +2001,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1460</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528650</v>
+        <v>528791</v>
       </c>
       <c r="R13" t="n">
-        <v>6998397</v>
+        <v>6998633</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2048,14 +2063,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2066,41 +2091,16 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -6394,10 +6394,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122816979</v>
+        <v>122817554</v>
       </c>
       <c r="B50" t="n">
-        <v>78503</v>
+        <v>57478</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6410,37 +6410,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528730</v>
+        <v>528648</v>
       </c>
       <c r="R50" t="n">
-        <v>6998447</v>
+        <v>6998359</v>
       </c>
       <c r="S50" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6467,24 +6472,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>09:03</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>09:03</t>
-        </is>
-      </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På kolad ved</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6499,12 +6494,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6841,10 +6836,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122817554</v>
+        <v>122816979</v>
       </c>
       <c r="B54" t="n">
-        <v>57478</v>
+        <v>78503</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6857,42 +6852,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>528648</v>
+        <v>528730</v>
       </c>
       <c r="R54" t="n">
-        <v>6998359</v>
+        <v>6998447</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6919,14 +6909,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På kolad ved</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6941,12 +6941,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -8248,10 +8248,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122817714</v>
+        <v>122818125</v>
       </c>
       <c r="B66" t="n">
-        <v>74863</v>
+        <v>78503</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8264,21 +8264,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8288,13 +8288,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>528625</v>
+        <v>528687</v>
       </c>
       <c r="R66" t="n">
-        <v>6998424</v>
+        <v>6998489</v>
       </c>
       <c r="S66" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8333,12 +8333,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På kolad ved på gammal tallstubbe i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8353,22 +8353,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122818675</v>
+        <v>122817714</v>
       </c>
       <c r="B67" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8381,46 +8381,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>528722</v>
+        <v>528625</v>
       </c>
       <c r="R67" t="n">
-        <v>6998660</v>
+        <v>6998424</v>
       </c>
       <c r="S67" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8449,7 +8440,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8459,7 +8450,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8486,10 +8482,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122817601</v>
+        <v>122818675</v>
       </c>
       <c r="B68" t="n">
-        <v>90972</v>
+        <v>78766</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8502,37 +8498,46 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>528645</v>
+        <v>528722</v>
       </c>
       <c r="R68" t="n">
-        <v>6998384</v>
+        <v>6998660</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8559,9 +8564,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8576,22 +8591,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122818125</v>
+        <v>122817601</v>
       </c>
       <c r="B69" t="n">
-        <v>78503</v>
+        <v>90972</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8604,21 +8619,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8628,10 +8643,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>528687</v>
+        <v>528645</v>
       </c>
       <c r="R69" t="n">
-        <v>6998489</v>
+        <v>6998384</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8661,24 +8676,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På kolad ved på gammal tallstubbe i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8693,12 +8693,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>

--- a/artfynd/A 55431-2024 artfynd.xlsx
+++ b/artfynd/A 55431-2024 artfynd.xlsx
@@ -1609,10 +1609,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122818323</v>
+        <v>122818955</v>
       </c>
       <c r="B10" t="n">
-        <v>79847</v>
+        <v>74786</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1625,37 +1625,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>1460</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528667</v>
+        <v>528791</v>
       </c>
       <c r="R10" t="n">
-        <v>6998534</v>
+        <v>6998633</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1684,7 +1689,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1694,12 +1699,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt på bark på stam av levande gammal sälg i gammal barrblandskog</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1714,22 +1719,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122818387</v>
+        <v>122818323</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1742,21 +1747,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1766,13 +1771,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528619</v>
+        <v>528667</v>
       </c>
       <c r="R11" t="n">
-        <v>6998495</v>
+        <v>6998534</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1799,11 +1804,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt på bark på stam av levande gammal sälg i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1812,48 +1832,23 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122817657</v>
+        <v>122818387</v>
       </c>
       <c r="B12" t="n">
         <v>78766</v>
@@ -1893,13 +1888,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528650</v>
+        <v>528619</v>
       </c>
       <c r="R12" t="n">
-        <v>6998397</v>
+        <v>6998495</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1929,11 +1924,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1985,10 +1975,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122818955</v>
+        <v>122817657</v>
       </c>
       <c r="B13" t="n">
-        <v>74786</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2001,42 +1991,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1460</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528791</v>
+        <v>528650</v>
       </c>
       <c r="R13" t="n">
-        <v>6998633</v>
+        <v>6998397</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2063,24 +2048,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2091,16 +2066,41 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -7548,10 +7548,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122818536</v>
+        <v>122817110</v>
       </c>
       <c r="B60" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7564,42 +7564,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>528665</v>
+        <v>528711</v>
       </c>
       <c r="R60" t="n">
-        <v>6998574</v>
+        <v>6998430</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7626,14 +7621,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7648,22 +7653,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122817110</v>
+        <v>122818536</v>
       </c>
       <c r="B61" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7676,37 +7681,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>528711</v>
+        <v>528665</v>
       </c>
       <c r="R61" t="n">
-        <v>6998430</v>
+        <v>6998574</v>
       </c>
       <c r="S61" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7733,24 +7743,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>09:11</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>09:11</t>
-        </is>
-      </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7765,12 +7765,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>

--- a/artfynd/A 55431-2024 artfynd.xlsx
+++ b/artfynd/A 55431-2024 artfynd.xlsx
@@ -7777,10 +7777,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122817339</v>
+        <v>122818770</v>
       </c>
       <c r="B62" t="n">
-        <v>79384</v>
+        <v>91243</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7793,37 +7793,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>658</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>528649</v>
+        <v>528718</v>
       </c>
       <c r="R62" t="n">
-        <v>6998383</v>
+        <v>6998641</v>
       </c>
       <c r="S62" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7850,24 +7850,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>På gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7882,22 +7867,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122818770</v>
+        <v>122817339</v>
       </c>
       <c r="B63" t="n">
-        <v>91243</v>
+        <v>79384</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7910,37 +7895,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>658</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>528718</v>
+        <v>528649</v>
       </c>
       <c r="R63" t="n">
-        <v>6998641</v>
+        <v>6998383</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7967,9 +7952,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>På gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7984,12 +7984,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>

--- a/artfynd/A 55431-2024 artfynd.xlsx
+++ b/artfynd/A 55431-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122818681</v>
+        <v>122818503</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,37 +802,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528686</v>
+        <v>528652</v>
       </c>
       <c r="R3" t="n">
-        <v>6998618</v>
+        <v>6998555</v>
       </c>
       <c r="S3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,6 +869,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -872,31 +882,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -913,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122818503</v>
+        <v>122818681</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,42 +914,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528652</v>
+        <v>528686</v>
       </c>
       <c r="R4" t="n">
-        <v>6998555</v>
+        <v>6998618</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,11 +976,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1009,6 +984,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">

--- a/artfynd/A 55431-2024 artfynd.xlsx
+++ b/artfynd/A 55431-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122818503</v>
+        <v>122817037</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -825,19 +825,24 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528652</v>
+        <v>528752</v>
       </c>
       <c r="R3" t="n">
-        <v>6998555</v>
+        <v>6998456</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +876,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,6 +887,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -898,10 +928,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122818681</v>
+        <v>122819379</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>98368</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,41 +940,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528686</v>
+        <v>528802</v>
       </c>
       <c r="R4" t="n">
-        <v>6998618</v>
+        <v>6998594</v>
       </c>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,11 +1010,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På marken i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -984,41 +1038,16 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1028,7 +1057,7 @@
         <v>122818534</v>
       </c>
       <c r="B5" t="n">
-        <v>79813</v>
+        <v>79816</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1147,10 +1176,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122819024</v>
+        <v>122817110</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1183,14 +1212,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528636</v>
+        <v>528711</v>
       </c>
       <c r="R6" t="n">
-        <v>6998609</v>
+        <v>6998430</v>
       </c>
       <c r="S6" t="n">
         <v>12</v>
@@ -1220,11 +1249,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1233,51 +1277,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Dead branch  # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122818654</v>
+        <v>122818864</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>74866</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1290,42 +1309,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528711</v>
+        <v>528732</v>
       </c>
       <c r="R7" t="n">
-        <v>6998632</v>
+        <v>6998659</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1352,14 +1366,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,22 +1398,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122817144</v>
+        <v>122818025</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>79851</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1402,46 +1426,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528705</v>
+        <v>528631</v>
       </c>
       <c r="R8" t="n">
-        <v>6998384</v>
+        <v>6998469</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1468,19 +1483,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>09:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1495,22 +1500,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122818126</v>
+        <v>122817758</v>
       </c>
       <c r="B9" t="n">
-        <v>79847</v>
+        <v>77702</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1523,21 +1528,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1547,10 +1552,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528624</v>
+        <v>528610</v>
       </c>
       <c r="R9" t="n">
-        <v>6998489</v>
+        <v>6998403</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1580,9 +1585,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1597,22 +1617,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122818955</v>
+        <v>122818040</v>
       </c>
       <c r="B10" t="n">
-        <v>74786</v>
+        <v>78769</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1625,42 +1645,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1460</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528791</v>
+        <v>528621</v>
       </c>
       <c r="R10" t="n">
-        <v>6998633</v>
+        <v>6998383</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1687,26 +1702,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1715,26 +1715,51 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122818323</v>
+        <v>122817554</v>
       </c>
       <c r="B11" t="n">
-        <v>79847</v>
+        <v>57481</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1747,37 +1772,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528667</v>
+        <v>528648</v>
       </c>
       <c r="R11" t="n">
-        <v>6998534</v>
+        <v>6998359</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1804,24 +1834,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt på bark på stam av levande gammal sälg i gammal barrblandskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1836,22 +1856,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122818387</v>
+        <v>122817937</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>90966</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1860,25 +1880,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1888,13 +1908,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528619</v>
+        <v>528686</v>
       </c>
       <c r="R12" t="n">
-        <v>6998495</v>
+        <v>6998446</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1921,11 +1941,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På död asp</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1934,51 +1969,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122817657</v>
+        <v>122818681</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2011,17 +2021,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528650</v>
+        <v>528686</v>
       </c>
       <c r="R13" t="n">
-        <v>6998397</v>
+        <v>6998618</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2051,11 +2061,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2107,10 +2112,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122817942</v>
+        <v>122817546</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>74866</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2123,42 +2128,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528655</v>
+        <v>528628</v>
       </c>
       <c r="R14" t="n">
-        <v>6998433</v>
+        <v>6998367</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2185,14 +2185,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2207,22 +2217,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122817550</v>
+        <v>122818126</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2235,39 +2245,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528648</v>
+        <v>528624</v>
       </c>
       <c r="R15" t="n">
-        <v>6998358</v>
+        <v>6998489</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2300,11 +2305,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2331,10 +2331,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122818168</v>
+        <v>122817186</v>
       </c>
       <c r="B16" t="n">
-        <v>79807</v>
+        <v>57431</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2347,34 +2347,48 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229497</v>
+        <v>102621</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528669</v>
+        <v>528689</v>
       </c>
       <c r="R16" t="n">
-        <v>6998500</v>
+        <v>6998416</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2404,26 +2418,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På bark på stam av död gammal asp (40 cm dbh) i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2432,41 +2431,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122818713</v>
+        <v>122818035</v>
       </c>
       <c r="B17" t="n">
-        <v>90952</v>
+        <v>79810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2475,38 +2459,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528718</v>
+        <v>528677</v>
       </c>
       <c r="R17" t="n">
-        <v>6998641</v>
+        <v>6998487</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2536,9 +2520,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2553,22 +2552,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122818514</v>
+        <v>122818654</v>
       </c>
       <c r="B18" t="n">
-        <v>74863</v>
+        <v>57481</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2581,34 +2580,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528635</v>
+        <v>528711</v>
       </c>
       <c r="R18" t="n">
-        <v>6998546</v>
+        <v>6998632</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2641,6 +2645,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2667,10 +2676,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122819448</v>
+        <v>122818032</v>
       </c>
       <c r="B19" t="n">
-        <v>79876</v>
+        <v>79879</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2701,21 +2710,16 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528696</v>
+        <v>528631</v>
       </c>
       <c r="R19" t="n">
-        <v>6998688</v>
+        <v>6998469</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2750,11 +2754,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Frodiga bålar.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2763,21 +2762,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2794,10 +2778,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122818122</v>
+        <v>122817144</v>
       </c>
       <c r="B20" t="n">
-        <v>79848</v>
+        <v>78769</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2810,37 +2794,46 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528631</v>
+        <v>528705</v>
       </c>
       <c r="R20" t="n">
-        <v>6998473</v>
+        <v>6998384</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2867,9 +2860,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2884,22 +2887,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122817413</v>
+        <v>122818036</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>79754</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2908,46 +2911,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528612</v>
+        <v>528686</v>
       </c>
       <c r="R21" t="n">
-        <v>6998323</v>
+        <v>6998471</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2974,14 +2972,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2996,22 +3004,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122818040</v>
+        <v>122819033</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>74678</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3020,25 +3028,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3048,13 +3056,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528621</v>
+        <v>528798</v>
       </c>
       <c r="R22" t="n">
-        <v>6998383</v>
+        <v>6998603</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3081,11 +3089,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal sälg i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3094,51 +3117,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122818966</v>
+        <v>122817219</v>
       </c>
       <c r="B23" t="n">
-        <v>79847</v>
+        <v>78769</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3151,39 +3149,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528791</v>
+        <v>528684</v>
       </c>
       <c r="R23" t="n">
-        <v>6998599</v>
+        <v>6998437</v>
       </c>
       <c r="S23" t="n">
         <v>8</v>
@@ -3213,24 +3206,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg (25 cm dbh) i gammal barrblandskog</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3242,40 +3225,50 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122817219</v>
+        <v>122817657</v>
       </c>
       <c r="B24" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3312,13 +3305,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528684</v>
+        <v>528650</v>
       </c>
       <c r="R24" t="n">
-        <v>6998437</v>
+        <v>6998397</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3404,10 +3397,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122817325</v>
+        <v>122817714</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>74866</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3420,42 +3413,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528640</v>
+        <v>528625</v>
       </c>
       <c r="R25" t="n">
-        <v>6998336</v>
+        <v>6998424</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3482,14 +3470,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3504,22 +3502,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122817645</v>
+        <v>122818165</v>
       </c>
       <c r="B26" t="n">
-        <v>57499</v>
+        <v>78769</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3528,50 +3526,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100110</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528643</v>
+        <v>528594</v>
       </c>
       <c r="R26" t="n">
-        <v>6998354</v>
+        <v>6998419</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3598,21 +3587,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3621,26 +3600,51 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122818174</v>
+        <v>122818966</v>
       </c>
       <c r="B27" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3653,27 +3657,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3682,13 +3686,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528625</v>
+        <v>528791</v>
       </c>
       <c r="R27" t="n">
-        <v>6998500</v>
+        <v>6998599</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3715,14 +3719,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På bark på stam av levande gammal sälg (25 cm dbh) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3733,26 +3747,41 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122818204</v>
+        <v>122818321</v>
       </c>
       <c r="B28" t="n">
-        <v>79847</v>
+        <v>74866</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3765,21 +3794,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3789,13 +3818,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528649</v>
+        <v>528805</v>
       </c>
       <c r="R28" t="n">
-        <v>6998490</v>
+        <v>6998631</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3824,7 +3853,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3834,12 +3863,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På innerbark på gammal björkhögstubbe i gammal barrblandskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3854,22 +3883,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122817546</v>
+        <v>122818387</v>
       </c>
       <c r="B29" t="n">
-        <v>74863</v>
+        <v>78769</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3882,21 +3911,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3906,13 +3935,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528628</v>
+        <v>528619</v>
       </c>
       <c r="R29" t="n">
-        <v>6998367</v>
+        <v>6998495</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3939,26 +3968,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3967,26 +3981,51 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122817273</v>
+        <v>122818653</v>
       </c>
       <c r="B30" t="n">
-        <v>78766</v>
+        <v>79850</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3999,46 +4038,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528623</v>
+        <v>528732</v>
       </c>
       <c r="R30" t="n">
-        <v>6998311</v>
+        <v>6998541</v>
       </c>
       <c r="S30" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4067,7 +4097,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4077,12 +4107,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På asplåga i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4097,22 +4127,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122817186</v>
+        <v>122819118</v>
       </c>
       <c r="B31" t="n">
-        <v>57428</v>
+        <v>78769</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4121,55 +4151,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102621</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528689</v>
+        <v>528690</v>
       </c>
       <c r="R31" t="n">
-        <v>6998416</v>
+        <v>6998652</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4201,6 +4217,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4209,6 +4230,31 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4225,10 +4271,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122818247</v>
+        <v>122816987</v>
       </c>
       <c r="B32" t="n">
-        <v>78766</v>
+        <v>79387</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4241,21 +4287,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4265,13 +4311,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528605</v>
+        <v>528755</v>
       </c>
       <c r="R32" t="n">
-        <v>6998454</v>
+        <v>6998446</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4298,11 +4344,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På bränd jöttetallstubbe</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4311,51 +4372,26 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122817142</v>
+        <v>122817413</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4397,10 +4433,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528699</v>
+        <v>528612</v>
       </c>
       <c r="R33" t="n">
-        <v>6998430</v>
+        <v>6998323</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4437,7 +4473,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4464,10 +4500,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122817517</v>
+        <v>122818174</v>
       </c>
       <c r="B34" t="n">
-        <v>78411</v>
+        <v>57481</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4480,34 +4516,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528643</v>
+        <v>528625</v>
       </c>
       <c r="R34" t="n">
-        <v>6998354</v>
+        <v>6998500</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4537,24 +4578,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På ved på gammal tallstubbe</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4569,22 +4600,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122818165</v>
+        <v>122818323</v>
       </c>
       <c r="B35" t="n">
-        <v>78766</v>
+        <v>79850</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4597,21 +4628,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4621,13 +4652,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528594</v>
+        <v>528667</v>
       </c>
       <c r="R35" t="n">
-        <v>6998419</v>
+        <v>6998534</v>
       </c>
       <c r="S35" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4654,11 +4685,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Rikligt på bark på stam av levande gammal sälg i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4667,51 +4713,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122817054</v>
+        <v>122817273</v>
       </c>
       <c r="B36" t="n">
-        <v>79751</v>
+        <v>78769</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4720,41 +4741,50 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528755</v>
+        <v>528623</v>
       </c>
       <c r="R36" t="n">
-        <v>6998448</v>
+        <v>6998311</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4783,7 +4813,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4793,12 +4823,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4813,22 +4843,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122817278</v>
+        <v>122817601</v>
       </c>
       <c r="B37" t="n">
-        <v>57478</v>
+        <v>90975</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4841,39 +4871,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528671</v>
+        <v>528645</v>
       </c>
       <c r="R37" t="n">
-        <v>6998337</v>
+        <v>6998384</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4906,11 +4931,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4937,10 +4957,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122817037</v>
+        <v>122819448</v>
       </c>
       <c r="B38" t="n">
-        <v>57478</v>
+        <v>79879</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4949,51 +4969,46 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528752</v>
+        <v>528696</v>
       </c>
       <c r="R38" t="n">
-        <v>6998456</v>
+        <v>6998688</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5027,7 +5042,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall.</t>
+          <t>Frodiga bålar.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5041,27 +5056,17 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Sten/berg på land</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Stone/rock on land</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5079,10 +5084,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122818613</v>
+        <v>122819024</v>
       </c>
       <c r="B39" t="n">
-        <v>98365</v>
+        <v>78769</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5091,55 +5096,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528723</v>
+        <v>528636</v>
       </c>
       <c r="R39" t="n">
-        <v>6998554</v>
+        <v>6998609</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5166,26 +5157,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På marken i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5194,26 +5170,51 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Dead branch  # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122818035</v>
+        <v>122818536</v>
       </c>
       <c r="B40" t="n">
-        <v>79807</v>
+        <v>57481</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5222,38 +5223,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528677</v>
+        <v>528665</v>
       </c>
       <c r="R40" t="n">
-        <v>6998487</v>
+        <v>6998574</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5283,24 +5289,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5315,22 +5311,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122818328</v>
+        <v>122818514</v>
       </c>
       <c r="B41" t="n">
-        <v>77699</v>
+        <v>74866</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5343,37 +5339,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528800</v>
+        <v>528635</v>
       </c>
       <c r="R41" t="n">
-        <v>6998633</v>
+        <v>6998546</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5400,24 +5396,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5432,22 +5413,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122817758</v>
+        <v>122817112</v>
       </c>
       <c r="B42" t="n">
-        <v>77699</v>
+        <v>78769</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5460,37 +5441,46 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528610</v>
+        <v>528711</v>
       </c>
       <c r="R42" t="n">
-        <v>6998403</v>
+        <v>6998411</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5519,7 +5509,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5529,12 +5519,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5561,10 +5551,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122817289</v>
+        <v>122818503</v>
       </c>
       <c r="B43" t="n">
-        <v>79145</v>
+        <v>57481</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5577,37 +5567,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>257107</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blek lundlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bacidia rosellizans</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>S.Ekman</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528632</v>
+        <v>528652</v>
       </c>
       <c r="R43" t="n">
-        <v>6998403</v>
+        <v>6998555</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5634,24 +5629,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>09:23</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>09:23</t>
-        </is>
-      </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5666,22 +5651,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122816987</v>
+        <v>122818125</v>
       </c>
       <c r="B44" t="n">
-        <v>79384</v>
+        <v>78506</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5694,21 +5679,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5718,13 +5703,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528755</v>
+        <v>528687</v>
       </c>
       <c r="R44" t="n">
-        <v>6998446</v>
+        <v>6998489</v>
       </c>
       <c r="S44" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5753,7 +5738,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5763,12 +5748,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På bränd jöttetallstubbe</t>
+          <t>På kolad ved på gammal tallstubbe i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5795,10 +5780,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122818573</v>
+        <v>122818675</v>
       </c>
       <c r="B45" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5828,20 +5813,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528630</v>
+        <v>528722</v>
       </c>
       <c r="R45" t="n">
-        <v>6998539</v>
+        <v>6998660</v>
       </c>
       <c r="S45" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5868,11 +5862,21 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5881,51 +5885,26 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122816988</v>
+        <v>122819397</v>
       </c>
       <c r="B46" t="n">
-        <v>57478</v>
+        <v>57497</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5938,16 +5917,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5955,30 +5934,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528756</v>
+        <v>528826</v>
       </c>
       <c r="R46" t="n">
-        <v>6998450</v>
+        <v>6998595</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6010,11 +5988,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på en tall.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6023,31 +5996,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6064,10 +6012,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122818653</v>
+        <v>122818328</v>
       </c>
       <c r="B47" t="n">
-        <v>79847</v>
+        <v>77702</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6080,21 +6028,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6104,13 +6052,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528732</v>
+        <v>528800</v>
       </c>
       <c r="R47" t="n">
-        <v>6998541</v>
+        <v>6998633</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6139,7 +6087,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6149,12 +6097,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På asplåga i gammal barrblandskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6169,22 +6117,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122818025</v>
+        <v>122816979</v>
       </c>
       <c r="B48" t="n">
-        <v>79848</v>
+        <v>78506</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6197,21 +6145,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6221,13 +6169,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528631</v>
+        <v>528730</v>
       </c>
       <c r="R48" t="n">
-        <v>6998469</v>
+        <v>6998447</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6254,9 +6202,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På kolad ved</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6271,22 +6234,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122817869</v>
+        <v>122817289</v>
       </c>
       <c r="B49" t="n">
-        <v>57499</v>
+        <v>79148</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6295,50 +6258,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100110</v>
+        <v>257107</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Blek lundlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Bacidia rosellizans</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>S.Ekman</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528645</v>
+        <v>528632</v>
       </c>
       <c r="R49" t="n">
-        <v>6998384</v>
+        <v>6998403</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6365,9 +6319,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6382,22 +6351,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122817554</v>
+        <v>122818026</v>
       </c>
       <c r="B50" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6410,39 +6379,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528648</v>
+        <v>528631</v>
       </c>
       <c r="R50" t="n">
-        <v>6998359</v>
+        <v>6998469</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6475,11 +6439,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6506,10 +6465,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122818864</v>
+        <v>122817325</v>
       </c>
       <c r="B51" t="n">
-        <v>74863</v>
+        <v>57481</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6522,37 +6481,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528732</v>
+        <v>528640</v>
       </c>
       <c r="R51" t="n">
-        <v>6998659</v>
+        <v>6998336</v>
       </c>
       <c r="S51" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6579,24 +6543,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6611,22 +6565,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122818026</v>
+        <v>122817278</v>
       </c>
       <c r="B52" t="n">
-        <v>79847</v>
+        <v>57481</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6639,34 +6593,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>528631</v>
+        <v>528671</v>
       </c>
       <c r="R52" t="n">
-        <v>6998469</v>
+        <v>6998337</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6699,6 +6658,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6725,10 +6689,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122819397</v>
+        <v>122817054</v>
       </c>
       <c r="B53" t="n">
-        <v>57494</v>
+        <v>79754</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6737,47 +6701,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>528826</v>
+        <v>528755</v>
       </c>
       <c r="R53" t="n">
-        <v>6998595</v>
+        <v>6998448</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6807,9 +6762,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6824,22 +6794,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122816979</v>
+        <v>122817645</v>
       </c>
       <c r="B54" t="n">
-        <v>78503</v>
+        <v>57502</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6848,41 +6818,50 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>100110</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>528730</v>
+        <v>528643</v>
       </c>
       <c r="R54" t="n">
-        <v>6998447</v>
+        <v>6998354</v>
       </c>
       <c r="S54" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6911,7 +6890,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6921,12 +6900,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:03</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>På kolad ved</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6941,22 +6915,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122819033</v>
+        <v>122817142</v>
       </c>
       <c r="B55" t="n">
-        <v>74675</v>
+        <v>57481</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6965,41 +6939,46 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6428</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>528798</v>
+        <v>528699</v>
       </c>
       <c r="R55" t="n">
-        <v>6998603</v>
+        <v>6998430</v>
       </c>
       <c r="S55" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7026,24 +7005,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal barrblandskog</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7058,22 +7027,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122819118</v>
+        <v>122818122</v>
       </c>
       <c r="B56" t="n">
-        <v>78766</v>
+        <v>79851</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7086,37 +7055,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>528690</v>
+        <v>528631</v>
       </c>
       <c r="R56" t="n">
-        <v>6998652</v>
+        <v>6998473</v>
       </c>
       <c r="S56" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7148,11 +7117,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7161,31 +7125,6 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7202,10 +7141,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122818759</v>
+        <v>122818573</v>
       </c>
       <c r="B57" t="n">
-        <v>79847</v>
+        <v>78769</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7218,37 +7157,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>528778</v>
+        <v>528630</v>
       </c>
       <c r="R57" t="n">
-        <v>6998602</v>
+        <v>6998539</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7275,26 +7214,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På gammal asp i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7303,26 +7227,51 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122818032</v>
+        <v>122819058</v>
       </c>
       <c r="B58" t="n">
-        <v>79876</v>
+        <v>78769</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7331,41 +7280,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>528631</v>
+        <v>528654</v>
       </c>
       <c r="R58" t="n">
-        <v>6998469</v>
+        <v>6998628</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7405,6 +7354,31 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7421,10 +7395,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122819058</v>
+        <v>122816988</v>
       </c>
       <c r="B59" t="n">
-        <v>78766</v>
+        <v>57481</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7437,37 +7411,47 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>528654</v>
+        <v>528756</v>
       </c>
       <c r="R59" t="n">
-        <v>6998628</v>
+        <v>6998450</v>
       </c>
       <c r="S59" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7499,6 +7483,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en tall.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -7510,7 +7499,7 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ59" t="inlineStr">
@@ -7525,12 +7514,12 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7548,10 +7537,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122817110</v>
+        <v>122818713</v>
       </c>
       <c r="B60" t="n">
-        <v>78766</v>
+        <v>90955</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7564,37 +7553,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>528711</v>
+        <v>528718</v>
       </c>
       <c r="R60" t="n">
-        <v>6998430</v>
+        <v>6998641</v>
       </c>
       <c r="S60" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7621,24 +7610,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>09:11</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>09:11</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7653,22 +7627,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122818536</v>
+        <v>122818955</v>
       </c>
       <c r="B61" t="n">
-        <v>57478</v>
+        <v>74789</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7681,39 +7655,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>1460</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>528665</v>
+        <v>528791</v>
       </c>
       <c r="R61" t="n">
-        <v>6998574</v>
+        <v>6998633</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7743,14 +7717,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7765,22 +7749,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122818770</v>
+        <v>122818759</v>
       </c>
       <c r="B62" t="n">
-        <v>91243</v>
+        <v>79850</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7793,34 +7777,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>528718</v>
+        <v>528778</v>
       </c>
       <c r="R62" t="n">
-        <v>6998641</v>
+        <v>6998602</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7850,9 +7834,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7867,22 +7866,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122817339</v>
+        <v>122817550</v>
       </c>
       <c r="B63" t="n">
-        <v>79384</v>
+        <v>57481</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7895,37 +7894,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
 